--- a/calculo_mppt.xlsx
+++ b/calculo_mppt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enzo.ferreira\Desktop\dimensionador-fotovoltaico-sigiloso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE5D5A3-77C5-4B9C-9461-BC6A10CE3BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4E7698-5107-441C-9AE4-86036426BA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-4695" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="517">
   <si>
     <t xml:space="preserve">  MAXEON 415 MF PE AL 40 - SPR-MAX3415-BLK-R</t>
   </si>
@@ -350,9 +350,6 @@
   </si>
   <si>
     <t xml:space="preserve">  Maxeon 530W BIFACIAL - SPR-P6-530-UPP (P-Type)</t>
-  </si>
-  <si>
-    <t>Sim</t>
   </si>
   <si>
     <t>Auxsol ASG-6SL-ZL</t>
@@ -2684,8 +2681,24 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFD9E2F3"/>
+          <bgColor rgb="FFD9E2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor theme="4"/>
           <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2700,37 +2713,21 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor theme="4"/>
           <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9E2F3"/>
-          <bgColor rgb="FFD9E2F3"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="MPPT-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="33"/>
-      <tableStyleElement type="firstRowStripe" dxfId="34"/>
+      <tableStyleElement type="headerRow" dxfId="34"/>
+      <tableStyleElement type="firstRowStripe" dxfId="33"/>
       <tableStyleElement type="secondRowStripe" dxfId="32"/>
     </tableStyle>
     <tableStyle name="MPPT-style 2" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="30"/>
-      <tableStyleElement type="firstRowStripe" dxfId="31"/>
+      <tableStyleElement type="headerRow" dxfId="31"/>
+      <tableStyleElement type="firstRowStripe" dxfId="30"/>
       <tableStyleElement type="secondRowStripe" dxfId="29"/>
     </tableStyle>
   </tableStyles>
@@ -3160,19 +3157,20 @@
     <col min="67" max="67" width="11.140625" customWidth="1"/>
     <col min="68" max="68" width="8.85546875" customWidth="1"/>
     <col min="69" max="69" width="8" customWidth="1"/>
-    <col min="70" max="70" width="7.28515625" customWidth="1"/>
-    <col min="71" max="83" width="6.7109375" customWidth="1"/>
-    <col min="84" max="85" width="8.7109375" customWidth="1"/>
-    <col min="86" max="98" width="6.7109375" customWidth="1"/>
-    <col min="99" max="99" width="8.7109375" customWidth="1"/>
-    <col min="100" max="112" width="4.28515625" customWidth="1"/>
-    <col min="113" max="116" width="8.7109375" customWidth="1"/>
+    <col min="70" max="70" width="7.28515625" hidden="1" customWidth="1"/>
+    <col min="71" max="83" width="6.7109375" hidden="1" customWidth="1"/>
+    <col min="84" max="85" width="8.7109375" hidden="1" customWidth="1"/>
+    <col min="86" max="98" width="6.7109375" hidden="1" customWidth="1"/>
+    <col min="99" max="99" width="8.7109375" hidden="1" customWidth="1"/>
+    <col min="100" max="112" width="4.28515625" hidden="1" customWidth="1"/>
+    <col min="113" max="114" width="8.7109375" hidden="1" customWidth="1"/>
+    <col min="115" max="116" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:116" ht="33" customHeight="1">
-      <c r="J1" s="1">
+      <c r="J1" s="1" t="str">
         <f>DL3</f>
-        <v>0</v>
+        <v>SIM</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -3271,9 +3269,9 @@
       <c r="G2" s="69"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="3">
+      <c r="J2" s="3" t="str">
         <f>DL5</f>
-        <v>0</v>
+        <v>SIM</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -3656,14 +3654,10 @@
       <c r="BI3" s="12">
         <v>14.49</v>
       </c>
-      <c r="BJ3" s="12">
-        <v>1</v>
-      </c>
-      <c r="BK3" s="12" t="s">
+      <c r="BJ3" s="12"/>
+      <c r="BK3" s="12"/>
+      <c r="BM3" t="s">
         <v>82</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>83</v>
       </c>
       <c r="BN3">
         <v>6</v>
@@ -3698,19 +3692,23 @@
       <c r="CW3">
         <v>1</v>
       </c>
-      <c r="DK3" s="15"/>
-      <c r="DL3" s="15"/>
+      <c r="DK3" s="15">
+        <v>186192</v>
+      </c>
+      <c r="DL3" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="4" spans="2:116">
       <c r="B4" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" s="7">
         <f>VLOOKUP(B2,BC3:BI309,3,0)</f>
         <v>40.700000000000003</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F4" s="16">
         <v>1</v>
@@ -3721,11 +3719,11 @@
       </c>
       <c r="H4" s="18">
         <f>IF($F4&lt;=J$2,$C$26,0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I4" s="19">
         <f>IF(H4&lt;$C$23,0,H4)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J4" s="20">
         <v>0</v>
@@ -3889,7 +3887,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BD4" s="12">
         <v>535</v>
@@ -3909,14 +3907,10 @@
       <c r="BI4" s="12">
         <v>14.45</v>
       </c>
-      <c r="BJ4" s="12">
-        <v>2</v>
-      </c>
-      <c r="BK4" s="12" t="s">
-        <v>82</v>
-      </c>
+      <c r="BJ4" s="12"/>
+      <c r="BK4" s="12"/>
       <c r="BM4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="BN4">
         <v>10.5</v>
@@ -3955,14 +3949,14 @@
     </row>
     <row r="5" spans="2:116">
       <c r="B5" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="7">
         <f>VLOOKUP(B2,BC3:BI309,4,0)</f>
         <v>35.299999999999997</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F5" s="26">
         <v>2</v>
@@ -3973,11 +3967,11 @@
       </c>
       <c r="H5" s="21">
         <f t="shared" ref="H5:H8" si="2">IF($F5&lt;=J$2,H$4*$F5,0)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I5" s="19">
         <f>IF(H4&lt;$C$23,0,H5)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J5" s="20">
         <v>1</v>
@@ -4141,7 +4135,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="BD5" s="12">
         <v>710</v>
@@ -4161,14 +4155,10 @@
       <c r="BI5" s="12">
         <v>18.61</v>
       </c>
-      <c r="BJ5" s="12">
-        <v>3</v>
-      </c>
-      <c r="BK5" s="12" t="s">
-        <v>82</v>
-      </c>
+      <c r="BJ5" s="12"/>
+      <c r="BK5" s="12"/>
       <c r="BM5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="BN5">
         <v>10</v>
@@ -4202,8 +4192,12 @@
       <c r="CW5">
         <v>1</v>
       </c>
-      <c r="DK5" s="15"/>
-      <c r="DL5" s="15"/>
+      <c r="DK5" s="15">
+        <v>167963</v>
+      </c>
+      <c r="DL5" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="6" spans="2:116">
       <c r="B6" s="7" t="s">
@@ -4225,11 +4219,11 @@
       </c>
       <c r="H6" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I6" s="19">
         <f>IF(H4&lt;$C$23,0,H6)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J6" s="20">
         <v>0</v>
@@ -4393,7 +4387,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BD6">
         <v>710</v>
@@ -4414,13 +4408,13 @@
         <v>18.45</v>
       </c>
       <c r="BJ6" s="12">
-        <v>4</v>
+        <v>201741</v>
       </c>
       <c r="BK6" s="12" t="s">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="BM6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BN6">
         <v>15</v>
@@ -4455,8 +4449,12 @@
       <c r="CW6">
         <v>1</v>
       </c>
-      <c r="DK6" s="25"/>
-      <c r="DL6" s="25"/>
+      <c r="DK6" s="25">
+        <v>179270</v>
+      </c>
+      <c r="DL6" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="7" spans="2:116">
       <c r="B7" s="7" t="s">
@@ -4467,7 +4465,7 @@
         <v>12.64</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F7" s="26">
         <v>4</v>
@@ -4478,11 +4476,11 @@
       </c>
       <c r="H7" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I7" s="19">
         <f>IF(H4&lt;$C$23,0,H7)</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J7" s="20">
         <v>0</v>
@@ -4646,7 +4644,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BD7" s="12">
         <v>615</v>
@@ -4666,14 +4664,10 @@
       <c r="BI7" s="12">
         <v>16.14</v>
       </c>
-      <c r="BJ7" s="12">
-        <v>5</v>
-      </c>
-      <c r="BK7" s="12" t="s">
-        <v>82</v>
-      </c>
+      <c r="BJ7" s="12"/>
+      <c r="BK7" s="12"/>
       <c r="BM7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BN7">
         <v>15</v>
@@ -4722,11 +4716,11 @@
       </c>
       <c r="H8" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I8" s="19">
         <f>IF(H4&lt;$C$23,0,H8)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J8" s="20">
         <v>0</v>
@@ -4890,7 +4884,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="BD8" s="12">
         <v>620</v>
@@ -4910,14 +4904,10 @@
       <c r="BI8" s="12">
         <v>16.3</v>
       </c>
-      <c r="BJ8" s="12">
-        <v>7</v>
-      </c>
-      <c r="BK8" s="12" t="s">
-        <v>82</v>
-      </c>
+      <c r="BJ8" s="12"/>
+      <c r="BK8" s="12"/>
       <c r="BM8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="BN8">
         <v>15</v>
@@ -4952,18 +4942,22 @@
       <c r="CW8">
         <v>2</v>
       </c>
-      <c r="DK8" s="25"/>
-      <c r="DL8" s="25"/>
+      <c r="DK8" s="25">
+        <v>186183</v>
+      </c>
+      <c r="DL8" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="9" spans="2:116">
       <c r="B9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="30">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>98</v>
-      </c>
-      <c r="C9" s="30">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>99</v>
       </c>
       <c r="F9" s="26">
         <v>1</v>
@@ -4974,11 +4968,11 @@
       </c>
       <c r="H9" s="21">
         <f>IF(AND($F9&lt;=J$2,H4&gt;0),H4-1,0)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I9" s="19">
         <f>IF(H9&lt;$C$23,0,H9)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J9" s="20">
         <v>0</v>
@@ -5142,7 +5136,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC9" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BD9" s="12">
         <v>620</v>
@@ -5163,13 +5157,13 @@
         <v>16.3</v>
       </c>
       <c r="BJ9" s="12">
-        <v>6</v>
+        <v>179728</v>
       </c>
       <c r="BK9" s="12" t="s">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="BM9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="BN9">
         <v>20</v>
@@ -5204,19 +5198,23 @@
       <c r="CW9">
         <v>2</v>
       </c>
-      <c r="DK9" s="15"/>
-      <c r="DL9" s="15"/>
+      <c r="DK9" s="15">
+        <v>179271</v>
+      </c>
+      <c r="DL9" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="10" spans="2:116">
       <c r="B10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10">
         <f>$C$4+($C$4*$C$6/100*($C$9-25))</f>
         <v>43.04025</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F10" s="26">
         <v>2</v>
@@ -5227,11 +5225,11 @@
       </c>
       <c r="H10" s="21">
         <f>IF(AND($F10&lt;=J$2,H9&gt;0),H9*$F10,0)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I10" s="19">
         <f>IF(H9&lt;$C$23,0,H10)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J10" s="20">
         <v>0</v>
@@ -5395,7 +5393,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="BD10" s="12">
         <v>610</v>
@@ -5418,7 +5416,7 @@
       <c r="BJ10" s="12"/>
       <c r="BK10" s="12"/>
       <c r="BM10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="BN10">
         <v>20</v>
@@ -5458,13 +5456,13 @@
     </row>
     <row r="11" spans="2:116">
       <c r="B11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C11" s="30">
         <v>75</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F11" s="26">
         <v>3</v>
@@ -5475,11 +5473,11 @@
       </c>
       <c r="H11" s="21">
         <f>IF(AND($F11&lt;=J$2,H9&gt;0),H9*$F11,0)</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I11" s="19">
         <f>IF(H9&lt;$C$23,0,H11)</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J11" s="20">
         <v>0</v>
@@ -5643,7 +5641,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="BD11">
         <v>590</v>
@@ -5664,7 +5662,7 @@
         <v>13.81</v>
       </c>
       <c r="BM11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="BN11">
         <v>25</v>
@@ -5699,19 +5697,23 @@
       <c r="CW11">
         <v>2</v>
       </c>
-      <c r="DK11" s="31"/>
-      <c r="DL11" s="31"/>
+      <c r="DK11" s="31">
+        <v>179272</v>
+      </c>
+      <c r="DL11" s="31" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="12" spans="2:116">
       <c r="B12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12">
         <f>$C$5+($C$5*$C$6/100*($C$11-25))</f>
         <v>31.240499999999997</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F12" s="26">
         <v>4</v>
@@ -5722,11 +5724,11 @@
       </c>
       <c r="H12" s="21">
         <f>IF(AND($F12&lt;=J$2,H9&gt;0),H9*$F12,0)</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I12" s="19">
         <f>IF(H9&lt;$C$23,0,H12)</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J12" s="20">
         <v>0</v>
@@ -5890,7 +5892,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BD12" s="12">
         <v>615</v>
@@ -5913,7 +5915,7 @@
       <c r="BJ12" s="12"/>
       <c r="BK12" s="12"/>
       <c r="BM12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BN12">
         <v>25</v>
@@ -5961,11 +5963,11 @@
       </c>
       <c r="H13" s="21">
         <f>IF(AND($F13&lt;=J$2,H9&gt;0),H9*$F13,0)</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I13" s="19">
         <f>IF(H9&lt;$C$23,0,H13)</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J13" s="20">
         <v>0</v>
@@ -6129,7 +6131,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BD13" s="12">
         <v>620</v>
@@ -6152,7 +6154,7 @@
       <c r="BJ13" s="12"/>
       <c r="BK13" s="12"/>
       <c r="BM13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BN13">
         <v>25</v>
@@ -6205,12 +6207,16 @@
       <c r="CY13">
         <v>1</v>
       </c>
-      <c r="DK13" s="15"/>
-      <c r="DL13" s="15"/>
+      <c r="DK13" s="15">
+        <v>186184</v>
+      </c>
+      <c r="DL13" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="14" spans="2:116">
       <c r="B14" s="73" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
@@ -6223,11 +6229,11 @@
       </c>
       <c r="H14" s="21">
         <f>IF(AND($F14&lt;=J$2,H9&gt;0),H9-1,0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I14" s="19">
         <f>IF(H14&lt;$C$23,0,H14)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J14" s="20">
         <v>0</v>
@@ -6391,7 +6397,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="BD14" s="12">
         <v>625</v>
@@ -6414,7 +6420,7 @@
       <c r="BJ14" s="12"/>
       <c r="BK14" s="12"/>
       <c r="BM14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BN14">
         <v>30</v>
@@ -6458,19 +6464,23 @@
       <c r="CX14">
         <v>2</v>
       </c>
-      <c r="DK14" s="25"/>
-      <c r="DL14" s="25"/>
+      <c r="DK14" s="25">
+        <v>179274</v>
+      </c>
+      <c r="DL14" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="15" spans="2:116">
       <c r="B15" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C15" s="32">
         <f>VLOOKUP($B$14,$BM$3:$DJ$315,2,0)</f>
         <v>10.5</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F15" s="26">
         <v>2</v>
@@ -6481,11 +6491,11 @@
       </c>
       <c r="H15" s="21">
         <f>IF(AND($F15&lt;=J$2,H14&gt;0),H14*$F15,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I15" s="19">
         <f>IF(H14&lt;$C$23,0,H15)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J15" s="20">
         <v>0</v>
@@ -6649,7 +6659,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BD15">
         <v>550</v>
@@ -6672,7 +6682,7 @@
       <c r="BJ15" s="12"/>
       <c r="BK15" s="12"/>
       <c r="BM15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BN15">
         <v>30</v>
@@ -6721,7 +6731,7 @@
     </row>
     <row r="16" spans="2:116">
       <c r="B16" s="32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16" s="32">
         <f>VLOOKUP($B$14,$BM$3:$DJ$315,3,0)</f>
@@ -6739,11 +6749,11 @@
       </c>
       <c r="H16" s="21">
         <f>IF(AND($F16&lt;=J$2,H14&gt;0),H14*$F16,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I16" s="19">
         <f>IF(H14&lt;$C$23,0,H16)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J16" s="20">
         <v>0</v>
@@ -6907,7 +6917,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BD16">
         <v>370</v>
@@ -6930,7 +6940,7 @@
       <c r="BJ16" s="12"/>
       <c r="BK16" s="12"/>
       <c r="BM16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BN16">
         <v>3</v>
@@ -6968,19 +6978,23 @@
       <c r="CV16">
         <v>1</v>
       </c>
-      <c r="DK16" s="25"/>
-      <c r="DL16" s="25"/>
+      <c r="DK16" s="25">
+        <v>168764</v>
+      </c>
+      <c r="DL16" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="17" spans="2:116">
       <c r="B17" s="32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C17" s="32">
         <f>VLOOKUP($B$14,$BM$3:$DJ$315,4,0)</f>
         <v>550</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F17" s="26">
         <v>4</v>
@@ -6991,11 +7005,11 @@
       </c>
       <c r="H17" s="21">
         <f>IF(AND($F17&lt;=J$2,H14&gt;0),H14*$F17,0)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I17" s="19">
         <f>IF(H14&lt;$C$23,0,H17)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J17" s="20">
         <v>0</v>
@@ -7159,7 +7173,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BD17">
         <v>400</v>
@@ -7182,7 +7196,7 @@
       <c r="BJ17" s="12"/>
       <c r="BK17" s="12"/>
       <c r="BM17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BN17">
         <v>40</v>
@@ -7234,19 +7248,23 @@
       <c r="CY17">
         <v>1</v>
       </c>
-      <c r="DK17" s="15"/>
-      <c r="DL17" s="15"/>
+      <c r="DK17" s="15">
+        <v>186177</v>
+      </c>
+      <c r="DL17" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="18" spans="2:116">
       <c r="B18" s="32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C18" s="32">
         <f>VLOOKUP($B$14,$BM$3:$DJ$315,5,0)</f>
         <v>40</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F18" s="26">
         <v>5</v>
@@ -7257,11 +7275,11 @@
       </c>
       <c r="H18" s="21">
         <f>IF(AND($F18&lt;=J$2,H14&gt;0),H14*$F18,0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I18" s="19">
         <f>IF(H14&lt;$C$23,0,H18)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J18" s="20">
         <v>0</v>
@@ -7425,7 +7443,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BD18">
         <v>405</v>
@@ -7448,7 +7466,7 @@
       <c r="BJ18" s="12"/>
       <c r="BK18" s="12"/>
       <c r="BM18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BN18">
         <v>4</v>
@@ -7482,8 +7500,12 @@
       <c r="CW18">
         <v>1</v>
       </c>
-      <c r="DK18" s="25"/>
-      <c r="DL18" s="25"/>
+      <c r="DK18" s="25">
+        <v>168765</v>
+      </c>
+      <c r="DL18" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="19" spans="2:116">
       <c r="F19" s="26">
@@ -7495,11 +7517,11 @@
       </c>
       <c r="H19" s="21">
         <f>IF(AND($F19&lt;=J$2,H14&gt;0),H14-1,0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I19" s="19">
         <f>IF(H19&lt;$C$23,0,H19)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J19" s="20">
         <v>0</v>
@@ -7663,7 +7685,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BD19">
         <v>420</v>
@@ -7686,7 +7708,7 @@
       <c r="BJ19" s="12"/>
       <c r="BK19" s="12"/>
       <c r="BM19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BN19">
         <v>5</v>
@@ -7737,7 +7759,7 @@
     </row>
     <row r="20" spans="2:116">
       <c r="B20" s="35" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C20" s="36" t="e">
         <f>$BA$65</f>
@@ -7752,11 +7774,11 @@
       </c>
       <c r="H20" s="21">
         <f>IF(AND($F20&lt;=J$2,H19&gt;0),H19*$F20,0)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I20" s="19">
         <f>IF(H19&lt;$C$23,0,H20)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J20" s="20">
         <v>0</v>
@@ -7920,7 +7942,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BD20">
         <v>435</v>
@@ -7943,7 +7965,7 @@
       <c r="BJ20" s="12"/>
       <c r="BK20" s="12"/>
       <c r="BM20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BN20">
         <v>6</v>
@@ -7977,19 +7999,23 @@
       <c r="CW20">
         <v>1</v>
       </c>
-      <c r="DK20" s="25"/>
-      <c r="DL20" s="25"/>
+      <c r="DK20" s="25">
+        <v>168766</v>
+      </c>
+      <c r="DL20" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="21" spans="2:116" ht="15.75" customHeight="1">
       <c r="B21" s="37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C21" s="38" t="e">
         <f>C20*C3</f>
         <v>#REF!</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F21" s="26">
         <v>3</v>
@@ -8000,11 +8026,11 @@
       </c>
       <c r="H21" s="21">
         <f>IF(AND($F21&lt;=J$2,H19&gt;0),H19*$F21,0)</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I21" s="19">
         <f>IF(H19&lt;$C$23,0,H21)</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J21" s="20">
         <v>0</v>
@@ -8168,7 +8194,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BD21">
         <v>440</v>
@@ -8191,7 +8217,7 @@
       <c r="BJ21" s="12"/>
       <c r="BK21" s="12"/>
       <c r="BM21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="BN21">
         <v>7.5</v>
@@ -8237,8 +8263,12 @@
       <c r="CW21">
         <v>1</v>
       </c>
-      <c r="DK21" s="15"/>
-      <c r="DL21" s="15"/>
+      <c r="DK21" s="15">
+        <v>167958</v>
+      </c>
+      <c r="DL21" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="22" spans="2:116" ht="15.75" customHeight="1">
       <c r="F22" s="26">
@@ -8250,11 +8280,11 @@
       </c>
       <c r="H22" s="21">
         <f>IF(AND($F22&lt;=J$2,H19&gt;0),H19*$F22,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I22" s="19">
         <f>IF(H19&lt;$C$23,0,H22)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J22" s="20">
         <v>0</v>
@@ -8418,7 +8448,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="BD22">
         <v>445</v>
@@ -8441,7 +8471,7 @@
       <c r="BJ22" s="12"/>
       <c r="BK22" s="12"/>
       <c r="BM22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BN22">
         <v>75</v>
@@ -8493,12 +8523,16 @@
       <c r="CY22">
         <v>3</v>
       </c>
-      <c r="DK22" s="25"/>
-      <c r="DL22" s="25"/>
+      <c r="DK22" s="25">
+        <v>186180</v>
+      </c>
+      <c r="DL22" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="23" spans="2:116" ht="15.75" customHeight="1">
       <c r="B23" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C23" s="36">
         <f>ROUNDUP($C$18/$C$12,0)</f>
@@ -8513,11 +8547,11 @@
       </c>
       <c r="H23" s="21">
         <f>IF(AND($F23&lt;=J$2,H19&gt;0),H19*$F23,0)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I23" s="19">
         <f>IF(H19&lt;$C$23,0,H23)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J23" s="20">
         <v>0</v>
@@ -8681,7 +8715,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD23">
         <v>450</v>
@@ -8704,7 +8738,7 @@
       <c r="BJ23" s="12"/>
       <c r="BK23" s="12"/>
       <c r="BM23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BN23">
         <v>75</v>
@@ -8792,12 +8826,16 @@
       <c r="DC23">
         <v>2</v>
       </c>
-      <c r="DK23" s="15"/>
-      <c r="DL23" s="15"/>
+      <c r="DK23" s="15">
+        <v>186186</v>
+      </c>
+      <c r="DL23" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="24" spans="2:116" ht="15.75" customHeight="1">
       <c r="B24" s="37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C24" s="38">
         <f>C23*C3</f>
@@ -8812,11 +8850,11 @@
       </c>
       <c r="H24" s="21">
         <f>IF(AND($F24&lt;=J$2,H19&gt;0),H19-1,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I24" s="19">
         <f>IF(H24&lt;$C$23,0,H24)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J24" s="20">
         <v>0</v>
@@ -8980,7 +9018,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC24" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BD24">
         <v>455</v>
@@ -9003,7 +9041,7 @@
       <c r="BJ24" s="12"/>
       <c r="BK24" s="12"/>
       <c r="BM24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="BN24">
         <v>100</v>
@@ -9130,11 +9168,11 @@
       </c>
       <c r="H25" s="21">
         <f>IF(AND($F25&lt;=J$2,H24&gt;0),H24*$F25,0)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I25" s="19">
         <f>IF(H24&lt;$C$23,0,H25)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J25" s="20">
         <v>0</v>
@@ -9298,7 +9336,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="BD25">
         <v>535</v>
@@ -9321,7 +9359,7 @@
       <c r="BJ25" s="12"/>
       <c r="BK25" s="12"/>
       <c r="BM25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BN25">
         <v>110</v>
@@ -9440,7 +9478,7 @@
     </row>
     <row r="26" spans="2:116" ht="15.75" customHeight="1">
       <c r="B26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C26">
         <f>ROUNDDOWN($C$17/$C$10,0)</f>
@@ -9455,11 +9493,11 @@
       </c>
       <c r="H26" s="21">
         <f>IF(AND($F26&lt;=J$2,H24&gt;0),H24*$F26,0)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I26" s="19">
         <f>IF(H24&lt;$C$23,0,H26)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J26" s="20">
         <v>0</v>
@@ -9623,7 +9661,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC26" s="40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BD26">
         <v>550</v>
@@ -9646,7 +9684,7 @@
       <c r="BJ26" s="12"/>
       <c r="BK26" s="12"/>
       <c r="BM26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="BN26">
         <v>15</v>
@@ -9709,7 +9747,7 @@
     </row>
     <row r="27" spans="2:116" ht="15.75" customHeight="1">
       <c r="B27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C27">
         <f>ROUNDDOWN($C$16/$C$3,0)</f>
@@ -9724,11 +9762,11 @@
       </c>
       <c r="H27" s="21">
         <f>IF(AND($F27&lt;=J$2,H24&gt;0),H24*$F27,0)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I27" s="19">
         <f>IF(H24&lt;$C$23,0,H27)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J27" s="20">
         <v>0</v>
@@ -9892,7 +9930,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="BD27">
         <v>550</v>
@@ -9911,7 +9949,7 @@
       <c r="BJ27" s="12"/>
       <c r="BK27" s="12"/>
       <c r="BM27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="BN27">
         <v>20</v>
@@ -9986,11 +10024,11 @@
       </c>
       <c r="H28" s="21">
         <f>IF(AND($F28&lt;=J$2,H24&gt;0),H24*$F28,0)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I28" s="19">
         <f>IF(H24&lt;$C$23,0,H28)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J28" s="20">
         <v>0</v>
@@ -10154,7 +10192,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC28" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BD28">
         <v>550</v>
@@ -10177,7 +10215,7 @@
       <c r="BJ28" s="12"/>
       <c r="BK28" s="12"/>
       <c r="BM28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="BN28">
         <v>20</v>
@@ -10248,11 +10286,11 @@
       </c>
       <c r="H29" s="21">
         <f>IF(AND($F29&lt;=J$2,H24&gt;0),H24-1,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I29" s="19">
         <f>IF(H29&lt;$C$23,0,H29)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J29" s="20">
         <v>0</v>
@@ -10416,7 +10454,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="BD29" s="12">
         <v>610</v>
@@ -10439,7 +10477,7 @@
       <c r="BJ29" s="12"/>
       <c r="BK29" s="12"/>
       <c r="BM29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="BN29">
         <v>250</v>
@@ -10576,11 +10614,11 @@
       </c>
       <c r="H30" s="21">
         <f>IF(AND($F30&lt;=J$2,H29&gt;0),H29*$F30,0)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I30" s="19">
         <f>IF(H29&lt;$C$23,0,H30)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J30" s="20">
         <v>0</v>
@@ -10744,7 +10782,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC30" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BD30" s="12">
         <v>700</v>
@@ -10767,7 +10805,7 @@
       <c r="BJ30" s="12"/>
       <c r="BK30" s="12"/>
       <c r="BM30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="BN30">
         <v>25</v>
@@ -10855,11 +10893,11 @@
       </c>
       <c r="H31" s="21">
         <f>IF(AND($F31&lt;=J$2,H29&gt;0),H29*$F31,0)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I31" s="19">
         <f>IF(H29&lt;$C$23,0,H31)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J31" s="20">
         <v>0</v>
@@ -11023,7 +11061,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BD31" s="12">
         <v>700</v>
@@ -11046,7 +11084,7 @@
       <c r="BJ31" s="12"/>
       <c r="BK31" s="12"/>
       <c r="BM31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="BN31">
         <v>25</v>
@@ -11118,7 +11156,7 @@
     </row>
     <row r="32" spans="2:116" ht="15.75" customHeight="1">
       <c r="B32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C32">
         <f t="shared" ref="C32:C46" si="24">ROUNDDOWN(C65/$C$7,0)</f>
@@ -11133,11 +11171,11 @@
       </c>
       <c r="H32" s="21">
         <f>IF(AND($F32&lt;=J$2,H29&gt;0),H29*$F32,0)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I32" s="19">
         <f>IF(H29&lt;$C$23,0,H32)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J32" s="20">
         <v>0</v>
@@ -11301,7 +11339,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="BD32">
         <v>440</v>
@@ -11324,7 +11362,7 @@
       <c r="BJ32" s="12"/>
       <c r="BK32" s="12"/>
       <c r="BM32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BN32">
         <v>25</v>
@@ -11387,7 +11425,7 @@
     </row>
     <row r="33" spans="2:116" ht="15.75" customHeight="1">
       <c r="B33" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C33">
         <f t="shared" si="24"/>
@@ -11402,11 +11440,11 @@
       </c>
       <c r="H33" s="21">
         <f>IF(AND($F33&lt;=J$2,H29&gt;0),H29*$F33,0)</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I33" s="19">
         <f>IF(H29&lt;$C$23,0,H33)</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J33" s="20">
         <v>0</v>
@@ -11570,7 +11608,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="BD33">
         <v>540</v>
@@ -11593,7 +11631,7 @@
       <c r="BJ33" s="12"/>
       <c r="BK33" s="12"/>
       <c r="BM33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BN33">
         <v>30</v>
@@ -11673,7 +11711,7 @@
     </row>
     <row r="34" spans="2:116" ht="15.75" customHeight="1">
       <c r="B34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C34">
         <f t="shared" si="24"/>
@@ -11688,11 +11726,11 @@
       </c>
       <c r="H34" s="21">
         <f>IF(AND($F34&lt;=J$2,H29&gt;0),H29-1,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I34" s="19">
         <f>IF(H34&lt;$C$23,0,H34)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J34" s="20">
         <v>0</v>
@@ -11856,7 +11894,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="BD34">
         <v>545</v>
@@ -11879,7 +11917,7 @@
       <c r="BJ34" s="12"/>
       <c r="BK34" s="12"/>
       <c r="BM34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="BN34">
         <v>30</v>
@@ -11949,7 +11987,7 @@
     </row>
     <row r="35" spans="2:116" ht="15.75" customHeight="1">
       <c r="B35" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C35">
         <f t="shared" si="24"/>
@@ -11964,11 +12002,11 @@
       </c>
       <c r="H35" s="21">
         <f>IF(AND($F35&lt;=J$2,H34&gt;0),H34*$F35,0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I35" s="19">
         <f>IF(H34&lt;$C$23,0,H35)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J35" s="20">
         <v>0</v>
@@ -12132,7 +12170,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC35" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="BD35">
         <v>555</v>
@@ -12155,7 +12193,7 @@
       <c r="BJ35" s="12"/>
       <c r="BK35" s="12"/>
       <c r="BM35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="BN35">
         <v>30</v>
@@ -12218,7 +12256,7 @@
     </row>
     <row r="36" spans="2:116" ht="15.75" customHeight="1">
       <c r="B36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C36">
         <f t="shared" si="24"/>
@@ -12233,11 +12271,11 @@
       </c>
       <c r="H36" s="21">
         <f>IF(AND($F36&lt;=J$2,H34&gt;0),H34*$F36,0)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I36" s="19">
         <f>IF(H34&lt;$C$23,0,H36)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J36" s="20">
         <v>0</v>
@@ -12401,7 +12439,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC36" s="40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="BD36">
         <v>450</v>
@@ -12424,7 +12462,7 @@
       <c r="BJ36" s="12"/>
       <c r="BK36" s="12"/>
       <c r="BM36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="BN36">
         <v>3</v>
@@ -12480,7 +12518,7 @@
     </row>
     <row r="37" spans="2:116" ht="15.75" customHeight="1">
       <c r="B37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C37">
         <f t="shared" si="24"/>
@@ -12495,11 +12533,11 @@
       </c>
       <c r="H37" s="21">
         <f>IF(AND($F37&lt;=J$2,H34&gt;0),H34*$F37,0)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I37" s="19">
         <f>IF(H34&lt;$C$23,0,H37)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J37" s="20">
         <v>0</v>
@@ -12663,7 +12701,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BD37">
         <v>360</v>
@@ -12686,7 +12724,7 @@
       <c r="BJ37" s="12"/>
       <c r="BK37" s="12"/>
       <c r="BM37" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="BN37">
         <v>50</v>
@@ -12763,7 +12801,7 @@
     </row>
     <row r="38" spans="2:116" ht="15.75" customHeight="1">
       <c r="B38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C38">
         <f t="shared" si="24"/>
@@ -12778,11 +12816,11 @@
       </c>
       <c r="H38" s="21">
         <f>IF(AND($F38&lt;=J$2,H34&gt;0),H34*$F38,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I38" s="19">
         <f>IF(H34&lt;$C$23,0,H38)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J38" s="20">
         <v>0</v>
@@ -12946,7 +12984,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC38" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="BD38">
         <v>400</v>
@@ -12969,7 +13007,7 @@
       <c r="BJ38" s="12"/>
       <c r="BK38" s="12"/>
       <c r="BM38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="BN38">
         <v>5</v>
@@ -13032,7 +13070,7 @@
     </row>
     <row r="39" spans="2:116" ht="15.75" customHeight="1">
       <c r="B39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C39">
         <f t="shared" si="24"/>
@@ -13047,11 +13085,11 @@
       </c>
       <c r="H39" s="21">
         <f>IF(AND($F39&lt;=J$2,H34&gt;0),H34-1,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I39" s="19">
         <f>IF(H39&lt;$C$23,0,H39)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J39" s="20">
         <v>0</v>
@@ -13215,7 +13253,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC39" s="40" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BD39">
         <v>560</v>
@@ -13238,7 +13276,7 @@
       <c r="BJ39" s="12"/>
       <c r="BK39" s="12"/>
       <c r="BM39" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BN39">
         <v>5</v>
@@ -13302,7 +13340,7 @@
     </row>
     <row r="40" spans="2:116" ht="15.75" customHeight="1">
       <c r="B40" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C40">
         <f t="shared" si="24"/>
@@ -13317,11 +13355,11 @@
       </c>
       <c r="H40" s="21">
         <f>IF(AND($F40&lt;=J$2,H39&gt;0),H39*$F40,0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I40" s="19">
         <f>IF(H39&lt;$C$23,0,H40)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J40" s="20">
         <v>0</v>
@@ -13485,7 +13523,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC40" s="40" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BD40">
         <v>585</v>
@@ -13508,7 +13546,7 @@
       <c r="BJ40" s="12"/>
       <c r="BK40" s="12"/>
       <c r="BM40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="BN40">
         <v>5</v>
@@ -13571,7 +13609,7 @@
     </row>
     <row r="41" spans="2:116" ht="15.75" customHeight="1">
       <c r="B41" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C41">
         <f t="shared" si="24"/>
@@ -13586,11 +13624,11 @@
       </c>
       <c r="H41" s="21">
         <f>IF(AND($F41&lt;=J$2,H39&gt;0),H39*$F41,0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I41" s="19">
         <f>IF(H39&lt;$C$23,0,H41)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J41" s="20">
         <v>0</v>
@@ -13754,7 +13792,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BD41" s="12">
         <v>610</v>
@@ -13777,7 +13815,7 @@
       <c r="BJ41" s="12"/>
       <c r="BK41" s="12"/>
       <c r="BM41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BN41">
         <v>60</v>
@@ -13854,7 +13892,7 @@
     </row>
     <row r="42" spans="2:116" ht="15.75" customHeight="1">
       <c r="B42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C42">
         <f t="shared" si="24"/>
@@ -13869,11 +13907,11 @@
       </c>
       <c r="H42" s="21">
         <f>IF(AND($F42&lt;=J$2,H39&gt;0),H39*$F42,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I42" s="19">
         <f>IF(H39&lt;$C$23,0,H42)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J42" s="20">
         <v>0</v>
@@ -14037,7 +14075,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BD42">
         <v>590</v>
@@ -14058,7 +14096,7 @@
         <v>14.03</v>
       </c>
       <c r="BM42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BN42">
         <v>75</v>
@@ -14172,7 +14210,7 @@
     </row>
     <row r="43" spans="2:116" ht="15.75" customHeight="1">
       <c r="B43" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C43">
         <f t="shared" si="24"/>
@@ -14187,11 +14225,11 @@
       </c>
       <c r="H43" s="21">
         <f>IF(AND($F43&lt;=J$2,H39&gt;0),H39*$F43,0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I43" s="19">
         <f>IF(H39&lt;$C$23,0,H43)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J43" s="20">
         <v>0</v>
@@ -14355,7 +14393,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC43" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BD43">
         <v>375</v>
@@ -14374,7 +14412,7 @@
       <c r="BJ43" s="12"/>
       <c r="BK43" s="12"/>
       <c r="BM43" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BN43">
         <v>7</v>
@@ -14437,7 +14475,7 @@
     </row>
     <row r="44" spans="2:116" ht="15.75" customHeight="1">
       <c r="B44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C44">
         <f t="shared" si="24"/>
@@ -14452,11 +14490,11 @@
       </c>
       <c r="H44" s="21">
         <f>IF(AND($F44&lt;=J$2,H39&gt;0),H39-1,0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I44" s="19">
         <f>IF(H44&lt;$C$23,0,H44)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J44" s="20">
         <v>0</v>
@@ -14620,7 +14658,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BD44">
         <v>400</v>
@@ -14643,7 +14681,7 @@
       <c r="BJ44" s="12"/>
       <c r="BK44" s="12"/>
       <c r="BM44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="BN44">
         <v>7</v>
@@ -14706,7 +14744,7 @@
     </row>
     <row r="45" spans="2:116" ht="15.75" customHeight="1">
       <c r="B45" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C45">
         <f t="shared" si="24"/>
@@ -14721,11 +14759,11 @@
       </c>
       <c r="H45" s="21">
         <f>IF(AND($F45&lt;=J$2,H44&gt;0),H44*$F45,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I45" s="19">
         <f>IF(H44&lt;$C$23,0,H45)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J45" s="20">
         <v>0</v>
@@ -14889,7 +14927,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC45" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BD45" s="12">
         <v>700</v>
@@ -14912,7 +14950,7 @@
       <c r="BJ45" s="12"/>
       <c r="BK45" s="12"/>
       <c r="BM45" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="BN45">
         <v>8</v>
@@ -14982,7 +15020,7 @@
     </row>
     <row r="46" spans="2:116" ht="15.75" customHeight="1">
       <c r="B46" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46">
         <f t="shared" si="24"/>
@@ -14997,11 +15035,11 @@
       </c>
       <c r="H46" s="21">
         <f>IF(AND($F46&lt;=J$2,H44&gt;0),H44*$F46,0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I46" s="19">
         <f>IF(H44&lt;$C$23,0,H46)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J46" s="20">
         <v>0</v>
@@ -15165,7 +15203,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC46" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="BD46" s="12">
         <v>570</v>
@@ -15188,7 +15226,7 @@
       <c r="BJ46" s="12"/>
       <c r="BK46" s="12"/>
       <c r="BM46" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BN46">
         <v>9</v>
@@ -15259,11 +15297,11 @@
       </c>
       <c r="H47" s="21">
         <f>IF(AND($F47&lt;=J$2,H44&gt;0),H44*$F47,0)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I47" s="19">
         <f>IF(H44&lt;$C$23,0,H47)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J47" s="20">
         <v>0</v>
@@ -15427,7 +15465,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC47" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BD47" s="12">
         <v>585</v>
@@ -15450,7 +15488,7 @@
       <c r="BJ47" s="12"/>
       <c r="BK47" s="12"/>
       <c r="BM47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="BN47">
         <v>3.6</v>
@@ -15521,11 +15559,11 @@
       </c>
       <c r="H48" s="21">
         <f>IF(AND($F48&lt;=J$2,H44&gt;0),H44*$F48,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I48" s="19">
         <f>IF(H44&lt;$C$23,0,H48)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J48" s="20">
         <v>0</v>
@@ -15689,7 +15727,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="BD48">
         <v>590</v>
@@ -15710,7 +15748,7 @@
         <v>14.05</v>
       </c>
       <c r="BM48" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BN48">
         <v>5</v>
@@ -15781,11 +15819,11 @@
       </c>
       <c r="H49" s="21">
         <f>IF(AND($F49&lt;=J$2,H44&gt;0),H44-1,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I49" s="19">
         <f>IF(H49&lt;$C$23,0,H49)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J49" s="20">
         <v>0</v>
@@ -15949,7 +15987,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC49" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BD49" s="12">
         <v>585</v>
@@ -15972,7 +16010,7 @@
       <c r="BJ49" s="12"/>
       <c r="BK49" s="12"/>
       <c r="BM49" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="BN49">
         <v>7</v>
@@ -16050,11 +16088,11 @@
       </c>
       <c r="H50" s="21">
         <f>IF(AND($F50&lt;=J$2,H49&gt;0),H49*$F50,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I50" s="19">
         <f>IF(H49&lt;$C$23,0,H50)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J50" s="20">
         <v>0</v>
@@ -16218,7 +16256,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC50" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BD50">
         <v>610</v>
@@ -16239,7 +16277,7 @@
         <v>15.94</v>
       </c>
       <c r="BM50" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BN50">
         <v>9</v>
@@ -16317,11 +16355,11 @@
       </c>
       <c r="H51" s="21">
         <f>IF(AND($F51&lt;=J$2,H49&gt;0),H49*$F51,0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I51" s="19">
         <f>IF(H49&lt;$C$23,0,H51)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J51" s="20">
         <v>0</v>
@@ -16485,7 +16523,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC51" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="BD51" s="12">
         <v>670</v>
@@ -16508,7 +16546,7 @@
       <c r="BJ51" s="12"/>
       <c r="BK51" s="12"/>
       <c r="BM51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="BN51">
         <v>8</v>
@@ -16579,11 +16617,11 @@
       </c>
       <c r="H52" s="21">
         <f>IF(AND($F52&lt;=J$2,H49&gt;0),H49*$F52,0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I52" s="19">
         <f>IF(H49&lt;$C$23,0,H52)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J52" s="20">
         <v>0</v>
@@ -16747,7 +16785,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC52" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="BD52" s="12">
         <v>690</v>
@@ -16770,7 +16808,7 @@
       <c r="BJ52" s="12"/>
       <c r="BK52" s="12"/>
       <c r="BM52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="BN52">
         <v>17</v>
@@ -16841,11 +16879,11 @@
       </c>
       <c r="H53" s="21">
         <f>IF(AND($F53&lt;=J$2,H49&gt;0),H49*$F53,0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I53" s="19">
         <f>IF(H49&lt;$C$23,0,H53)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J53" s="20">
         <v>0</v>
@@ -17009,7 +17047,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="BD53" s="12">
         <v>700</v>
@@ -17032,7 +17070,7 @@
       <c r="BJ53" s="12"/>
       <c r="BK53" s="12"/>
       <c r="BM53" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BN53">
         <v>25</v>
@@ -17095,7 +17133,7 @@
     </row>
     <row r="54" spans="2:116" ht="15.75" customHeight="1">
       <c r="B54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C54" s="42">
         <f>$C$15*1.3*1000</f>
@@ -17110,11 +17148,11 @@
       </c>
       <c r="H54" s="21">
         <f>IF(AND($F54&lt;=J$2,H49&gt;0),H49-1,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" s="19">
         <f>IF(H54&lt;$C$23,0,H54)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" s="20">
         <v>0</v>
@@ -17278,7 +17316,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC54" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BD54" s="12">
         <v>700</v>
@@ -17301,7 +17339,7 @@
       <c r="BJ54" s="12"/>
       <c r="BK54" s="12"/>
       <c r="BM54" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="BN54">
         <v>4.2</v>
@@ -17364,7 +17402,7 @@
     </row>
     <row r="55" spans="2:116" ht="15.75" customHeight="1">
       <c r="B55" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C55" t="e">
         <f>$C$21</f>
@@ -17379,11 +17417,11 @@
       </c>
       <c r="H55" s="21">
         <f>IF(AND($F55&lt;=J$2,H54&gt;0),H54*$F55,0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I55" s="19">
         <f>IF(H54&lt;$C$23,0,H55)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J55" s="20">
         <v>0</v>
@@ -17547,7 +17585,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="BD55" s="12">
         <v>600</v>
@@ -17570,7 +17608,7 @@
       <c r="BJ55" s="12"/>
       <c r="BK55" s="12"/>
       <c r="BM55" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BN55">
         <v>6</v>
@@ -17604,8 +17642,12 @@
       <c r="CW55">
         <v>1</v>
       </c>
-      <c r="DK55" s="15"/>
-      <c r="DL55" s="15"/>
+      <c r="DK55" s="15">
+        <v>182198</v>
+      </c>
+      <c r="DL55" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="56" spans="2:116" ht="15.75" customHeight="1">
       <c r="B56" s="21" t="e">
@@ -17621,11 +17663,11 @@
       </c>
       <c r="H56" s="21">
         <f>IF(AND($F56&lt;=J$2,H54&gt;0),H54*$F56,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I56" s="19">
         <f>IF(H54&lt;$C$23,0,H56)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J56" s="20">
         <v>0</v>
@@ -17789,7 +17831,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC56" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="BD56">
         <v>610</v>
@@ -17810,7 +17852,7 @@
         <v>15.88</v>
       </c>
       <c r="BM56" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="BN56">
         <v>7.5</v>
@@ -17857,11 +17899,11 @@
       </c>
       <c r="H57" s="21">
         <f>IF(AND($F57&lt;=J$2,H54&gt;0),H54*$F57,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I57" s="19">
         <f>IF(H54&lt;$C$23,0,H57)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J57" s="20">
         <v>0</v>
@@ -18025,7 +18067,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC57" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="BD57">
         <v>615</v>
@@ -18046,7 +18088,7 @@
         <v>15.92</v>
       </c>
       <c r="BM57" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="BN57">
         <v>100</v>
@@ -18157,12 +18199,12 @@
         <v>107282</v>
       </c>
       <c r="DL57" s="31" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="58" spans="2:116" ht="15.75" customHeight="1">
       <c r="B58" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C58" s="43">
         <f>(80/100)*VLOOKUP($B$2,BC3:BI309,6,0)</f>
@@ -18177,11 +18219,11 @@
       </c>
       <c r="H58" s="21">
         <f>IF(AND($F58&lt;=J$2,H54&gt;0),H54*$F58,0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I58" s="19">
         <f>IF(H54&lt;$C$23,0,H58)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J58" s="20">
         <v>0</v>
@@ -18345,7 +18387,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC58" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BD58" s="12">
         <v>700</v>
@@ -18368,7 +18410,7 @@
       <c r="BJ58" s="12"/>
       <c r="BK58" s="12"/>
       <c r="BM58" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BN58">
         <v>100</v>
@@ -18480,11 +18522,11 @@
     </row>
     <row r="59" spans="2:116" ht="15.75" customHeight="1">
       <c r="B59" s="44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C59" s="21" t="e">
         <f t="array" ref="C59">MIN(IF($C$120:$C$134=0," ",$C$120:$C$134))</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F59" s="26">
         <v>1</v>
@@ -18495,7 +18537,7 @@
       </c>
       <c r="H59" s="21">
         <f>IF(AND($F59&lt;=J$2,H54&gt;0),H54-1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="19">
         <f>IF(H59&lt;$C$23,0,H59)</f>
@@ -18663,7 +18705,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC59" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BD59">
         <v>560</v>
@@ -18686,7 +18728,7 @@
       <c r="BJ59" s="12"/>
       <c r="BK59" s="12"/>
       <c r="BM59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="BN59">
         <v>10</v>
@@ -18734,7 +18776,7 @@
         <v>107277</v>
       </c>
       <c r="DL59" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="60" spans="2:116" ht="15.75" customHeight="1">
@@ -18747,7 +18789,7 @@
       </c>
       <c r="H60" s="21">
         <f>IF(AND($F60&lt;=J$2,H59&gt;0),H59*$F60,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I60" s="19">
         <f>IF(H59&lt;$C$23,0,H60)</f>
@@ -18915,7 +18957,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC60" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BD60">
         <v>310</v>
@@ -18934,7 +18976,7 @@
       <c r="BJ60" s="12"/>
       <c r="BK60" s="12"/>
       <c r="BM60" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BN60">
         <v>10</v>
@@ -18984,7 +19026,7 @@
     <row r="61" spans="2:116" ht="15.75" customHeight="1">
       <c r="B61" s="43" t="e">
         <f>IF(OR(AND(B14="Livoltek Off Grid GF1-5K48S1",C3=665),AND(C59&lt;C58,$C$7&gt;18)),"Ruim","Bom")</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F61" s="26">
         <v>3</v>
@@ -18995,7 +19037,7 @@
       </c>
       <c r="H61" s="21">
         <f>IF(AND($F61&lt;=J$2,H59&gt;0),H59*$F61,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I61" s="19">
         <f>IF(H59&lt;$C$23,0,H61)</f>
@@ -19163,7 +19205,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC61" s="40" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="BD61">
         <v>585</v>
@@ -19186,7 +19228,7 @@
       <c r="BJ61" s="12"/>
       <c r="BK61" s="12"/>
       <c r="BM61" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="BN61">
         <v>12</v>
@@ -19251,7 +19293,7 @@
       </c>
       <c r="H62" s="21">
         <f>IF(AND($F62&lt;=J$2,H59&gt;0),H59*$F62,0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I62" s="19">
         <f>IF(H59&lt;$C$23,0,H62)</f>
@@ -19419,7 +19461,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC62" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="BD62">
         <v>460</v>
@@ -19442,7 +19484,7 @@
       <c r="BJ62" s="12"/>
       <c r="BK62" s="12"/>
       <c r="BM62" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="BN62">
         <v>15</v>
@@ -19490,7 +19532,7 @@
       </c>
       <c r="H63" s="21">
         <f>IF(AND($F63&lt;=J$2,H59&gt;0),H59*$F63,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I63" s="19">
         <f>IF(H59&lt;$C$23,0,H63)</f>
@@ -19658,7 +19700,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC63" s="50" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="BD63">
         <v>550</v>
@@ -19681,7 +19723,7 @@
       <c r="BJ63" s="12"/>
       <c r="BK63" s="12"/>
       <c r="BM63" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BN63">
         <v>15</v>
@@ -19721,7 +19763,7 @@
     </row>
     <row r="64" spans="2:116" ht="15.75" customHeight="1">
       <c r="BC64" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BD64">
         <v>560</v>
@@ -19744,7 +19786,7 @@
       <c r="BJ64" s="12"/>
       <c r="BK64" s="12"/>
       <c r="BM64" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="BN64">
         <v>20</v>
@@ -19800,22 +19842,22 @@
         <v>185834</v>
       </c>
       <c r="DL64" s="25" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="65" spans="2:116" ht="15.75" customHeight="1">
       <c r="B65" s="51" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C65" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,6,0)</f>
         <v>40</v>
       </c>
       <c r="D65" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G65" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J65">
         <f>SUM(J4:J63)</f>
@@ -19924,7 +19966,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC65" s="40" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BD65">
         <v>560</v>
@@ -19947,7 +19989,7 @@
       <c r="BJ65" s="12"/>
       <c r="BK65" s="12"/>
       <c r="BM65" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="BN65">
         <v>20</v>
@@ -19987,21 +20029,21 @@
     </row>
     <row r="66" spans="2:116" ht="15.75" customHeight="1">
       <c r="B66" s="51" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C66" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,7,0)</f>
         <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G66" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J66">
         <f t="shared" ref="J66:AZ66" si="32">IF(J2&gt;=1,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66">
         <f t="shared" si="32"/>
@@ -20120,7 +20162,7 @@
         <v>50</v>
       </c>
       <c r="BC66" s="40" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BD66">
         <v>580</v>
@@ -20143,7 +20185,7 @@
       <c r="BJ66" s="12"/>
       <c r="BK66" s="12"/>
       <c r="BM66" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="BN66">
         <v>20</v>
@@ -20183,19 +20225,19 @@
     </row>
     <row r="67" spans="2:116" ht="15.75" customHeight="1">
       <c r="B67" s="51" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C67" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,8,0)</f>
         <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q67" s="53"/>
       <c r="R67" s="53"/>
       <c r="BC67" s="40" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="BD67">
         <v>585</v>
@@ -20218,7 +20260,7 @@
       <c r="BJ67" s="12"/>
       <c r="BK67" s="12"/>
       <c r="BM67" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="BN67">
         <v>250</v>
@@ -20293,24 +20335,24 @@
         <v>107284</v>
       </c>
       <c r="DL67" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="68" spans="2:116" ht="15.75" customHeight="1">
       <c r="B68" s="51" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C68" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,9,0)</f>
         <v>0</v>
       </c>
       <c r="D68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q68" s="53"/>
       <c r="R68" s="53"/>
       <c r="BC68" s="40" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BD68">
         <v>590</v>
@@ -20333,7 +20375,7 @@
       <c r="BJ68" s="12"/>
       <c r="BK68" s="12"/>
       <c r="BM68" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BN68">
         <v>250</v>
@@ -20409,19 +20451,19 @@
     </row>
     <row r="69" spans="2:116" ht="15.75" customHeight="1">
       <c r="B69" s="51" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C69" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,10,0)</f>
         <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q69" s="53"/>
       <c r="R69" s="53"/>
       <c r="BC69" s="40" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BD69">
         <v>590</v>
@@ -20444,7 +20486,7 @@
       <c r="BJ69" s="12"/>
       <c r="BK69" s="12"/>
       <c r="BM69" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="BN69">
         <v>25</v>
@@ -20484,19 +20526,19 @@
     </row>
     <row r="70" spans="2:116" ht="15.75" customHeight="1">
       <c r="B70" s="51" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C70" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,11,0)</f>
         <v>0</v>
       </c>
       <c r="D70" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q70" s="53"/>
       <c r="R70" s="53"/>
       <c r="BC70" s="40" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="BD70">
         <v>595</v>
@@ -20519,7 +20561,7 @@
       <c r="BJ70" s="12"/>
       <c r="BK70" s="12"/>
       <c r="BM70" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="BN70">
         <v>25</v>
@@ -20559,19 +20601,19 @@
     </row>
     <row r="71" spans="2:116" ht="15.75" customHeight="1">
       <c r="B71" s="51" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C71" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,12,0)</f>
         <v>0</v>
       </c>
       <c r="D71" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q71" s="53"/>
       <c r="R71" s="53"/>
       <c r="BC71" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="BD71" s="12">
         <v>610</v>
@@ -20594,7 +20636,7 @@
       <c r="BJ71" s="12"/>
       <c r="BK71" s="12"/>
       <c r="BM71" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="BN71">
         <v>30</v>
@@ -20661,19 +20703,19 @@
     </row>
     <row r="72" spans="2:116" ht="15.75" customHeight="1">
       <c r="B72" s="51" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C72" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,13,0)</f>
         <v>0</v>
       </c>
       <c r="D72" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q72" s="53"/>
       <c r="R72" s="53"/>
       <c r="BC72" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="BD72" s="12">
         <v>610</v>
@@ -20696,7 +20738,7 @@
       <c r="BJ72" s="12"/>
       <c r="BK72" s="12"/>
       <c r="BM72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="BN72">
         <v>3</v>
@@ -20739,24 +20781,24 @@
         <v>107271</v>
       </c>
       <c r="DL72" s="25" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="73" spans="2:116" ht="15.75" customHeight="1">
       <c r="B73" s="51" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C73" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,14,0)</f>
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q73" s="53"/>
       <c r="R73" s="53"/>
       <c r="BC73" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="BD73">
         <v>650</v>
@@ -20779,7 +20821,7 @@
       <c r="BJ73" s="12"/>
       <c r="BK73" s="12"/>
       <c r="BM73" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="BN73">
         <v>3</v>
@@ -20823,19 +20865,19 @@
     </row>
     <row r="74" spans="2:116" ht="15.75" customHeight="1">
       <c r="B74" s="51" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C74" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,15,0)</f>
         <v>0</v>
       </c>
       <c r="D74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q74" s="53"/>
       <c r="R74" s="53"/>
       <c r="BC74" s="40" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="BD74">
         <v>665</v>
@@ -20858,7 +20900,7 @@
       <c r="BJ74" s="12"/>
       <c r="BK74" s="12"/>
       <c r="BM74" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BN74">
         <v>4</v>
@@ -20909,24 +20951,24 @@
         <v>121772</v>
       </c>
       <c r="DL74" s="25" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="75" spans="2:116" ht="15.75" customHeight="1">
       <c r="B75" s="51" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C75" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,16,0)</f>
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q75" s="53"/>
       <c r="R75" s="53"/>
       <c r="BC75" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="BD75" s="12">
         <v>670</v>
@@ -20949,7 +20991,7 @@
       <c r="BJ75" s="12"/>
       <c r="BK75" s="12"/>
       <c r="BM75" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BN75">
         <v>4</v>
@@ -21001,19 +21043,19 @@
     </row>
     <row r="76" spans="2:116" ht="15.75" customHeight="1">
       <c r="B76" s="51" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C76" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,17,0)</f>
         <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q76" s="53"/>
       <c r="R76" s="53"/>
       <c r="BC76" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="BD76" s="12">
         <v>700</v>
@@ -21036,7 +21078,7 @@
       <c r="BJ76" s="12"/>
       <c r="BK76" s="12"/>
       <c r="BM76" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="BN76">
         <v>50</v>
@@ -21103,19 +21145,19 @@
     </row>
     <row r="77" spans="2:116" ht="15.75" customHeight="1">
       <c r="B77" s="51" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C77" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,18,0)</f>
         <v>0</v>
       </c>
       <c r="D77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q77" s="53"/>
       <c r="R77" s="53"/>
       <c r="BC77" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="BD77">
         <v>570</v>
@@ -21136,7 +21178,7 @@
         <v>15.12</v>
       </c>
       <c r="BM77" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="BN77">
         <v>5</v>
@@ -21179,24 +21221,24 @@
         <v>107272</v>
       </c>
       <c r="DL77" s="31" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="78" spans="2:116" ht="15.75" customHeight="1">
       <c r="B78" s="51" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C78" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,19,0)</f>
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q78" s="53"/>
       <c r="R78" s="53"/>
       <c r="BC78" s="40" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="BD78">
         <v>585</v>
@@ -21219,7 +21261,7 @@
       <c r="BJ78" s="12"/>
       <c r="BK78" s="12"/>
       <c r="BM78" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BN78">
         <v>5</v>
@@ -21263,19 +21305,19 @@
     </row>
     <row r="79" spans="2:116" ht="15.75" customHeight="1">
       <c r="B79" s="51" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C79" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,20,0)</f>
         <v>0</v>
       </c>
       <c r="D79" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q79" s="53"/>
       <c r="R79" s="53"/>
       <c r="BC79" s="40" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BD79" s="12">
         <v>620</v>
@@ -21298,7 +21340,7 @@
       <c r="BJ79" s="12"/>
       <c r="BK79" s="12"/>
       <c r="BM79" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="BN79">
         <v>60</v>
@@ -21375,7 +21417,7 @@
       <c r="Q80" s="53"/>
       <c r="R80" s="53"/>
       <c r="BC80" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="BD80" s="12">
         <v>620</v>
@@ -21398,7 +21440,7 @@
       <c r="BJ80" s="12"/>
       <c r="BK80" s="12"/>
       <c r="BM80" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="BN80">
         <v>6</v>
@@ -21441,14 +21483,14 @@
         <v>107273</v>
       </c>
       <c r="DL80" s="25" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="81" spans="2:116" ht="15.75" customHeight="1">
       <c r="Q81" s="53"/>
       <c r="R81" s="53"/>
       <c r="BC81" s="40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BD81" s="12">
         <v>620</v>
@@ -21471,7 +21513,7 @@
       <c r="BJ81" s="12"/>
       <c r="BK81" s="12"/>
       <c r="BM81" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BN81">
         <v>6</v>
@@ -21517,7 +21559,7 @@
       <c r="Q82" s="53"/>
       <c r="R82" s="53"/>
       <c r="BC82" s="40" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="BD82">
         <v>690</v>
@@ -21540,7 +21582,7 @@
       <c r="BJ82" s="12"/>
       <c r="BK82" s="12"/>
       <c r="BM82" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="BN82">
         <v>7.5</v>
@@ -21589,19 +21631,19 @@
     </row>
     <row r="83" spans="2:116" ht="15.75" customHeight="1">
       <c r="B83" s="51" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C83" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,21,0)</f>
         <v>32</v>
       </c>
       <c r="D83" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q83" s="53"/>
       <c r="R83" s="53"/>
       <c r="BC83" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="BD83" s="12">
         <v>445</v>
@@ -21624,7 +21666,7 @@
       <c r="BJ83" s="12"/>
       <c r="BK83" s="12"/>
       <c r="BM83" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BN83">
         <v>75</v>
@@ -21708,19 +21750,19 @@
     </row>
     <row r="84" spans="2:116" ht="15.75" customHeight="1">
       <c r="B84" s="51" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C84" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,22,0)</f>
         <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q84" s="53"/>
       <c r="R84" s="53"/>
       <c r="BC84" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="BD84" s="12">
         <v>450</v>
@@ -21743,7 +21785,7 @@
       <c r="BJ84" s="12"/>
       <c r="BK84" s="12"/>
       <c r="BM84" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="BN84">
         <v>75</v>
@@ -21854,24 +21896,24 @@
         <v>107281</v>
       </c>
       <c r="DL84" s="25" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="85" spans="2:116" ht="15.75" customHeight="1">
       <c r="B85" s="51" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C85" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,23,0)</f>
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q85" s="53"/>
       <c r="R85" s="53"/>
       <c r="BC85" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="BD85" s="12">
         <v>455</v>
@@ -21894,7 +21936,7 @@
       <c r="BJ85" s="12"/>
       <c r="BK85" s="12"/>
       <c r="BM85" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="BN85">
         <v>75</v>
@@ -22006,19 +22048,19 @@
     </row>
     <row r="86" spans="2:116" ht="15.75" customHeight="1">
       <c r="B86" s="51" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C86" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,24,0)</f>
         <v>0</v>
       </c>
       <c r="D86" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q86" s="53"/>
       <c r="R86" s="53"/>
       <c r="BC86" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="BD86">
         <v>440</v>
@@ -22041,7 +22083,7 @@
       <c r="BJ86" s="12"/>
       <c r="BK86" s="12"/>
       <c r="BM86" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="BN86">
         <v>8</v>
@@ -22104,19 +22146,19 @@
     </row>
     <row r="87" spans="2:116" ht="15.75" customHeight="1">
       <c r="B87" s="51" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C87" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,25,0)</f>
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q87" s="53"/>
       <c r="R87" s="53"/>
       <c r="BC87" s="40" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="BD87">
         <v>555</v>
@@ -22139,7 +22181,7 @@
       <c r="BJ87" s="12"/>
       <c r="BK87" s="12"/>
       <c r="BM87" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="BN87">
         <v>8</v>
@@ -22202,19 +22244,19 @@
     </row>
     <row r="88" spans="2:116" ht="15.75" customHeight="1">
       <c r="B88" s="51" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C88" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,26,0)</f>
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q88" s="53"/>
       <c r="R88" s="53"/>
       <c r="BC88" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="BD88" s="12">
         <v>610</v>
@@ -22237,7 +22279,7 @@
       <c r="BJ88" s="12"/>
       <c r="BK88" s="12"/>
       <c r="BM88" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="BN88">
         <v>3.6</v>
@@ -22270,19 +22312,19 @@
     </row>
     <row r="89" spans="2:116" ht="15.75" customHeight="1">
       <c r="B89" s="51" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C89" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,27,0)</f>
         <v>0</v>
       </c>
       <c r="D89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q89" s="53"/>
       <c r="R89" s="53"/>
       <c r="BC89" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="BD89" s="12">
         <v>610</v>
@@ -22305,7 +22347,7 @@
       <c r="BJ89" s="12"/>
       <c r="BK89" s="12"/>
       <c r="BM89" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="BN89">
         <v>5.5</v>
@@ -22344,19 +22386,19 @@
     </row>
     <row r="90" spans="2:116" ht="15.75" customHeight="1">
       <c r="B90" s="51" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C90" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,28,0)</f>
         <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q90" s="53"/>
       <c r="R90" s="53"/>
       <c r="BC90" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="BD90">
         <v>460</v>
@@ -22379,7 +22421,7 @@
       <c r="BJ90" s="12"/>
       <c r="BK90" s="12"/>
       <c r="BM90" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="BN90">
         <v>6.6</v>
@@ -22418,19 +22460,19 @@
     </row>
     <row r="91" spans="2:116" ht="15.75" customHeight="1">
       <c r="B91" s="51" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C91" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,29,0)</f>
         <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q91" s="53"/>
       <c r="R91" s="53"/>
       <c r="BC91" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="BD91">
         <v>605</v>
@@ -22450,8 +22492,14 @@
       <c r="BI91">
         <v>16.16</v>
       </c>
+      <c r="BJ91">
+        <v>228604</v>
+      </c>
+      <c r="BK91" t="s">
+        <v>516</v>
+      </c>
       <c r="BM91" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="BN91">
         <v>7.3</v>
@@ -22490,19 +22538,19 @@
     </row>
     <row r="92" spans="2:116" ht="15.75" customHeight="1">
       <c r="B92" s="51" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C92" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,30,0)</f>
         <v>0</v>
       </c>
       <c r="D92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q92" s="53"/>
       <c r="R92" s="53"/>
       <c r="BC92" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="BD92" s="12">
         <v>700</v>
@@ -22525,7 +22573,7 @@
       <c r="BJ92" s="12"/>
       <c r="BK92" s="12"/>
       <c r="BM92" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="BN92">
         <v>5</v>
@@ -22576,19 +22624,19 @@
     </row>
     <row r="93" spans="2:116" ht="15.75" customHeight="1">
       <c r="B93" s="51" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C93" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,31,0)</f>
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q93" s="53"/>
       <c r="R93" s="53"/>
       <c r="BC93" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BD93">
         <v>560</v>
@@ -22611,7 +22659,7 @@
       <c r="BJ93" s="12"/>
       <c r="BK93" s="12"/>
       <c r="BM93" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BN93">
         <v>7.5</v>
@@ -22650,19 +22698,19 @@
     </row>
     <row r="94" spans="2:116" ht="15.75" customHeight="1">
       <c r="B94" s="51" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C94" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,32,0)</f>
         <v>0</v>
       </c>
       <c r="D94" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q94" s="53"/>
       <c r="R94" s="53"/>
       <c r="BC94" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BD94">
         <v>545</v>
@@ -22685,7 +22733,7 @@
       <c r="BJ94" s="12"/>
       <c r="BK94" s="12"/>
       <c r="BM94" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BN94">
         <v>2.2000000000000002</v>
@@ -22742,19 +22790,19 @@
     </row>
     <row r="95" spans="2:116" ht="15.75" customHeight="1">
       <c r="B95" s="51" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C95" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,33,0)</f>
         <v>0</v>
       </c>
       <c r="D95" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q95" s="53"/>
       <c r="R95" s="53"/>
       <c r="BC95" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BD95" s="12">
         <v>700</v>
@@ -22777,7 +22825,7 @@
       <c r="BJ95" s="12"/>
       <c r="BK95" s="12"/>
       <c r="BM95" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BN95">
         <v>10</v>
@@ -22840,19 +22888,19 @@
     </row>
     <row r="96" spans="2:116" ht="15.75" customHeight="1">
       <c r="B96" s="51" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C96" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,34,0)</f>
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q96" s="53"/>
       <c r="R96" s="53"/>
       <c r="BC96" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="BD96" s="12">
         <v>570</v>
@@ -22875,7 +22923,7 @@
       <c r="BJ96" s="12"/>
       <c r="BK96" s="12"/>
       <c r="BM96" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="BN96">
         <v>10</v>
@@ -22923,19 +22971,19 @@
     </row>
     <row r="97" spans="1:116" ht="15.75" customHeight="1">
       <c r="B97" s="51" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C97" s="51">
         <f>VLOOKUP($B$14,$BM$3:$DH$315,35,0)</f>
         <v>0</v>
       </c>
       <c r="D97" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q97" s="53"/>
       <c r="R97" s="53"/>
       <c r="BC97" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="BD97">
         <v>570</v>
@@ -22956,7 +23004,7 @@
         <v>14.25</v>
       </c>
       <c r="BM97" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="BN97">
         <v>3.3</v>
@@ -23013,7 +23061,7 @@
     </row>
     <row r="98" spans="1:116" ht="15.75" customHeight="1">
       <c r="BC98" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="BD98" s="12">
         <v>585</v>
@@ -23036,7 +23084,7 @@
       <c r="BJ98" s="12"/>
       <c r="BK98" s="12"/>
       <c r="BM98" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="BN98">
         <v>3</v>
@@ -23092,7 +23140,7 @@
     </row>
     <row r="99" spans="1:116" ht="15.75" customHeight="1">
       <c r="BC99" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BD99" s="12">
         <v>700</v>
@@ -23115,7 +23163,7 @@
       <c r="BJ99" s="12"/>
       <c r="BK99" s="12"/>
       <c r="BM99" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="BN99">
         <v>3</v>
@@ -23171,7 +23219,7 @@
     </row>
     <row r="100" spans="1:116" ht="15.75" customHeight="1">
       <c r="BC100" s="40" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BD100" s="12">
         <v>550</v>
@@ -23194,7 +23242,7 @@
       <c r="BJ100" s="60"/>
       <c r="BK100" s="60"/>
       <c r="BM100" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="BN100">
         <v>5</v>
@@ -23257,7 +23305,7 @@
     </row>
     <row r="101" spans="1:116" ht="15.75" customHeight="1">
       <c r="BC101" s="40" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="BD101" s="12">
         <v>550</v>
@@ -23280,7 +23328,7 @@
       <c r="BJ101" s="60"/>
       <c r="BK101" s="60"/>
       <c r="BM101" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BN101">
         <v>5</v>
@@ -23331,18 +23379,18 @@
     </row>
     <row r="102" spans="1:116" ht="15.75" customHeight="1">
       <c r="A102" s="53" t="s">
+        <v>348</v>
+      </c>
+      <c r="B102" s="53"/>
+      <c r="C102" s="53" t="e">
+        <f>IF(J2&gt;0,$C65/J2,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D102" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC102" t="s">
         <v>349</v>
-      </c>
-      <c r="B102" s="53"/>
-      <c r="C102" s="53">
-        <f>IF(J2&gt;0,$C65/J2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D102" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC102" t="s">
-        <v>350</v>
       </c>
       <c r="BD102">
         <v>560</v>
@@ -23365,7 +23413,7 @@
       <c r="BJ102" s="12"/>
       <c r="BK102" s="12"/>
       <c r="BM102" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="BN102">
         <v>5</v>
@@ -23428,7 +23476,7 @@
     </row>
     <row r="103" spans="1:116" ht="15.75" customHeight="1">
       <c r="A103" s="53" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B103" s="53"/>
       <c r="C103" s="53" t="e">
@@ -23436,10 +23484,10 @@
         <v>#REF!</v>
       </c>
       <c r="D103" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BC103" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="BD103">
         <v>505</v>
@@ -23462,7 +23510,7 @@
       <c r="BJ103" s="12"/>
       <c r="BK103" s="12"/>
       <c r="BM103" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="BN103">
         <v>6</v>
@@ -23525,7 +23573,7 @@
     </row>
     <row r="104" spans="1:116" ht="15.75" customHeight="1">
       <c r="A104" s="53" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B104" s="53"/>
       <c r="C104" s="53" t="e">
@@ -23533,10 +23581,10 @@
         <v>#REF!</v>
       </c>
       <c r="D104" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BC104" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="BD104">
         <v>450</v>
@@ -23559,7 +23607,7 @@
       <c r="BJ104" s="12"/>
       <c r="BK104" s="12"/>
       <c r="BM104" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BN104">
         <v>6</v>
@@ -23623,7 +23671,7 @@
     </row>
     <row r="105" spans="1:116" ht="15.75" customHeight="1">
       <c r="A105" s="53" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B105" s="53"/>
       <c r="C105" s="53" t="e">
@@ -23631,10 +23679,10 @@
         <v>#REF!</v>
       </c>
       <c r="D105" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BC105" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="BD105">
         <v>550</v>
@@ -23657,7 +23705,7 @@
       <c r="BJ105" s="12"/>
       <c r="BK105" s="12"/>
       <c r="BM105" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BN105">
         <v>6</v>
@@ -23696,7 +23744,7 @@
     </row>
     <row r="106" spans="1:116" ht="15.75" customHeight="1">
       <c r="A106" s="53" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B106" s="53"/>
       <c r="C106" s="53" t="e">
@@ -23704,10 +23752,10 @@
         <v>#REF!</v>
       </c>
       <c r="D106" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BC106" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="BD106">
         <v>440</v>
@@ -23730,7 +23778,7 @@
       <c r="BJ106" s="12"/>
       <c r="BK106" s="12"/>
       <c r="BM106" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="BN106">
         <v>6</v>
@@ -23793,7 +23841,7 @@
     </row>
     <row r="107" spans="1:116" ht="15.75" customHeight="1">
       <c r="A107" s="53" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B107" s="53"/>
       <c r="C107" s="53" t="e">
@@ -23801,10 +23849,10 @@
         <v>#REF!</v>
       </c>
       <c r="D107" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BC107" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="BD107">
         <v>505</v>
@@ -23827,7 +23875,7 @@
       <c r="BJ107" s="12"/>
       <c r="BK107" s="12"/>
       <c r="BM107" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="BN107">
         <v>7</v>
@@ -23886,7 +23934,7 @@
     </row>
     <row r="108" spans="1:116" ht="15.75" customHeight="1">
       <c r="A108" s="53" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B108" s="53"/>
       <c r="C108" s="53" t="e">
@@ -23894,10 +23942,10 @@
         <v>#REF!</v>
       </c>
       <c r="D108" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BC108" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="BD108">
         <v>545</v>
@@ -23920,7 +23968,7 @@
       <c r="BJ108" s="60"/>
       <c r="BK108" s="60"/>
       <c r="BM108" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="BN108">
         <v>8</v>
@@ -23983,7 +24031,7 @@
     </row>
     <row r="109" spans="1:116" ht="15.75" customHeight="1">
       <c r="A109" s="53" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B109" s="53"/>
       <c r="C109" s="53" t="e">
@@ -23991,10 +24039,10 @@
         <v>#REF!</v>
       </c>
       <c r="D109" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BC109" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="BD109" s="12">
         <v>640</v>
@@ -24017,7 +24065,7 @@
       <c r="BJ109" s="12"/>
       <c r="BK109" s="12"/>
       <c r="BM109" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="BN109">
         <v>8</v>
@@ -24088,7 +24136,7 @@
     </row>
     <row r="110" spans="1:116" ht="15.75" customHeight="1">
       <c r="A110" s="53" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B110" s="53"/>
       <c r="C110" s="53" t="e">
@@ -24096,10 +24144,10 @@
         <v>#REF!</v>
       </c>
       <c r="D110" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BC110" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="BD110">
         <v>620</v>
@@ -24119,8 +24167,14 @@
       <c r="BI110">
         <v>16.21</v>
       </c>
+      <c r="BJ110">
+        <v>213692</v>
+      </c>
+      <c r="BK110" t="s">
+        <v>516</v>
+      </c>
       <c r="BM110" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="BN110">
         <v>8</v>
@@ -24179,7 +24233,7 @@
     </row>
     <row r="111" spans="1:116" ht="15.75" customHeight="1">
       <c r="A111" s="53" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B111" s="53"/>
       <c r="C111" s="53" t="e">
@@ -24187,7 +24241,7 @@
         <v>#REF!</v>
       </c>
       <c r="D111" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BC111" t="s">
         <v>0</v>
@@ -24210,10 +24264,14 @@
       <c r="BI111" s="12">
         <v>12.64</v>
       </c>
-      <c r="BJ111" s="12"/>
-      <c r="BK111" s="12"/>
+      <c r="BJ111" s="12">
+        <v>206291</v>
+      </c>
+      <c r="BK111" s="12" t="s">
+        <v>516</v>
+      </c>
       <c r="BM111" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="BN111">
         <v>25</v>
@@ -24278,7 +24336,7 @@
     </row>
     <row r="112" spans="1:116" ht="15.75" customHeight="1">
       <c r="A112" s="53" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B112" s="53"/>
       <c r="C112" s="53" t="e">
@@ -24286,10 +24344,10 @@
         <v>#REF!</v>
       </c>
       <c r="D112" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM112" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="BN112">
         <v>30</v>
@@ -24352,7 +24410,7 @@
     </row>
     <row r="113" spans="1:116" ht="15.75" customHeight="1">
       <c r="A113" s="53" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B113" s="53"/>
       <c r="C113" s="53" t="e">
@@ -24360,10 +24418,10 @@
         <v>#REF!</v>
       </c>
       <c r="D113" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM113" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="BN113">
         <v>3</v>
@@ -24418,12 +24476,12 @@
         <v>70396</v>
       </c>
       <c r="DL113" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="114" spans="1:116" ht="15.75" customHeight="1">
       <c r="A114" s="53" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B114" s="53"/>
       <c r="C114" s="53" t="e">
@@ -24431,10 +24489,10 @@
         <v>#REF!</v>
       </c>
       <c r="D114" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM114" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BN114">
         <v>5</v>
@@ -24489,12 +24547,12 @@
         <v>70397</v>
       </c>
       <c r="DL114" s="41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="115" spans="1:116" ht="15.75" customHeight="1">
       <c r="A115" s="53" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B115" s="53"/>
       <c r="C115" s="53" t="e">
@@ -24502,10 +24560,10 @@
         <v>#REF!</v>
       </c>
       <c r="D115" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM115" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="BN115">
         <v>30</v>
@@ -24561,7 +24619,7 @@
     </row>
     <row r="116" spans="1:116" ht="15.75" customHeight="1">
       <c r="A116" s="53" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B116" s="53"/>
       <c r="C116" s="53" t="e">
@@ -24569,10 +24627,10 @@
         <v>#REF!</v>
       </c>
       <c r="D116" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM116" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BN116">
         <v>30</v>
@@ -24631,7 +24689,7 @@
       <c r="B117" s="53"/>
       <c r="C117" s="53"/>
       <c r="BM117" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BN117">
         <v>50</v>
@@ -24691,7 +24749,7 @@
       <c r="B118" s="53"/>
       <c r="C118" s="53"/>
       <c r="BM118" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="BN118">
         <v>6</v>
@@ -24733,7 +24791,7 @@
       <c r="B119" s="53"/>
       <c r="C119" s="53"/>
       <c r="BM119" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="BN119">
         <v>15</v>
@@ -24784,18 +24842,18 @@
     </row>
     <row r="120" spans="1:116" ht="15.75" customHeight="1">
       <c r="A120" s="53" t="s">
+        <v>390</v>
+      </c>
+      <c r="B120" s="53"/>
+      <c r="C120" s="53" t="e">
+        <f>IF(J2&gt;0,$C83/J2,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D120" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM120" t="s">
         <v>391</v>
-      </c>
-      <c r="B120" s="53"/>
-      <c r="C120" s="53">
-        <f>IF(J2&gt;0,$C83/J2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D120" t="s">
-        <v>93</v>
-      </c>
-      <c r="BM120" t="s">
-        <v>392</v>
       </c>
       <c r="BN120">
         <v>20</v>
@@ -24846,7 +24904,7 @@
     </row>
     <row r="121" spans="1:116" ht="15.75" customHeight="1">
       <c r="A121" s="53" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B121" s="53"/>
       <c r="C121" s="53" t="e">
@@ -24854,10 +24912,10 @@
         <v>#REF!</v>
       </c>
       <c r="D121" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM121" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="BN121">
         <v>20</v>
@@ -24914,7 +24972,7 @@
     </row>
     <row r="122" spans="1:116" ht="15.75" customHeight="1">
       <c r="A122" s="53" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B122" s="53"/>
       <c r="C122" s="53" t="e">
@@ -24922,10 +24980,10 @@
         <v>#REF!</v>
       </c>
       <c r="D122" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM122" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="BN122">
         <v>25</v>
@@ -24964,7 +25022,7 @@
     </row>
     <row r="123" spans="1:116" ht="15.75" customHeight="1">
       <c r="A123" s="53" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B123" s="53"/>
       <c r="C123" s="53" t="e">
@@ -24972,10 +25030,10 @@
         <v>#REF!</v>
       </c>
       <c r="D123" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM123" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="BN123">
         <v>25</v>
@@ -25042,7 +25100,7 @@
     </row>
     <row r="124" spans="1:116" ht="15.75" customHeight="1">
       <c r="A124" s="53" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B124" s="53"/>
       <c r="C124" s="53" t="e">
@@ -25050,10 +25108,10 @@
         <v>#REF!</v>
       </c>
       <c r="D124" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM124" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="BN124">
         <v>30</v>
@@ -25112,7 +25170,7 @@
     </row>
     <row r="125" spans="1:116" ht="15.75" customHeight="1">
       <c r="A125" s="53" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B125" s="53"/>
       <c r="C125" s="53" t="e">
@@ -25120,10 +25178,10 @@
         <v>#REF!</v>
       </c>
       <c r="D125" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM125" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="BN125">
         <v>75</v>
@@ -25216,7 +25274,7 @@
     </row>
     <row r="126" spans="1:116" ht="15.75" customHeight="1">
       <c r="A126" s="53" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B126" s="53"/>
       <c r="C126" s="53" t="e">
@@ -25224,10 +25282,10 @@
         <v>#REF!</v>
       </c>
       <c r="D126" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM126" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="BN126">
         <v>17</v>
@@ -25278,7 +25336,7 @@
     </row>
     <row r="127" spans="1:116" ht="15.75" customHeight="1">
       <c r="A127" s="53" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B127" s="53"/>
       <c r="C127" s="53" t="e">
@@ -25286,10 +25344,10 @@
         <v>#REF!</v>
       </c>
       <c r="D127" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM127" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="BN127">
         <v>25</v>
@@ -25352,7 +25410,7 @@
     </row>
     <row r="128" spans="1:116" ht="15.75" customHeight="1">
       <c r="A128" s="53" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B128" s="53"/>
       <c r="C128" s="53" t="e">
@@ -25360,11 +25418,11 @@
         <v>#REF!</v>
       </c>
       <c r="D128" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BC128" s="12"/>
       <c r="BM128" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="BN128">
         <v>50</v>
@@ -25455,7 +25513,7 @@
     </row>
     <row r="129" spans="1:116" ht="15.75" customHeight="1">
       <c r="A129" s="53" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B129" s="53"/>
       <c r="C129" s="53" t="e">
@@ -25463,10 +25521,10 @@
         <v>#REF!</v>
       </c>
       <c r="D129" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM129" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="BN129">
         <v>110</v>
@@ -25599,7 +25657,7 @@
     </row>
     <row r="130" spans="1:116" ht="15.75" customHeight="1">
       <c r="A130" s="53" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B130" s="53"/>
       <c r="C130" s="53" t="e">
@@ -25607,10 +25665,10 @@
         <v>#REF!</v>
       </c>
       <c r="D130" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM130" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="BN130">
         <v>25</v>
@@ -25680,7 +25738,7 @@
     </row>
     <row r="131" spans="1:116" ht="15.75" customHeight="1">
       <c r="A131" s="53" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B131" s="53"/>
       <c r="C131" s="53" t="e">
@@ -25688,10 +25746,10 @@
         <v>#REF!</v>
       </c>
       <c r="D131" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM131" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="BN131">
         <v>15</v>
@@ -25734,7 +25792,7 @@
     </row>
     <row r="132" spans="1:116" ht="15.75" customHeight="1">
       <c r="A132" s="53" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B132" s="53"/>
       <c r="C132" s="53" t="e">
@@ -25742,10 +25800,10 @@
         <v>#REF!</v>
       </c>
       <c r="D132" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM132" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="BN132">
         <v>15</v>
@@ -25799,7 +25857,7 @@
     </row>
     <row r="133" spans="1:116" ht="15.75" customHeight="1">
       <c r="A133" s="53" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B133" s="53"/>
       <c r="C133" s="53" t="e">
@@ -25807,10 +25865,10 @@
         <v>#REF!</v>
       </c>
       <c r="D133" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM133" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="BN133">
         <v>5</v>
@@ -25853,7 +25911,7 @@
     </row>
     <row r="134" spans="1:116" ht="15.75" customHeight="1">
       <c r="A134" s="53" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B134" s="53"/>
       <c r="C134" s="53" t="e">
@@ -25861,10 +25919,10 @@
         <v>#REF!</v>
       </c>
       <c r="D134" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BM134" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="BN134">
         <v>7.5</v>
@@ -25907,7 +25965,7 @@
     </row>
     <row r="135" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM135" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="BN135">
         <v>60</v>
@@ -25990,7 +26048,7 @@
     </row>
     <row r="136" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM136" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="BN136">
         <v>10</v>
@@ -26029,7 +26087,7 @@
     </row>
     <row r="137" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM137" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="BN137">
         <v>12</v>
@@ -26068,7 +26126,7 @@
     </row>
     <row r="138" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM138" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="BN138">
         <v>15</v>
@@ -26107,7 +26165,7 @@
     </row>
     <row r="139" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM139" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="BN139">
         <v>20</v>
@@ -26151,7 +26209,7 @@
     </row>
     <row r="140" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM140" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="BN140">
         <v>6</v>
@@ -26189,7 +26247,7 @@
     </row>
     <row r="141" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM141" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BN141">
         <v>110</v>
@@ -26307,12 +26365,12 @@
         <v>7490</v>
       </c>
       <c r="DL141" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="142" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM142" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BN142">
         <v>110</v>
@@ -26417,7 +26475,7 @@
     </row>
     <row r="143" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM143" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BN143">
         <v>125</v>
@@ -26446,7 +26504,7 @@
     </row>
     <row r="144" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM144" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="BN144">
         <v>15</v>
@@ -26509,7 +26567,7 @@
     </row>
     <row r="145" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM145" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="BN145">
         <v>7.7</v>
@@ -26573,7 +26631,7 @@
     </row>
     <row r="146" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM146" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="BN146">
         <v>7</v>
@@ -26611,7 +26669,7 @@
     </row>
     <row r="147" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM147" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="BN147">
         <v>25</v>
@@ -26681,7 +26739,7 @@
     </row>
     <row r="148" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM148" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="BN148">
         <v>30</v>
@@ -26751,7 +26809,7 @@
     </row>
     <row r="149" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM149" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="BN149">
         <v>50</v>
@@ -26828,7 +26886,7 @@
     </row>
     <row r="150" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM150" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="BN150">
         <v>60</v>
@@ -26905,7 +26963,7 @@
     </row>
     <row r="151" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM151" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="BN151">
         <v>75</v>
@@ -27017,7 +27075,7 @@
     </row>
     <row r="152" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM152" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="BN152">
         <v>75</v>
@@ -27107,12 +27165,12 @@
         <v>88619</v>
       </c>
       <c r="DL152" s="41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="153" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM153" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BN153">
         <v>75</v>
@@ -27204,7 +27262,7 @@
     </row>
     <row r="154" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM154" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="BN154">
         <v>8</v>
@@ -27274,7 +27332,7 @@
     </row>
     <row r="155" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM155" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="BN155">
         <v>37.5</v>
@@ -27351,12 +27409,12 @@
         <v>75607</v>
       </c>
       <c r="DL155" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="156" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM156" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BN156">
         <v>37.5</v>
@@ -27434,7 +27492,7 @@
     </row>
     <row r="157" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM157" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="BN157">
         <v>60</v>
@@ -27525,12 +27583,12 @@
         <v>83337</v>
       </c>
       <c r="DL157" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="158" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM158" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="BN158">
         <v>60</v>
@@ -27622,7 +27680,7 @@
     </row>
     <row r="159" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM159" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="BN159">
         <v>25</v>
@@ -27669,7 +27727,7 @@
     </row>
     <row r="160" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM160" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="BN160">
         <v>30</v>
@@ -27725,7 +27783,7 @@
     </row>
     <row r="161" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM161" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="BN161">
         <v>50</v>
@@ -27790,7 +27848,7 @@
     </row>
     <row r="162" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM162" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="BN162">
         <v>20</v>
@@ -27828,7 +27886,7 @@
     </row>
     <row r="163" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM163" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="BN163">
         <v>100</v>
@@ -27938,7 +27996,7 @@
     </row>
     <row r="164" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM164" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="BN164">
         <v>75</v>
@@ -28030,7 +28088,7 @@
     </row>
     <row r="165" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM165" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="BN165">
         <v>5</v>
@@ -28093,7 +28151,7 @@
     </row>
     <row r="166" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM166" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="BN166">
         <v>5</v>
@@ -28130,12 +28188,12 @@
         <v>105322</v>
       </c>
       <c r="DL166" s="41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="167" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM167" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="BN167">
         <v>5</v>
@@ -28198,7 +28256,7 @@
     </row>
     <row r="168" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM168" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="BN168">
         <v>60</v>
@@ -28297,7 +28355,7 @@
     </row>
     <row r="169" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM169" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="BN169">
         <v>60</v>
@@ -28390,7 +28448,7 @@
     </row>
     <row r="170" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM170" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="BN170">
         <v>75</v>
@@ -28495,7 +28553,7 @@
     </row>
     <row r="171" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM171" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="BN171">
         <v>75</v>
@@ -28588,7 +28646,7 @@
     </row>
     <row r="172" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM172" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="BN172">
         <v>50</v>
@@ -28665,7 +28723,7 @@
     </row>
     <row r="173" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM173" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="BN173">
         <v>10</v>
@@ -28735,12 +28793,12 @@
         <v>152041</v>
       </c>
       <c r="DL173" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="174" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM174" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="BN174">
         <v>12</v>
@@ -28779,7 +28837,7 @@
     </row>
     <row r="175" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM175" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="BN175">
         <v>15</v>
@@ -28843,7 +28901,7 @@
     </row>
     <row r="176" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM176" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="BN176">
         <v>15</v>
@@ -28906,12 +28964,12 @@
         <v>152048</v>
       </c>
       <c r="DL176" s="41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="177" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM177" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="BN177">
         <v>17</v>
@@ -28961,7 +29019,7 @@
     </row>
     <row r="178" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM178" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="BN178">
         <v>17</v>
@@ -29025,7 +29083,7 @@
     </row>
     <row r="179" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM179" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="BN179">
         <v>20</v>
@@ -29088,12 +29146,12 @@
         <v>52731</v>
       </c>
       <c r="DL179" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="180" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM180" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="BN180">
         <v>20</v>
@@ -29163,12 +29221,12 @@
         <v>152049</v>
       </c>
       <c r="DL180" s="41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="181" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM181" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="BN181">
         <v>250</v>
@@ -29234,7 +29292,7 @@
     </row>
     <row r="182" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM182" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="BN182">
         <v>25</v>
@@ -29298,7 +29356,7 @@
     </row>
     <row r="183" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM183" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="BN183">
         <v>25</v>
@@ -29369,7 +29427,7 @@
     </row>
     <row r="184" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM184" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="BN184">
         <v>30</v>
@@ -29439,12 +29497,12 @@
         <v>143407</v>
       </c>
       <c r="DL184" s="41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="185" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM185" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="BN185">
         <v>30</v>
@@ -29522,7 +29580,7 @@
     </row>
     <row r="186" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM186" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="BN186">
         <v>33</v>
@@ -29569,12 +29627,12 @@
         <v>152046</v>
       </c>
       <c r="DL186" s="41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="187" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM187" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="BN187">
         <v>36</v>
@@ -29633,7 +29691,7 @@
     </row>
     <row r="188" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM188" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="BN188">
         <v>36</v>
@@ -29710,12 +29768,12 @@
         <v>152074</v>
       </c>
       <c r="DL188" s="41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="189" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM189" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="BN189">
         <v>37.5</v>
@@ -29793,7 +29851,7 @@
     </row>
     <row r="190" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM190" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="BN190">
         <v>4</v>
@@ -29857,7 +29915,7 @@
     </row>
     <row r="191" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM191" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="BN191">
         <v>40</v>
@@ -29929,7 +29987,7 @@
     </row>
     <row r="192" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM192" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="BN192">
         <v>5</v>
@@ -29993,7 +30051,7 @@
     </row>
     <row r="193" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM193" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="BN193">
         <v>50</v>
@@ -30077,12 +30135,12 @@
         <v>143409</v>
       </c>
       <c r="DL193" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="194" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM194" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="BN194">
         <v>7.3</v>
@@ -30152,7 +30210,7 @@
     </row>
     <row r="195" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM195" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="BN195">
         <v>7.5</v>
@@ -30209,12 +30267,12 @@
         <v>153992</v>
       </c>
       <c r="DL195" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="196" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM196" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="BN196">
         <v>8</v>
@@ -30285,7 +30343,7 @@
     </row>
     <row r="197" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM197" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="BN197">
         <v>9.1</v>
@@ -30355,7 +30413,7 @@
     </row>
     <row r="198" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM198" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="BN198">
         <v>110</v>
@@ -30475,7 +30533,7 @@
     </row>
     <row r="199" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM199" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="BN199">
         <v>12</v>
@@ -30525,7 +30583,7 @@
     </row>
     <row r="200" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM200" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="BN200">
         <v>3</v>
@@ -30563,12 +30621,12 @@
         <v>152036</v>
       </c>
       <c r="DL200" s="41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="201" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM201" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="BN201">
         <v>37.5</v>
@@ -30635,7 +30693,7 @@
     </row>
     <row r="202" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM202" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="BN202">
         <v>4</v>
@@ -30698,12 +30756,12 @@
         <v>152038</v>
       </c>
       <c r="DL202" s="41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="203" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM203" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="BN203">
         <v>5</v>
@@ -30753,7 +30811,7 @@
     </row>
     <row r="204" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM204" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="BN204">
         <v>5</v>
@@ -30817,7 +30875,7 @@
     </row>
     <row r="205" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM205" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="BN205">
         <v>6</v>
@@ -30855,7 +30913,7 @@
     </row>
     <row r="206" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM206" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="BN206">
         <v>6</v>
@@ -30893,12 +30951,12 @@
         <v>143406</v>
       </c>
       <c r="DL206" s="41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="207" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM207" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="BN207">
         <v>60</v>
@@ -30973,7 +31031,7 @@
     </row>
     <row r="208" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM208" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="BN208">
         <v>75</v>
@@ -31079,7 +31137,7 @@
     </row>
     <row r="209" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM209" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="BN209">
         <v>75</v>
@@ -31171,7 +31229,7 @@
     </row>
     <row r="210" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM210" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="BN210">
         <v>8</v>
@@ -31221,7 +31279,7 @@
     </row>
     <row r="211" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM211" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="BN211">
         <v>10</v>
@@ -31268,7 +31326,7 @@
     </row>
     <row r="212" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM212" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="BN212">
         <v>110</v>
@@ -31380,7 +31438,7 @@
     </row>
     <row r="213" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM213" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="BN213">
         <v>110</v>
@@ -31508,7 +31566,7 @@
     </row>
     <row r="214" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM214" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="BN214">
         <v>12</v>
@@ -31546,7 +31604,7 @@
     </row>
     <row r="215" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM215" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="BN215">
         <v>15</v>
@@ -31584,7 +31642,7 @@
     </row>
     <row r="216" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM216" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="BN216">
         <v>20</v>
@@ -31622,7 +31680,7 @@
     </row>
     <row r="217" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM217" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="BN217">
         <v>250</v>
@@ -31756,7 +31814,7 @@
     </row>
     <row r="218" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM218" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="BN218">
         <v>25</v>
@@ -31799,7 +31857,7 @@
     </row>
     <row r="219" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM219" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="BN219">
         <v>25</v>
@@ -31846,7 +31904,7 @@
     </row>
     <row r="220" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM220" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="BN220">
         <v>30</v>
@@ -31893,7 +31951,7 @@
     </row>
     <row r="221" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM221" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="BN221">
         <v>333</v>
@@ -32027,7 +32085,7 @@
     </row>
     <row r="222" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM222" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="BN222">
         <v>350</v>
@@ -32161,7 +32219,7 @@
     </row>
     <row r="223" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM223" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="BN223">
         <v>36</v>
@@ -32217,7 +32275,7 @@
     </row>
     <row r="224" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM224" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="BN224">
         <v>40</v>
@@ -32272,7 +32330,7 @@
     </row>
     <row r="225" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM225" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="BN225">
         <v>5</v>
@@ -32310,7 +32368,7 @@
     </row>
     <row r="226" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM226" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="BN226">
         <v>50</v>
@@ -32402,7 +32460,7 @@
     </row>
     <row r="227" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM227" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="BN227">
         <v>6</v>
@@ -32440,7 +32498,7 @@
     </row>
     <row r="228" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM228" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="BN228">
         <v>7.5</v>
@@ -32487,7 +32545,7 @@
     </row>
     <row r="229" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM229" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="BN229">
         <v>75</v>
@@ -32599,7 +32657,7 @@
     </row>
     <row r="230" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM230" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="BN230">
         <v>75</v>

--- a/calculo_mppt.xlsx
+++ b/calculo_mppt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enzo.ferreira\Desktop\dimensionador-fotovoltaico-sigiloso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4E7698-5107-441C-9AE4-86036426BA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C44B9E-45AF-4D22-9019-EED95523DB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-4695" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="517">
   <si>
     <t xml:space="preserve">  MAXEON 415 MF PE AL 40 - SPR-MAX3415-BLK-R</t>
   </si>
@@ -3168,9 +3168,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:116" ht="33" customHeight="1">
-      <c r="J1" s="1" t="str">
+      <c r="J1" s="1">
         <f>DL3</f>
-        <v>SIM</v>
+        <v>0</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -3269,9 +3269,9 @@
       <c r="G2" s="69"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="3" t="str">
+      <c r="J2" s="3">
         <f>DL5</f>
-        <v>SIM</v>
+        <v>0</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -3695,9 +3695,7 @@
       <c r="DK3" s="15">
         <v>186192</v>
       </c>
-      <c r="DL3" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL3" s="15"/>
     </row>
     <row r="4" spans="2:116">
       <c r="B4" s="7" t="s">
@@ -3719,11 +3717,11 @@
       </c>
       <c r="H4" s="18">
         <f>IF($F4&lt;=J$2,$C$26,0)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I4" s="19">
         <f>IF(H4&lt;$C$23,0,H4)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J4" s="20">
         <v>0</v>
@@ -3967,11 +3965,11 @@
       </c>
       <c r="H5" s="21">
         <f t="shared" ref="H5:H8" si="2">IF($F5&lt;=J$2,H$4*$F5,0)</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I5" s="19">
         <f>IF(H4&lt;$C$23,0,H5)</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J5" s="20">
         <v>1</v>
@@ -4195,9 +4193,7 @@
       <c r="DK5" s="15">
         <v>167963</v>
       </c>
-      <c r="DL5" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL5" s="15"/>
     </row>
     <row r="6" spans="2:116">
       <c r="B6" s="7" t="s">
@@ -4219,11 +4215,11 @@
       </c>
       <c r="H6" s="21">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I6" s="19">
         <f>IF(H4&lt;$C$23,0,H6)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J6" s="20">
         <v>0</v>
@@ -4452,9 +4448,7 @@
       <c r="DK6" s="25">
         <v>179270</v>
       </c>
-      <c r="DL6" s="25" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL6" s="25"/>
     </row>
     <row r="7" spans="2:116">
       <c r="B7" s="7" t="s">
@@ -4476,11 +4470,11 @@
       </c>
       <c r="H7" s="21">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I7" s="19">
         <f>IF(H4&lt;$C$23,0,H7)</f>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J7" s="20">
         <v>0</v>
@@ -4716,11 +4710,11 @@
       </c>
       <c r="H8" s="21">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I8" s="19">
         <f>IF(H4&lt;$C$23,0,H8)</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J8" s="20">
         <v>0</v>
@@ -4945,9 +4939,7 @@
       <c r="DK8" s="25">
         <v>186183</v>
       </c>
-      <c r="DL8" s="25" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL8" s="25"/>
     </row>
     <row r="9" spans="2:116">
       <c r="B9" t="s">
@@ -4968,11 +4960,11 @@
       </c>
       <c r="H9" s="21">
         <f>IF(AND($F9&lt;=J$2,H4&gt;0),H4-1,0)</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I9" s="19">
         <f>IF(H9&lt;$C$23,0,H9)</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J9" s="20">
         <v>0</v>
@@ -5201,9 +5193,7 @@
       <c r="DK9" s="15">
         <v>179271</v>
       </c>
-      <c r="DL9" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL9" s="15"/>
     </row>
     <row r="10" spans="2:116">
       <c r="B10" t="s">
@@ -5225,11 +5215,11 @@
       </c>
       <c r="H10" s="21">
         <f>IF(AND($F10&lt;=J$2,H9&gt;0),H9*$F10,0)</f>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I10" s="19">
         <f>IF(H9&lt;$C$23,0,H10)</f>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J10" s="20">
         <v>0</v>
@@ -5473,11 +5463,11 @@
       </c>
       <c r="H11" s="21">
         <f>IF(AND($F11&lt;=J$2,H9&gt;0),H9*$F11,0)</f>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I11" s="19">
         <f>IF(H9&lt;$C$23,0,H11)</f>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J11" s="20">
         <v>0</v>
@@ -5700,9 +5690,7 @@
       <c r="DK11" s="31">
         <v>179272</v>
       </c>
-      <c r="DL11" s="31" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL11" s="31"/>
     </row>
     <row r="12" spans="2:116">
       <c r="B12" t="s">
@@ -5724,11 +5712,11 @@
       </c>
       <c r="H12" s="21">
         <f>IF(AND($F12&lt;=J$2,H9&gt;0),H9*$F12,0)</f>
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I12" s="19">
         <f>IF(H9&lt;$C$23,0,H12)</f>
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J12" s="20">
         <v>0</v>
@@ -5963,11 +5951,11 @@
       </c>
       <c r="H13" s="21">
         <f>IF(AND($F13&lt;=J$2,H9&gt;0),H9*$F13,0)</f>
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I13" s="19">
         <f>IF(H9&lt;$C$23,0,H13)</f>
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J13" s="20">
         <v>0</v>
@@ -6210,9 +6198,7 @@
       <c r="DK13" s="15">
         <v>186184</v>
       </c>
-      <c r="DL13" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL13" s="15"/>
     </row>
     <row r="14" spans="2:116">
       <c r="B14" s="73" t="s">
@@ -6229,11 +6215,11 @@
       </c>
       <c r="H14" s="21">
         <f>IF(AND($F14&lt;=J$2,H9&gt;0),H9-1,0)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I14" s="19">
         <f>IF(H14&lt;$C$23,0,H14)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J14" s="20">
         <v>0</v>
@@ -6467,9 +6453,7 @@
       <c r="DK14" s="25">
         <v>179274</v>
       </c>
-      <c r="DL14" s="25" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL14" s="25"/>
     </row>
     <row r="15" spans="2:116">
       <c r="B15" s="32" t="s">
@@ -6491,11 +6475,11 @@
       </c>
       <c r="H15" s="21">
         <f>IF(AND($F15&lt;=J$2,H14&gt;0),H14*$F15,0)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I15" s="19">
         <f>IF(H14&lt;$C$23,0,H15)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J15" s="20">
         <v>0</v>
@@ -6749,11 +6733,11 @@
       </c>
       <c r="H16" s="21">
         <f>IF(AND($F16&lt;=J$2,H14&gt;0),H14*$F16,0)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I16" s="19">
         <f>IF(H14&lt;$C$23,0,H16)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J16" s="20">
         <v>0</v>
@@ -6981,9 +6965,7 @@
       <c r="DK16" s="25">
         <v>168764</v>
       </c>
-      <c r="DL16" s="25" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL16" s="25"/>
     </row>
     <row r="17" spans="2:116">
       <c r="B17" s="32" t="s">
@@ -7005,11 +6987,11 @@
       </c>
       <c r="H17" s="21">
         <f>IF(AND($F17&lt;=J$2,H14&gt;0),H14*$F17,0)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I17" s="19">
         <f>IF(H14&lt;$C$23,0,H17)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J17" s="20">
         <v>0</v>
@@ -7251,9 +7233,7 @@
       <c r="DK17" s="15">
         <v>186177</v>
       </c>
-      <c r="DL17" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL17" s="15"/>
     </row>
     <row r="18" spans="2:116">
       <c r="B18" s="32" t="s">
@@ -7275,11 +7255,11 @@
       </c>
       <c r="H18" s="21">
         <f>IF(AND($F18&lt;=J$2,H14&gt;0),H14*$F18,0)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I18" s="19">
         <f>IF(H14&lt;$C$23,0,H18)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J18" s="20">
         <v>0</v>
@@ -7503,9 +7483,7 @@
       <c r="DK18" s="25">
         <v>168765</v>
       </c>
-      <c r="DL18" s="25" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL18" s="25"/>
     </row>
     <row r="19" spans="2:116">
       <c r="F19" s="26">
@@ -7517,11 +7495,11 @@
       </c>
       <c r="H19" s="21">
         <f>IF(AND($F19&lt;=J$2,H14&gt;0),H14-1,0)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I19" s="19">
         <f>IF(H19&lt;$C$23,0,H19)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J19" s="20">
         <v>0</v>
@@ -7774,11 +7752,11 @@
       </c>
       <c r="H20" s="21">
         <f>IF(AND($F20&lt;=J$2,H19&gt;0),H19*$F20,0)</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I20" s="19">
         <f>IF(H19&lt;$C$23,0,H20)</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J20" s="20">
         <v>0</v>
@@ -8002,9 +7980,7 @@
       <c r="DK20" s="25">
         <v>168766</v>
       </c>
-      <c r="DL20" s="25" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL20" s="25"/>
     </row>
     <row r="21" spans="2:116" ht="15.75" customHeight="1">
       <c r="B21" s="37" t="s">
@@ -8026,11 +8002,11 @@
       </c>
       <c r="H21" s="21">
         <f>IF(AND($F21&lt;=J$2,H19&gt;0),H19*$F21,0)</f>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I21" s="19">
         <f>IF(H19&lt;$C$23,0,H21)</f>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J21" s="20">
         <v>0</v>
@@ -8266,9 +8242,7 @@
       <c r="DK21" s="15">
         <v>167958</v>
       </c>
-      <c r="DL21" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL21" s="15"/>
     </row>
     <row r="22" spans="2:116" ht="15.75" customHeight="1">
       <c r="F22" s="26">
@@ -8280,11 +8254,11 @@
       </c>
       <c r="H22" s="21">
         <f>IF(AND($F22&lt;=J$2,H19&gt;0),H19*$F22,0)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I22" s="19">
         <f>IF(H19&lt;$C$23,0,H22)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J22" s="20">
         <v>0</v>
@@ -8526,9 +8500,7 @@
       <c r="DK22" s="25">
         <v>186180</v>
       </c>
-      <c r="DL22" s="25" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL22" s="25"/>
     </row>
     <row r="23" spans="2:116" ht="15.75" customHeight="1">
       <c r="B23" s="35" t="s">
@@ -8547,11 +8519,11 @@
       </c>
       <c r="H23" s="21">
         <f>IF(AND($F23&lt;=J$2,H19&gt;0),H19*$F23,0)</f>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I23" s="19">
         <f>IF(H19&lt;$C$23,0,H23)</f>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J23" s="20">
         <v>0</v>
@@ -8829,9 +8801,7 @@
       <c r="DK23" s="15">
         <v>186186</v>
       </c>
-      <c r="DL23" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL23" s="15"/>
     </row>
     <row r="24" spans="2:116" ht="15.75" customHeight="1">
       <c r="B24" s="37" t="s">
@@ -8850,11 +8820,11 @@
       </c>
       <c r="H24" s="21">
         <f>IF(AND($F24&lt;=J$2,H19&gt;0),H19-1,0)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I24" s="19">
         <f>IF(H24&lt;$C$23,0,H24)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J24" s="20">
         <v>0</v>
@@ -9168,11 +9138,11 @@
       </c>
       <c r="H25" s="21">
         <f>IF(AND($F25&lt;=J$2,H24&gt;0),H24*$F25,0)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I25" s="19">
         <f>IF(H24&lt;$C$23,0,H25)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J25" s="20">
         <v>0</v>
@@ -9493,11 +9463,11 @@
       </c>
       <c r="H26" s="21">
         <f>IF(AND($F26&lt;=J$2,H24&gt;0),H24*$F26,0)</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I26" s="19">
         <f>IF(H24&lt;$C$23,0,H26)</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J26" s="20">
         <v>0</v>
@@ -9762,11 +9732,11 @@
       </c>
       <c r="H27" s="21">
         <f>IF(AND($F27&lt;=J$2,H24&gt;0),H24*$F27,0)</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I27" s="19">
         <f>IF(H24&lt;$C$23,0,H27)</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J27" s="20">
         <v>0</v>
@@ -10024,11 +9994,11 @@
       </c>
       <c r="H28" s="21">
         <f>IF(AND($F28&lt;=J$2,H24&gt;0),H24*$F28,0)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I28" s="19">
         <f>IF(H24&lt;$C$23,0,H28)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J28" s="20">
         <v>0</v>
@@ -10286,11 +10256,11 @@
       </c>
       <c r="H29" s="21">
         <f>IF(AND($F29&lt;=J$2,H24&gt;0),H24-1,0)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I29" s="19">
         <f>IF(H29&lt;$C$23,0,H29)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J29" s="20">
         <v>0</v>
@@ -10614,11 +10584,11 @@
       </c>
       <c r="H30" s="21">
         <f>IF(AND($F30&lt;=J$2,H29&gt;0),H29*$F30,0)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I30" s="19">
         <f>IF(H29&lt;$C$23,0,H30)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J30" s="20">
         <v>0</v>
@@ -10893,11 +10863,11 @@
       </c>
       <c r="H31" s="21">
         <f>IF(AND($F31&lt;=J$2,H29&gt;0),H29*$F31,0)</f>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I31" s="19">
         <f>IF(H29&lt;$C$23,0,H31)</f>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J31" s="20">
         <v>0</v>
@@ -11171,11 +11141,11 @@
       </c>
       <c r="H32" s="21">
         <f>IF(AND($F32&lt;=J$2,H29&gt;0),H29*$F32,0)</f>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I32" s="19">
         <f>IF(H29&lt;$C$23,0,H32)</f>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J32" s="20">
         <v>0</v>
@@ -11440,11 +11410,11 @@
       </c>
       <c r="H33" s="21">
         <f>IF(AND($F33&lt;=J$2,H29&gt;0),H29*$F33,0)</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I33" s="19">
         <f>IF(H29&lt;$C$23,0,H33)</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J33" s="20">
         <v>0</v>
@@ -11726,11 +11696,11 @@
       </c>
       <c r="H34" s="21">
         <f>IF(AND($F34&lt;=J$2,H29&gt;0),H29-1,0)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I34" s="19">
         <f>IF(H34&lt;$C$23,0,H34)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J34" s="20">
         <v>0</v>
@@ -12002,11 +11972,11 @@
       </c>
       <c r="H35" s="21">
         <f>IF(AND($F35&lt;=J$2,H34&gt;0),H34*$F35,0)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I35" s="19">
         <f>IF(H34&lt;$C$23,0,H35)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J35" s="20">
         <v>0</v>
@@ -12271,11 +12241,11 @@
       </c>
       <c r="H36" s="21">
         <f>IF(AND($F36&lt;=J$2,H34&gt;0),H34*$F36,0)</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I36" s="19">
         <f>IF(H34&lt;$C$23,0,H36)</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J36" s="20">
         <v>0</v>
@@ -12533,11 +12503,11 @@
       </c>
       <c r="H37" s="21">
         <f>IF(AND($F37&lt;=J$2,H34&gt;0),H34*$F37,0)</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I37" s="19">
         <f>IF(H34&lt;$C$23,0,H37)</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J37" s="20">
         <v>0</v>
@@ -12816,11 +12786,11 @@
       </c>
       <c r="H38" s="21">
         <f>IF(AND($F38&lt;=J$2,H34&gt;0),H34*$F38,0)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I38" s="19">
         <f>IF(H34&lt;$C$23,0,H38)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J38" s="20">
         <v>0</v>
@@ -13085,11 +13055,11 @@
       </c>
       <c r="H39" s="21">
         <f>IF(AND($F39&lt;=J$2,H34&gt;0),H34-1,0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I39" s="19">
         <f>IF(H39&lt;$C$23,0,H39)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J39" s="20">
         <v>0</v>
@@ -13355,11 +13325,11 @@
       </c>
       <c r="H40" s="21">
         <f>IF(AND($F40&lt;=J$2,H39&gt;0),H39*$F40,0)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I40" s="19">
         <f>IF(H39&lt;$C$23,0,H40)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J40" s="20">
         <v>0</v>
@@ -13624,11 +13594,11 @@
       </c>
       <c r="H41" s="21">
         <f>IF(AND($F41&lt;=J$2,H39&gt;0),H39*$F41,0)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I41" s="19">
         <f>IF(H39&lt;$C$23,0,H41)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J41" s="20">
         <v>0</v>
@@ -13907,11 +13877,11 @@
       </c>
       <c r="H42" s="21">
         <f>IF(AND($F42&lt;=J$2,H39&gt;0),H39*$F42,0)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I42" s="19">
         <f>IF(H39&lt;$C$23,0,H42)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J42" s="20">
         <v>0</v>
@@ -14225,11 +14195,11 @@
       </c>
       <c r="H43" s="21">
         <f>IF(AND($F43&lt;=J$2,H39&gt;0),H39*$F43,0)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I43" s="19">
         <f>IF(H39&lt;$C$23,0,H43)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J43" s="20">
         <v>0</v>
@@ -14490,11 +14460,11 @@
       </c>
       <c r="H44" s="21">
         <f>IF(AND($F44&lt;=J$2,H39&gt;0),H39-1,0)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I44" s="19">
         <f>IF(H44&lt;$C$23,0,H44)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J44" s="20">
         <v>0</v>
@@ -14759,11 +14729,11 @@
       </c>
       <c r="H45" s="21">
         <f>IF(AND($F45&lt;=J$2,H44&gt;0),H44*$F45,0)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I45" s="19">
         <f>IF(H44&lt;$C$23,0,H45)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J45" s="20">
         <v>0</v>
@@ -15035,11 +15005,11 @@
       </c>
       <c r="H46" s="21">
         <f>IF(AND($F46&lt;=J$2,H44&gt;0),H44*$F46,0)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I46" s="19">
         <f>IF(H44&lt;$C$23,0,H46)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J46" s="20">
         <v>0</v>
@@ -15297,11 +15267,11 @@
       </c>
       <c r="H47" s="21">
         <f>IF(AND($F47&lt;=J$2,H44&gt;0),H44*$F47,0)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I47" s="19">
         <f>IF(H44&lt;$C$23,0,H47)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J47" s="20">
         <v>0</v>
@@ -15559,11 +15529,11 @@
       </c>
       <c r="H48" s="21">
         <f>IF(AND($F48&lt;=J$2,H44&gt;0),H44*$F48,0)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I48" s="19">
         <f>IF(H44&lt;$C$23,0,H48)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J48" s="20">
         <v>0</v>
@@ -15819,11 +15789,11 @@
       </c>
       <c r="H49" s="21">
         <f>IF(AND($F49&lt;=J$2,H44&gt;0),H44-1,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I49" s="19">
         <f>IF(H49&lt;$C$23,0,H49)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J49" s="20">
         <v>0</v>
@@ -16088,11 +16058,11 @@
       </c>
       <c r="H50" s="21">
         <f>IF(AND($F50&lt;=J$2,H49&gt;0),H49*$F50,0)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I50" s="19">
         <f>IF(H49&lt;$C$23,0,H50)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J50" s="20">
         <v>0</v>
@@ -16355,11 +16325,11 @@
       </c>
       <c r="H51" s="21">
         <f>IF(AND($F51&lt;=J$2,H49&gt;0),H49*$F51,0)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I51" s="19">
         <f>IF(H49&lt;$C$23,0,H51)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J51" s="20">
         <v>0</v>
@@ -16617,11 +16587,11 @@
       </c>
       <c r="H52" s="21">
         <f>IF(AND($F52&lt;=J$2,H49&gt;0),H49*$F52,0)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I52" s="19">
         <f>IF(H49&lt;$C$23,0,H52)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J52" s="20">
         <v>0</v>
@@ -16879,11 +16849,11 @@
       </c>
       <c r="H53" s="21">
         <f>IF(AND($F53&lt;=J$2,H49&gt;0),H49*$F53,0)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I53" s="19">
         <f>IF(H49&lt;$C$23,0,H53)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J53" s="20">
         <v>0</v>
@@ -17148,11 +17118,11 @@
       </c>
       <c r="H54" s="21">
         <f>IF(AND($F54&lt;=J$2,H49&gt;0),H49-1,0)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I54" s="19">
         <f>IF(H54&lt;$C$23,0,H54)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" s="20">
         <v>0</v>
@@ -17417,11 +17387,11 @@
       </c>
       <c r="H55" s="21">
         <f>IF(AND($F55&lt;=J$2,H54&gt;0),H54*$F55,0)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I55" s="19">
         <f>IF(H54&lt;$C$23,0,H55)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J55" s="20">
         <v>0</v>
@@ -17645,9 +17615,7 @@
       <c r="DK55" s="15">
         <v>182198</v>
       </c>
-      <c r="DL55" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL55" s="15"/>
     </row>
     <row r="56" spans="2:116" ht="15.75" customHeight="1">
       <c r="B56" s="21" t="e">
@@ -17663,11 +17631,11 @@
       </c>
       <c r="H56" s="21">
         <f>IF(AND($F56&lt;=J$2,H54&gt;0),H54*$F56,0)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I56" s="19">
         <f>IF(H54&lt;$C$23,0,H56)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J56" s="20">
         <v>0</v>
@@ -17899,11 +17867,11 @@
       </c>
       <c r="H57" s="21">
         <f>IF(AND($F57&lt;=J$2,H54&gt;0),H54*$F57,0)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I57" s="19">
         <f>IF(H54&lt;$C$23,0,H57)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J57" s="20">
         <v>0</v>
@@ -18198,9 +18166,7 @@
       <c r="DK57" s="31">
         <v>107282</v>
       </c>
-      <c r="DL57" s="31" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL57" s="31"/>
     </row>
     <row r="58" spans="2:116" ht="15.75" customHeight="1">
       <c r="B58" t="s">
@@ -18219,11 +18185,11 @@
       </c>
       <c r="H58" s="21">
         <f>IF(AND($F58&lt;=J$2,H54&gt;0),H54*$F58,0)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I58" s="19">
         <f>IF(H54&lt;$C$23,0,H58)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J58" s="20">
         <v>0</v>
@@ -18526,7 +18492,7 @@
       </c>
       <c r="C59" s="21" t="e">
         <f t="array" ref="C59">MIN(IF($C$120:$C$134=0," ",$C$120:$C$134))</f>
-        <v>#VALUE!</v>
+        <v>#REF!</v>
       </c>
       <c r="F59" s="26">
         <v>1</v>
@@ -18537,7 +18503,7 @@
       </c>
       <c r="H59" s="21">
         <f>IF(AND($F59&lt;=J$2,H54&gt;0),H54-1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="19">
         <f>IF(H59&lt;$C$23,0,H59)</f>
@@ -18775,9 +18741,7 @@
       <c r="DK59" s="15">
         <v>107277</v>
       </c>
-      <c r="DL59" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL59" s="15"/>
     </row>
     <row r="60" spans="2:116" ht="15.75" customHeight="1">
       <c r="F60" s="26">
@@ -18789,7 +18753,7 @@
       </c>
       <c r="H60" s="21">
         <f>IF(AND($F60&lt;=J$2,H59&gt;0),H59*$F60,0)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I60" s="19">
         <f>IF(H59&lt;$C$23,0,H60)</f>
@@ -19026,7 +18990,7 @@
     <row r="61" spans="2:116" ht="15.75" customHeight="1">
       <c r="B61" s="43" t="e">
         <f>IF(OR(AND(B14="Livoltek Off Grid GF1-5K48S1",C3=665),AND(C59&lt;C58,$C$7&gt;18)),"Ruim","Bom")</f>
-        <v>#VALUE!</v>
+        <v>#REF!</v>
       </c>
       <c r="F61" s="26">
         <v>3</v>
@@ -19037,7 +19001,7 @@
       </c>
       <c r="H61" s="21">
         <f>IF(AND($F61&lt;=J$2,H59&gt;0),H59*$F61,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I61" s="19">
         <f>IF(H59&lt;$C$23,0,H61)</f>
@@ -19293,7 +19257,7 @@
       </c>
       <c r="H62" s="21">
         <f>IF(AND($F62&lt;=J$2,H59&gt;0),H59*$F62,0)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I62" s="19">
         <f>IF(H59&lt;$C$23,0,H62)</f>
@@ -19532,7 +19496,7 @@
       </c>
       <c r="H63" s="21">
         <f>IF(AND($F63&lt;=J$2,H59&gt;0),H59*$F63,0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I63" s="19">
         <f>IF(H59&lt;$C$23,0,H63)</f>
@@ -19841,9 +19805,7 @@
       <c r="DK64" s="25">
         <v>185834</v>
       </c>
-      <c r="DL64" s="25" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL64" s="25"/>
     </row>
     <row r="65" spans="2:116" ht="15.75" customHeight="1">
       <c r="B65" s="51" t="s">
@@ -20043,7 +20005,7 @@
       </c>
       <c r="J66">
         <f t="shared" ref="J66:AZ66" si="32">IF(J2&gt;=1,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66">
         <f t="shared" si="32"/>
@@ -20334,9 +20296,7 @@
       <c r="DK67" s="15">
         <v>107284</v>
       </c>
-      <c r="DL67" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL67" s="15"/>
     </row>
     <row r="68" spans="2:116" ht="15.75" customHeight="1">
       <c r="B68" s="51" t="s">
@@ -20780,9 +20740,7 @@
       <c r="DK72" s="25">
         <v>107271</v>
       </c>
-      <c r="DL72" s="25" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL72" s="25"/>
     </row>
     <row r="73" spans="2:116" ht="15.75" customHeight="1">
       <c r="B73" s="51" t="s">
@@ -20950,9 +20908,7 @@
       <c r="DK74" s="25">
         <v>121772</v>
       </c>
-      <c r="DL74" s="25" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL74" s="25"/>
     </row>
     <row r="75" spans="2:116" ht="15.75" customHeight="1">
       <c r="B75" s="51" t="s">
@@ -21220,9 +21176,7 @@
       <c r="DK77" s="31">
         <v>107272</v>
       </c>
-      <c r="DL77" s="31" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL77" s="31"/>
     </row>
     <row r="78" spans="2:116" ht="15.75" customHeight="1">
       <c r="B78" s="51" t="s">
@@ -21482,9 +21436,7 @@
       <c r="DK80" s="25">
         <v>107273</v>
       </c>
-      <c r="DL80" s="25" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL80" s="25"/>
     </row>
     <row r="81" spans="2:116" ht="15.75" customHeight="1">
       <c r="Q81" s="53"/>
@@ -21895,9 +21847,7 @@
       <c r="DK84" s="25">
         <v>107281</v>
       </c>
-      <c r="DL84" s="25" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL84" s="25"/>
     </row>
     <row r="85" spans="2:116" ht="15.75" customHeight="1">
       <c r="B85" s="51" t="s">
@@ -23382,9 +23332,9 @@
         <v>348</v>
       </c>
       <c r="B102" s="53"/>
-      <c r="C102" s="53" t="e">
+      <c r="C102" s="53">
         <f>IF(J2&gt;0,$C65/J2,0)</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="D102" t="s">
         <v>92</v>
@@ -24475,9 +24425,7 @@
       <c r="DK113" s="15">
         <v>70396</v>
       </c>
-      <c r="DL113" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL113" s="15"/>
     </row>
     <row r="114" spans="1:116" ht="15.75" customHeight="1">
       <c r="A114" s="53" t="s">
@@ -24546,9 +24494,7 @@
       <c r="DK114" s="41">
         <v>70397</v>
       </c>
-      <c r="DL114" s="41" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL114" s="41"/>
     </row>
     <row r="115" spans="1:116" ht="15.75" customHeight="1">
       <c r="A115" s="53" t="s">
@@ -24845,9 +24791,9 @@
         <v>390</v>
       </c>
       <c r="B120" s="53"/>
-      <c r="C120" s="53" t="e">
+      <c r="C120" s="53">
         <f>IF(J2&gt;0,$C83/J2,0)</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="D120" t="s">
         <v>92</v>
@@ -26082,8 +26028,12 @@
       <c r="CW136">
         <v>2</v>
       </c>
-      <c r="DK136" s="41"/>
-      <c r="DL136" s="41"/>
+      <c r="DK136" s="41">
+        <v>215049</v>
+      </c>
+      <c r="DL136" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="137" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM137" t="s">
@@ -26121,8 +26071,12 @@
       <c r="CW137">
         <v>2</v>
       </c>
-      <c r="DK137" s="15"/>
-      <c r="DL137" s="15"/>
+      <c r="DK137" s="15">
+        <v>215050</v>
+      </c>
+      <c r="DL137" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="138" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM138" t="s">
@@ -26160,8 +26114,12 @@
       <c r="CW138">
         <v>2</v>
       </c>
-      <c r="DK138" s="41"/>
-      <c r="DL138" s="41"/>
+      <c r="DK138" s="41">
+        <v>215051</v>
+      </c>
+      <c r="DL138" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="139" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM139" t="s">
@@ -26204,8 +26162,12 @@
       <c r="CW139">
         <v>2</v>
       </c>
-      <c r="DK139" s="15"/>
-      <c r="DL139" s="15"/>
+      <c r="DK139" s="15">
+        <v>215052</v>
+      </c>
+      <c r="DL139" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="140" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM140" t="s">
@@ -26242,8 +26204,12 @@
       <c r="CW140">
         <v>1</v>
       </c>
-      <c r="DK140" s="41"/>
-      <c r="DL140" s="41"/>
+      <c r="DK140" s="41">
+        <v>123552</v>
+      </c>
+      <c r="DL140" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="141" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM141" t="s">
@@ -26364,9 +26330,7 @@
       <c r="DK141" s="15">
         <v>7490</v>
       </c>
-      <c r="DL141" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL141" s="15"/>
     </row>
     <row r="142" spans="1:116" ht="15.75" customHeight="1">
       <c r="BM142" t="s">
@@ -27164,9 +27128,7 @@
       <c r="DK152" s="41">
         <v>88619</v>
       </c>
-      <c r="DL152" s="41" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL152" s="41"/>
     </row>
     <row r="153" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM153" t="s">
@@ -27408,9 +27370,7 @@
       <c r="DK155" s="15">
         <v>75607</v>
       </c>
-      <c r="DL155" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL155" s="15"/>
     </row>
     <row r="156" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM156" t="s">
@@ -27582,9 +27542,7 @@
       <c r="DK157" s="15">
         <v>83337</v>
       </c>
-      <c r="DL157" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL157" s="15"/>
     </row>
     <row r="158" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM158" t="s">
@@ -28187,9 +28145,7 @@
       <c r="DK166" s="41">
         <v>105322</v>
       </c>
-      <c r="DL166" s="41" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL166" s="41"/>
     </row>
     <row r="167" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM167" t="s">
@@ -28792,9 +28748,7 @@
       <c r="DK173" s="15">
         <v>152041</v>
       </c>
-      <c r="DL173" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL173" s="15"/>
     </row>
     <row r="174" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM174" t="s">
@@ -28963,9 +28917,7 @@
       <c r="DK176" s="41">
         <v>152048</v>
       </c>
-      <c r="DL176" s="41" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL176" s="41"/>
     </row>
     <row r="177" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM177" t="s">
@@ -29145,9 +29097,7 @@
       <c r="DK179" s="15">
         <v>52731</v>
       </c>
-      <c r="DL179" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL179" s="15"/>
     </row>
     <row r="180" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM180" t="s">
@@ -29220,9 +29170,7 @@
       <c r="DK180" s="41">
         <v>152049</v>
       </c>
-      <c r="DL180" s="41" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL180" s="41"/>
     </row>
     <row r="181" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM181" t="s">
@@ -29496,9 +29444,7 @@
       <c r="DK184" s="41">
         <v>143407</v>
       </c>
-      <c r="DL184" s="41" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL184" s="41"/>
     </row>
     <row r="185" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM185" t="s">
@@ -29626,9 +29572,7 @@
       <c r="DK186" s="41">
         <v>152046</v>
       </c>
-      <c r="DL186" s="41" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL186" s="41"/>
     </row>
     <row r="187" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM187" t="s">
@@ -29767,9 +29711,7 @@
       <c r="DK188" s="41">
         <v>152074</v>
       </c>
-      <c r="DL188" s="41" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL188" s="41"/>
     </row>
     <row r="189" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM189" t="s">
@@ -30134,9 +30076,7 @@
       <c r="DK193" s="15">
         <v>143409</v>
       </c>
-      <c r="DL193" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL193" s="15"/>
     </row>
     <row r="194" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM194" t="s">
@@ -30266,9 +30206,7 @@
       <c r="DK195" s="15">
         <v>153992</v>
       </c>
-      <c r="DL195" s="15" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL195" s="15"/>
     </row>
     <row r="196" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM196" t="s">
@@ -30620,9 +30558,7 @@
       <c r="DK200" s="41">
         <v>152036</v>
       </c>
-      <c r="DL200" s="41" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL200" s="41"/>
     </row>
     <row r="201" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM201" t="s">
@@ -30755,9 +30691,7 @@
       <c r="DK202" s="41">
         <v>152038</v>
       </c>
-      <c r="DL202" s="41" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL202" s="41"/>
     </row>
     <row r="203" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM203" t="s">
@@ -30950,9 +30884,7 @@
       <c r="DK206" s="41">
         <v>143406</v>
       </c>
-      <c r="DL206" s="41" t="s">
-        <v>516</v>
-      </c>
+      <c r="DL206" s="41"/>
     </row>
     <row r="207" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM207" t="s">

--- a/calculo_mppt.xlsx
+++ b/calculo_mppt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enzo.ferreira\Desktop\dimensionador-fotovoltaico-sigiloso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C44B9E-45AF-4D22-9019-EED95523DB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F38EAEA-0749-4E04-9B61-21F7A2C9C3D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-4695" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="517">
   <si>
     <t xml:space="preserve">  MAXEON 415 MF PE AL 40 - SPR-MAX3415-BLK-R</t>
   </si>
@@ -3168,9 +3168,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:116" ht="33" customHeight="1">
-      <c r="J1" s="1">
+      <c r="J1" s="1" t="str">
         <f>DL3</f>
-        <v>0</v>
+        <v>SIM</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -3269,9 +3269,9 @@
       <c r="G2" s="69"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="3">
+      <c r="J2" s="3" t="str">
         <f>DL5</f>
-        <v>0</v>
+        <v>SIM</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -3695,7 +3695,9 @@
       <c r="DK3" s="15">
         <v>186192</v>
       </c>
-      <c r="DL3" s="15"/>
+      <c r="DL3" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="4" spans="2:116">
       <c r="B4" s="7" t="s">
@@ -3717,11 +3719,11 @@
       </c>
       <c r="H4" s="18">
         <f>IF($F4&lt;=J$2,$C$26,0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I4" s="19">
         <f>IF(H4&lt;$C$23,0,H4)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J4" s="20">
         <v>0</v>
@@ -3965,11 +3967,11 @@
       </c>
       <c r="H5" s="21">
         <f t="shared" ref="H5:H8" si="2">IF($F5&lt;=J$2,H$4*$F5,0)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I5" s="19">
         <f>IF(H4&lt;$C$23,0,H5)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J5" s="20">
         <v>1</v>
@@ -4193,7 +4195,9 @@
       <c r="DK5" s="15">
         <v>167963</v>
       </c>
-      <c r="DL5" s="15"/>
+      <c r="DL5" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="6" spans="2:116">
       <c r="B6" s="7" t="s">
@@ -4215,11 +4219,11 @@
       </c>
       <c r="H6" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I6" s="19">
         <f>IF(H4&lt;$C$23,0,H6)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J6" s="20">
         <v>0</v>
@@ -4448,7 +4452,9 @@
       <c r="DK6" s="25">
         <v>179270</v>
       </c>
-      <c r="DL6" s="25"/>
+      <c r="DL6" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="7" spans="2:116">
       <c r="B7" s="7" t="s">
@@ -4470,11 +4476,11 @@
       </c>
       <c r="H7" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I7" s="19">
         <f>IF(H4&lt;$C$23,0,H7)</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J7" s="20">
         <v>0</v>
@@ -4710,11 +4716,11 @@
       </c>
       <c r="H8" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I8" s="19">
         <f>IF(H4&lt;$C$23,0,H8)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J8" s="20">
         <v>0</v>
@@ -4939,7 +4945,9 @@
       <c r="DK8" s="25">
         <v>186183</v>
       </c>
-      <c r="DL8" s="25"/>
+      <c r="DL8" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="9" spans="2:116">
       <c r="B9" t="s">
@@ -4960,11 +4968,11 @@
       </c>
       <c r="H9" s="21">
         <f>IF(AND($F9&lt;=J$2,H4&gt;0),H4-1,0)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I9" s="19">
         <f>IF(H9&lt;$C$23,0,H9)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J9" s="20">
         <v>0</v>
@@ -5193,7 +5201,9 @@
       <c r="DK9" s="15">
         <v>179271</v>
       </c>
-      <c r="DL9" s="15"/>
+      <c r="DL9" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="10" spans="2:116">
       <c r="B10" t="s">
@@ -5215,11 +5225,11 @@
       </c>
       <c r="H10" s="21">
         <f>IF(AND($F10&lt;=J$2,H9&gt;0),H9*$F10,0)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I10" s="19">
         <f>IF(H9&lt;$C$23,0,H10)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J10" s="20">
         <v>0</v>
@@ -5463,11 +5473,11 @@
       </c>
       <c r="H11" s="21">
         <f>IF(AND($F11&lt;=J$2,H9&gt;0),H9*$F11,0)</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I11" s="19">
         <f>IF(H9&lt;$C$23,0,H11)</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J11" s="20">
         <v>0</v>
@@ -5690,7 +5700,9 @@
       <c r="DK11" s="31">
         <v>179272</v>
       </c>
-      <c r="DL11" s="31"/>
+      <c r="DL11" s="31" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="12" spans="2:116">
       <c r="B12" t="s">
@@ -5712,11 +5724,11 @@
       </c>
       <c r="H12" s="21">
         <f>IF(AND($F12&lt;=J$2,H9&gt;0),H9*$F12,0)</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I12" s="19">
         <f>IF(H9&lt;$C$23,0,H12)</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J12" s="20">
         <v>0</v>
@@ -5951,11 +5963,11 @@
       </c>
       <c r="H13" s="21">
         <f>IF(AND($F13&lt;=J$2,H9&gt;0),H9*$F13,0)</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I13" s="19">
         <f>IF(H9&lt;$C$23,0,H13)</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J13" s="20">
         <v>0</v>
@@ -6198,7 +6210,9 @@
       <c r="DK13" s="15">
         <v>186184</v>
       </c>
-      <c r="DL13" s="15"/>
+      <c r="DL13" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="14" spans="2:116">
       <c r="B14" s="73" t="s">
@@ -6215,11 +6229,11 @@
       </c>
       <c r="H14" s="21">
         <f>IF(AND($F14&lt;=J$2,H9&gt;0),H9-1,0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I14" s="19">
         <f>IF(H14&lt;$C$23,0,H14)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J14" s="20">
         <v>0</v>
@@ -6453,7 +6467,9 @@
       <c r="DK14" s="25">
         <v>179274</v>
       </c>
-      <c r="DL14" s="25"/>
+      <c r="DL14" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="15" spans="2:116">
       <c r="B15" s="32" t="s">
@@ -6475,11 +6491,11 @@
       </c>
       <c r="H15" s="21">
         <f>IF(AND($F15&lt;=J$2,H14&gt;0),H14*$F15,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I15" s="19">
         <f>IF(H14&lt;$C$23,0,H15)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J15" s="20">
         <v>0</v>
@@ -6733,11 +6749,11 @@
       </c>
       <c r="H16" s="21">
         <f>IF(AND($F16&lt;=J$2,H14&gt;0),H14*$F16,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I16" s="19">
         <f>IF(H14&lt;$C$23,0,H16)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J16" s="20">
         <v>0</v>
@@ -6965,7 +6981,9 @@
       <c r="DK16" s="25">
         <v>168764</v>
       </c>
-      <c r="DL16" s="25"/>
+      <c r="DL16" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="17" spans="2:116">
       <c r="B17" s="32" t="s">
@@ -6987,11 +7005,11 @@
       </c>
       <c r="H17" s="21">
         <f>IF(AND($F17&lt;=J$2,H14&gt;0),H14*$F17,0)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I17" s="19">
         <f>IF(H14&lt;$C$23,0,H17)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J17" s="20">
         <v>0</v>
@@ -7233,7 +7251,9 @@
       <c r="DK17" s="15">
         <v>186177</v>
       </c>
-      <c r="DL17" s="15"/>
+      <c r="DL17" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="18" spans="2:116">
       <c r="B18" s="32" t="s">
@@ -7255,11 +7275,11 @@
       </c>
       <c r="H18" s="21">
         <f>IF(AND($F18&lt;=J$2,H14&gt;0),H14*$F18,0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I18" s="19">
         <f>IF(H14&lt;$C$23,0,H18)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J18" s="20">
         <v>0</v>
@@ -7483,7 +7503,9 @@
       <c r="DK18" s="25">
         <v>168765</v>
       </c>
-      <c r="DL18" s="25"/>
+      <c r="DL18" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="19" spans="2:116">
       <c r="F19" s="26">
@@ -7495,11 +7517,11 @@
       </c>
       <c r="H19" s="21">
         <f>IF(AND($F19&lt;=J$2,H14&gt;0),H14-1,0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I19" s="19">
         <f>IF(H19&lt;$C$23,0,H19)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J19" s="20">
         <v>0</v>
@@ -7752,11 +7774,11 @@
       </c>
       <c r="H20" s="21">
         <f>IF(AND($F20&lt;=J$2,H19&gt;0),H19*$F20,0)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I20" s="19">
         <f>IF(H19&lt;$C$23,0,H20)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J20" s="20">
         <v>0</v>
@@ -7980,7 +8002,9 @@
       <c r="DK20" s="25">
         <v>168766</v>
       </c>
-      <c r="DL20" s="25"/>
+      <c r="DL20" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="21" spans="2:116" ht="15.75" customHeight="1">
       <c r="B21" s="37" t="s">
@@ -8002,11 +8026,11 @@
       </c>
       <c r="H21" s="21">
         <f>IF(AND($F21&lt;=J$2,H19&gt;0),H19*$F21,0)</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I21" s="19">
         <f>IF(H19&lt;$C$23,0,H21)</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J21" s="20">
         <v>0</v>
@@ -8242,7 +8266,9 @@
       <c r="DK21" s="15">
         <v>167958</v>
       </c>
-      <c r="DL21" s="15"/>
+      <c r="DL21" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="22" spans="2:116" ht="15.75" customHeight="1">
       <c r="F22" s="26">
@@ -8254,11 +8280,11 @@
       </c>
       <c r="H22" s="21">
         <f>IF(AND($F22&lt;=J$2,H19&gt;0),H19*$F22,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I22" s="19">
         <f>IF(H19&lt;$C$23,0,H22)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J22" s="20">
         <v>0</v>
@@ -8500,7 +8526,9 @@
       <c r="DK22" s="25">
         <v>186180</v>
       </c>
-      <c r="DL22" s="25"/>
+      <c r="DL22" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="23" spans="2:116" ht="15.75" customHeight="1">
       <c r="B23" s="35" t="s">
@@ -8519,11 +8547,11 @@
       </c>
       <c r="H23" s="21">
         <f>IF(AND($F23&lt;=J$2,H19&gt;0),H19*$F23,0)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I23" s="19">
         <f>IF(H19&lt;$C$23,0,H23)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J23" s="20">
         <v>0</v>
@@ -8801,7 +8829,9 @@
       <c r="DK23" s="15">
         <v>186186</v>
       </c>
-      <c r="DL23" s="15"/>
+      <c r="DL23" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="24" spans="2:116" ht="15.75" customHeight="1">
       <c r="B24" s="37" t="s">
@@ -8820,11 +8850,11 @@
       </c>
       <c r="H24" s="21">
         <f>IF(AND($F24&lt;=J$2,H19&gt;0),H19-1,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I24" s="19">
         <f>IF(H24&lt;$C$23,0,H24)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J24" s="20">
         <v>0</v>
@@ -9138,11 +9168,11 @@
       </c>
       <c r="H25" s="21">
         <f>IF(AND($F25&lt;=J$2,H24&gt;0),H24*$F25,0)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I25" s="19">
         <f>IF(H24&lt;$C$23,0,H25)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J25" s="20">
         <v>0</v>
@@ -9463,11 +9493,11 @@
       </c>
       <c r="H26" s="21">
         <f>IF(AND($F26&lt;=J$2,H24&gt;0),H24*$F26,0)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I26" s="19">
         <f>IF(H24&lt;$C$23,0,H26)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J26" s="20">
         <v>0</v>
@@ -9732,11 +9762,11 @@
       </c>
       <c r="H27" s="21">
         <f>IF(AND($F27&lt;=J$2,H24&gt;0),H24*$F27,0)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I27" s="19">
         <f>IF(H24&lt;$C$23,0,H27)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J27" s="20">
         <v>0</v>
@@ -9994,11 +10024,11 @@
       </c>
       <c r="H28" s="21">
         <f>IF(AND($F28&lt;=J$2,H24&gt;0),H24*$F28,0)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I28" s="19">
         <f>IF(H24&lt;$C$23,0,H28)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J28" s="20">
         <v>0</v>
@@ -10256,11 +10286,11 @@
       </c>
       <c r="H29" s="21">
         <f>IF(AND($F29&lt;=J$2,H24&gt;0),H24-1,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I29" s="19">
         <f>IF(H29&lt;$C$23,0,H29)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J29" s="20">
         <v>0</v>
@@ -10584,11 +10614,11 @@
       </c>
       <c r="H30" s="21">
         <f>IF(AND($F30&lt;=J$2,H29&gt;0),H29*$F30,0)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I30" s="19">
         <f>IF(H29&lt;$C$23,0,H30)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J30" s="20">
         <v>0</v>
@@ -10863,11 +10893,11 @@
       </c>
       <c r="H31" s="21">
         <f>IF(AND($F31&lt;=J$2,H29&gt;0),H29*$F31,0)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I31" s="19">
         <f>IF(H29&lt;$C$23,0,H31)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J31" s="20">
         <v>0</v>
@@ -11141,11 +11171,11 @@
       </c>
       <c r="H32" s="21">
         <f>IF(AND($F32&lt;=J$2,H29&gt;0),H29*$F32,0)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I32" s="19">
         <f>IF(H29&lt;$C$23,0,H32)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J32" s="20">
         <v>0</v>
@@ -11410,11 +11440,11 @@
       </c>
       <c r="H33" s="21">
         <f>IF(AND($F33&lt;=J$2,H29&gt;0),H29*$F33,0)</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I33" s="19">
         <f>IF(H29&lt;$C$23,0,H33)</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J33" s="20">
         <v>0</v>
@@ -11696,11 +11726,11 @@
       </c>
       <c r="H34" s="21">
         <f>IF(AND($F34&lt;=J$2,H29&gt;0),H29-1,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I34" s="19">
         <f>IF(H34&lt;$C$23,0,H34)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J34" s="20">
         <v>0</v>
@@ -11972,11 +12002,11 @@
       </c>
       <c r="H35" s="21">
         <f>IF(AND($F35&lt;=J$2,H34&gt;0),H34*$F35,0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I35" s="19">
         <f>IF(H34&lt;$C$23,0,H35)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J35" s="20">
         <v>0</v>
@@ -12241,11 +12271,11 @@
       </c>
       <c r="H36" s="21">
         <f>IF(AND($F36&lt;=J$2,H34&gt;0),H34*$F36,0)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I36" s="19">
         <f>IF(H34&lt;$C$23,0,H36)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J36" s="20">
         <v>0</v>
@@ -12503,11 +12533,11 @@
       </c>
       <c r="H37" s="21">
         <f>IF(AND($F37&lt;=J$2,H34&gt;0),H34*$F37,0)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I37" s="19">
         <f>IF(H34&lt;$C$23,0,H37)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J37" s="20">
         <v>0</v>
@@ -12786,11 +12816,11 @@
       </c>
       <c r="H38" s="21">
         <f>IF(AND($F38&lt;=J$2,H34&gt;0),H34*$F38,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I38" s="19">
         <f>IF(H34&lt;$C$23,0,H38)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J38" s="20">
         <v>0</v>
@@ -13055,11 +13085,11 @@
       </c>
       <c r="H39" s="21">
         <f>IF(AND($F39&lt;=J$2,H34&gt;0),H34-1,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I39" s="19">
         <f>IF(H39&lt;$C$23,0,H39)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J39" s="20">
         <v>0</v>
@@ -13325,11 +13355,11 @@
       </c>
       <c r="H40" s="21">
         <f>IF(AND($F40&lt;=J$2,H39&gt;0),H39*$F40,0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I40" s="19">
         <f>IF(H39&lt;$C$23,0,H40)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J40" s="20">
         <v>0</v>
@@ -13594,11 +13624,11 @@
       </c>
       <c r="H41" s="21">
         <f>IF(AND($F41&lt;=J$2,H39&gt;0),H39*$F41,0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I41" s="19">
         <f>IF(H39&lt;$C$23,0,H41)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J41" s="20">
         <v>0</v>
@@ -13877,11 +13907,11 @@
       </c>
       <c r="H42" s="21">
         <f>IF(AND($F42&lt;=J$2,H39&gt;0),H39*$F42,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I42" s="19">
         <f>IF(H39&lt;$C$23,0,H42)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J42" s="20">
         <v>0</v>
@@ -14195,11 +14225,11 @@
       </c>
       <c r="H43" s="21">
         <f>IF(AND($F43&lt;=J$2,H39&gt;0),H39*$F43,0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I43" s="19">
         <f>IF(H39&lt;$C$23,0,H43)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J43" s="20">
         <v>0</v>
@@ -14460,11 +14490,11 @@
       </c>
       <c r="H44" s="21">
         <f>IF(AND($F44&lt;=J$2,H39&gt;0),H39-1,0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I44" s="19">
         <f>IF(H44&lt;$C$23,0,H44)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J44" s="20">
         <v>0</v>
@@ -14729,11 +14759,11 @@
       </c>
       <c r="H45" s="21">
         <f>IF(AND($F45&lt;=J$2,H44&gt;0),H44*$F45,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I45" s="19">
         <f>IF(H44&lt;$C$23,0,H45)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J45" s="20">
         <v>0</v>
@@ -15005,11 +15035,11 @@
       </c>
       <c r="H46" s="21">
         <f>IF(AND($F46&lt;=J$2,H44&gt;0),H44*$F46,0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I46" s="19">
         <f>IF(H44&lt;$C$23,0,H46)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J46" s="20">
         <v>0</v>
@@ -15267,11 +15297,11 @@
       </c>
       <c r="H47" s="21">
         <f>IF(AND($F47&lt;=J$2,H44&gt;0),H44*$F47,0)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I47" s="19">
         <f>IF(H44&lt;$C$23,0,H47)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J47" s="20">
         <v>0</v>
@@ -15529,11 +15559,11 @@
       </c>
       <c r="H48" s="21">
         <f>IF(AND($F48&lt;=J$2,H44&gt;0),H44*$F48,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I48" s="19">
         <f>IF(H44&lt;$C$23,0,H48)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J48" s="20">
         <v>0</v>
@@ -15789,11 +15819,11 @@
       </c>
       <c r="H49" s="21">
         <f>IF(AND($F49&lt;=J$2,H44&gt;0),H44-1,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I49" s="19">
         <f>IF(H49&lt;$C$23,0,H49)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J49" s="20">
         <v>0</v>
@@ -16058,11 +16088,11 @@
       </c>
       <c r="H50" s="21">
         <f>IF(AND($F50&lt;=J$2,H49&gt;0),H49*$F50,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I50" s="19">
         <f>IF(H49&lt;$C$23,0,H50)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J50" s="20">
         <v>0</v>
@@ -16325,11 +16355,11 @@
       </c>
       <c r="H51" s="21">
         <f>IF(AND($F51&lt;=J$2,H49&gt;0),H49*$F51,0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I51" s="19">
         <f>IF(H49&lt;$C$23,0,H51)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J51" s="20">
         <v>0</v>
@@ -16587,11 +16617,11 @@
       </c>
       <c r="H52" s="21">
         <f>IF(AND($F52&lt;=J$2,H49&gt;0),H49*$F52,0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I52" s="19">
         <f>IF(H49&lt;$C$23,0,H52)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J52" s="20">
         <v>0</v>
@@ -16849,11 +16879,11 @@
       </c>
       <c r="H53" s="21">
         <f>IF(AND($F53&lt;=J$2,H49&gt;0),H49*$F53,0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I53" s="19">
         <f>IF(H49&lt;$C$23,0,H53)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J53" s="20">
         <v>0</v>
@@ -17118,11 +17148,11 @@
       </c>
       <c r="H54" s="21">
         <f>IF(AND($F54&lt;=J$2,H49&gt;0),H49-1,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" s="19">
         <f>IF(H54&lt;$C$23,0,H54)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" s="20">
         <v>0</v>
@@ -17387,11 +17417,11 @@
       </c>
       <c r="H55" s="21">
         <f>IF(AND($F55&lt;=J$2,H54&gt;0),H54*$F55,0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I55" s="19">
         <f>IF(H54&lt;$C$23,0,H55)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J55" s="20">
         <v>0</v>
@@ -17615,7 +17645,9 @@
       <c r="DK55" s="15">
         <v>182198</v>
       </c>
-      <c r="DL55" s="15"/>
+      <c r="DL55" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="56" spans="2:116" ht="15.75" customHeight="1">
       <c r="B56" s="21" t="e">
@@ -17631,11 +17663,11 @@
       </c>
       <c r="H56" s="21">
         <f>IF(AND($F56&lt;=J$2,H54&gt;0),H54*$F56,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I56" s="19">
         <f>IF(H54&lt;$C$23,0,H56)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J56" s="20">
         <v>0</v>
@@ -17867,11 +17899,11 @@
       </c>
       <c r="H57" s="21">
         <f>IF(AND($F57&lt;=J$2,H54&gt;0),H54*$F57,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I57" s="19">
         <f>IF(H54&lt;$C$23,0,H57)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J57" s="20">
         <v>0</v>
@@ -18166,7 +18198,9 @@
       <c r="DK57" s="31">
         <v>107282</v>
       </c>
-      <c r="DL57" s="31"/>
+      <c r="DL57" s="31" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="58" spans="2:116" ht="15.75" customHeight="1">
       <c r="B58" t="s">
@@ -18185,11 +18219,11 @@
       </c>
       <c r="H58" s="21">
         <f>IF(AND($F58&lt;=J$2,H54&gt;0),H54*$F58,0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I58" s="19">
         <f>IF(H54&lt;$C$23,0,H58)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J58" s="20">
         <v>0</v>
@@ -18492,7 +18526,7 @@
       </c>
       <c r="C59" s="21" t="e">
         <f t="array" ref="C59">MIN(IF($C$120:$C$134=0," ",$C$120:$C$134))</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F59" s="26">
         <v>1</v>
@@ -18503,7 +18537,7 @@
       </c>
       <c r="H59" s="21">
         <f>IF(AND($F59&lt;=J$2,H54&gt;0),H54-1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="19">
         <f>IF(H59&lt;$C$23,0,H59)</f>
@@ -18741,7 +18775,9 @@
       <c r="DK59" s="15">
         <v>107277</v>
       </c>
-      <c r="DL59" s="15"/>
+      <c r="DL59" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="60" spans="2:116" ht="15.75" customHeight="1">
       <c r="F60" s="26">
@@ -18753,7 +18789,7 @@
       </c>
       <c r="H60" s="21">
         <f>IF(AND($F60&lt;=J$2,H59&gt;0),H59*$F60,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I60" s="19">
         <f>IF(H59&lt;$C$23,0,H60)</f>
@@ -18990,7 +19026,7 @@
     <row r="61" spans="2:116" ht="15.75" customHeight="1">
       <c r="B61" s="43" t="e">
         <f>IF(OR(AND(B14="Livoltek Off Grid GF1-5K48S1",C3=665),AND(C59&lt;C58,$C$7&gt;18)),"Ruim","Bom")</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F61" s="26">
         <v>3</v>
@@ -19001,7 +19037,7 @@
       </c>
       <c r="H61" s="21">
         <f>IF(AND($F61&lt;=J$2,H59&gt;0),H59*$F61,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I61" s="19">
         <f>IF(H59&lt;$C$23,0,H61)</f>
@@ -19257,7 +19293,7 @@
       </c>
       <c r="H62" s="21">
         <f>IF(AND($F62&lt;=J$2,H59&gt;0),H59*$F62,0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I62" s="19">
         <f>IF(H59&lt;$C$23,0,H62)</f>
@@ -19496,7 +19532,7 @@
       </c>
       <c r="H63" s="21">
         <f>IF(AND($F63&lt;=J$2,H59&gt;0),H59*$F63,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I63" s="19">
         <f>IF(H59&lt;$C$23,0,H63)</f>
@@ -19805,7 +19841,9 @@
       <c r="DK64" s="25">
         <v>185834</v>
       </c>
-      <c r="DL64" s="25"/>
+      <c r="DL64" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="65" spans="2:116" ht="15.75" customHeight="1">
       <c r="B65" s="51" t="s">
@@ -20005,7 +20043,7 @@
       </c>
       <c r="J66">
         <f t="shared" ref="J66:AZ66" si="32">IF(J2&gt;=1,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66">
         <f t="shared" si="32"/>
@@ -20296,7 +20334,9 @@
       <c r="DK67" s="15">
         <v>107284</v>
       </c>
-      <c r="DL67" s="15"/>
+      <c r="DL67" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="68" spans="2:116" ht="15.75" customHeight="1">
       <c r="B68" s="51" t="s">
@@ -20740,7 +20780,9 @@
       <c r="DK72" s="25">
         <v>107271</v>
       </c>
-      <c r="DL72" s="25"/>
+      <c r="DL72" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="73" spans="2:116" ht="15.75" customHeight="1">
       <c r="B73" s="51" t="s">
@@ -20908,7 +20950,9 @@
       <c r="DK74" s="25">
         <v>121772</v>
       </c>
-      <c r="DL74" s="25"/>
+      <c r="DL74" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="75" spans="2:116" ht="15.75" customHeight="1">
       <c r="B75" s="51" t="s">
@@ -21176,7 +21220,9 @@
       <c r="DK77" s="31">
         <v>107272</v>
       </c>
-      <c r="DL77" s="31"/>
+      <c r="DL77" s="31" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="78" spans="2:116" ht="15.75" customHeight="1">
       <c r="B78" s="51" t="s">
@@ -21436,7 +21482,9 @@
       <c r="DK80" s="25">
         <v>107273</v>
       </c>
-      <c r="DL80" s="25"/>
+      <c r="DL80" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="81" spans="2:116" ht="15.75" customHeight="1">
       <c r="Q81" s="53"/>
@@ -21847,7 +21895,9 @@
       <c r="DK84" s="25">
         <v>107281</v>
       </c>
-      <c r="DL84" s="25"/>
+      <c r="DL84" s="25" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="85" spans="2:116" ht="15.75" customHeight="1">
       <c r="B85" s="51" t="s">
@@ -23332,9 +23382,9 @@
         <v>348</v>
       </c>
       <c r="B102" s="53"/>
-      <c r="C102" s="53">
+      <c r="C102" s="53" t="e">
         <f>IF(J2&gt;0,$C65/J2,0)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D102" t="s">
         <v>92</v>
@@ -24425,7 +24475,9 @@
       <c r="DK113" s="15">
         <v>70396</v>
       </c>
-      <c r="DL113" s="15"/>
+      <c r="DL113" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="114" spans="1:116" ht="15.75" customHeight="1">
       <c r="A114" s="53" t="s">
@@ -24494,7 +24546,9 @@
       <c r="DK114" s="41">
         <v>70397</v>
       </c>
-      <c r="DL114" s="41"/>
+      <c r="DL114" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="115" spans="1:116" ht="15.75" customHeight="1">
       <c r="A115" s="53" t="s">
@@ -24791,9 +24845,9 @@
         <v>390</v>
       </c>
       <c r="B120" s="53"/>
-      <c r="C120" s="53">
+      <c r="C120" s="53" t="e">
         <f>IF(J2&gt;0,$C83/J2,0)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D120" t="s">
         <v>92</v>
@@ -27128,7 +27182,9 @@
       <c r="DK152" s="41">
         <v>88619</v>
       </c>
-      <c r="DL152" s="41"/>
+      <c r="DL152" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="153" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM153" t="s">
@@ -27370,7 +27426,9 @@
       <c r="DK155" s="15">
         <v>75607</v>
       </c>
-      <c r="DL155" s="15"/>
+      <c r="DL155" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="156" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM156" t="s">
@@ -27542,7 +27600,9 @@
       <c r="DK157" s="15">
         <v>83337</v>
       </c>
-      <c r="DL157" s="15"/>
+      <c r="DL157" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="158" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM158" t="s">
@@ -28145,7 +28205,9 @@
       <c r="DK166" s="41">
         <v>105322</v>
       </c>
-      <c r="DL166" s="41"/>
+      <c r="DL166" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="167" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM167" t="s">
@@ -28748,7 +28810,9 @@
       <c r="DK173" s="15">
         <v>152041</v>
       </c>
-      <c r="DL173" s="15"/>
+      <c r="DL173" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="174" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM174" t="s">
@@ -28917,7 +28981,9 @@
       <c r="DK176" s="41">
         <v>152048</v>
       </c>
-      <c r="DL176" s="41"/>
+      <c r="DL176" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="177" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM177" t="s">
@@ -29097,7 +29163,9 @@
       <c r="DK179" s="15">
         <v>52731</v>
       </c>
-      <c r="DL179" s="15"/>
+      <c r="DL179" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="180" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM180" t="s">
@@ -29170,7 +29238,9 @@
       <c r="DK180" s="41">
         <v>152049</v>
       </c>
-      <c r="DL180" s="41"/>
+      <c r="DL180" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="181" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM181" t="s">
@@ -29444,7 +29514,9 @@
       <c r="DK184" s="41">
         <v>143407</v>
       </c>
-      <c r="DL184" s="41"/>
+      <c r="DL184" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="185" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM185" t="s">
@@ -29572,7 +29644,9 @@
       <c r="DK186" s="41">
         <v>152046</v>
       </c>
-      <c r="DL186" s="41"/>
+      <c r="DL186" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="187" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM187" t="s">
@@ -29711,7 +29785,9 @@
       <c r="DK188" s="41">
         <v>152074</v>
       </c>
-      <c r="DL188" s="41"/>
+      <c r="DL188" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="189" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM189" t="s">
@@ -30076,7 +30152,9 @@
       <c r="DK193" s="15">
         <v>143409</v>
       </c>
-      <c r="DL193" s="15"/>
+      <c r="DL193" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="194" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM194" t="s">
@@ -30206,7 +30284,9 @@
       <c r="DK195" s="15">
         <v>153992</v>
       </c>
-      <c r="DL195" s="15"/>
+      <c r="DL195" s="15" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="196" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM196" t="s">
@@ -30558,7 +30638,9 @@
       <c r="DK200" s="41">
         <v>152036</v>
       </c>
-      <c r="DL200" s="41"/>
+      <c r="DL200" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="201" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM201" t="s">
@@ -30691,7 +30773,9 @@
       <c r="DK202" s="41">
         <v>152038</v>
       </c>
-      <c r="DL202" s="41"/>
+      <c r="DL202" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="203" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM203" t="s">
@@ -30884,7 +30968,9 @@
       <c r="DK206" s="41">
         <v>143406</v>
       </c>
-      <c r="DL206" s="41"/>
+      <c r="DL206" s="41" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="207" spans="65:116" ht="15.75" customHeight="1">
       <c r="BM207" t="s">

--- a/calculo_mppt.xlsx
+++ b/calculo_mppt.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enzo.ferreira\Desktop\dimensionador-fotovoltaico-sigiloso\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabriel.menezes\Downloads\Repositório Dimensionamento\dimensionador-fotovoltaico-sigiloso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BCD306-FCBC-4483-9BA5-5490C348E3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65A7B0E-DF04-4014-BB68-6EC1D1385CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-4695" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MPPT" sheetId="1" r:id="rId1"/>
@@ -100,11 +100,24 @@
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="399">
   <si>
     <t>Módulo</t>
   </si>
@@ -1538,6 +1551,9 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Growatt MIN 6000TL-X</t>
   </si>
 </sst>
 </file>
@@ -1751,8 +1767,24 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFD9E2F3"/>
+          <bgColor rgb="FFD9E2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor theme="4"/>
           <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1767,37 +1799,21 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor theme="4"/>
           <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9E2F3"/>
-          <bgColor rgb="FFD9E2F3"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="MPPT-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
       <tableStyleElement type="secondRowStripe" dxfId="6"/>
     </tableStyle>
     <tableStyle name="MPPT-style 2" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="firstRowStripe" dxfId="4"/>
       <tableStyleElement type="secondRowStripe" dxfId="3"/>
     </tableStyle>
   </tableStyles>
@@ -2137,36 +2153,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:BK1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" customWidth="1"/>
-    <col min="2" max="2" width="61.28515625" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" customWidth="1"/>
-    <col min="5" max="5" width="7.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="1.7109375" customWidth="1"/>
-    <col min="12" max="12" width="39.7109375" customWidth="1"/>
-    <col min="13" max="13" width="7.140625" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" customWidth="1"/>
-    <col min="15" max="15" width="8.85546875" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="61.33203125" customWidth="1"/>
+    <col min="3" max="3" width="7.44140625" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" customWidth="1"/>
+    <col min="5" max="5" width="7.44140625" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="1.6640625" customWidth="1"/>
+    <col min="12" max="12" width="39.6640625" customWidth="1"/>
+    <col min="13" max="13" width="7.109375" customWidth="1"/>
+    <col min="14" max="14" width="11.109375" customWidth="1"/>
+    <col min="15" max="15" width="8.88671875" customWidth="1"/>
     <col min="16" max="16" width="8" customWidth="1"/>
-    <col min="17" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="7.28515625" customWidth="1"/>
-    <col min="20" max="32" width="6.7109375" customWidth="1"/>
-    <col min="33" max="34" width="8.7109375" customWidth="1"/>
-    <col min="35" max="47" width="6.7109375" customWidth="1"/>
-    <col min="48" max="48" width="8.7109375" customWidth="1"/>
-    <col min="49" max="61" width="4.28515625" customWidth="1"/>
-    <col min="62" max="63" width="8.7109375" customWidth="1"/>
+    <col min="17" max="18" width="8.6640625" customWidth="1"/>
+    <col min="19" max="19" width="7.33203125" customWidth="1"/>
+    <col min="20" max="32" width="6.6640625" customWidth="1"/>
+    <col min="33" max="34" width="8.6640625" customWidth="1"/>
+    <col min="35" max="47" width="6.6640625" customWidth="1"/>
+    <col min="48" max="48" width="8.6640625" customWidth="1"/>
+    <col min="49" max="61" width="4.33203125" customWidth="1"/>
+    <col min="62" max="63" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:63" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:63" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2351,7 +2367,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>61</v>
       </c>
@@ -2418,7 +2434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>64</v>
       </c>
@@ -2480,7 +2496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>66</v>
       </c>
@@ -2546,7 +2562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>396</v>
       </c>
@@ -2617,7 +2633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>69</v>
       </c>
@@ -2680,7 +2696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>71</v>
       </c>
@@ -2747,7 +2763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>73</v>
       </c>
@@ -2818,7 +2834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>75</v>
       </c>
@@ -2881,7 +2897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>77</v>
       </c>
@@ -2946,7 +2962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>79</v>
       </c>
@@ -3009,7 +3025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>81</v>
       </c>
@@ -3094,7 +3110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>83</v>
       </c>
@@ -3170,7 +3186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>85</v>
       </c>
@@ -3242,7 +3258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>87</v>
       </c>
@@ -3312,7 +3328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:60" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:60" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>89</v>
       </c>
@@ -3396,7 +3412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:60" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:60" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>91</v>
       </c>
@@ -3462,7 +3478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:60" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:60" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>93</v>
       </c>
@@ -3536,7 +3552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:60" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:60" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>95</v>
       </c>
@@ -3602,7 +3618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>97</v>
       </c>
@@ -3680,7 +3696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>99</v>
       </c>
@@ -3764,7 +3780,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>101</v>
       </c>
@@ -3884,7 +3900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>103</v>
       </c>
@@ -4026,7 +4042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>105</v>
       </c>
@@ -4168,7 +4184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="14" t="s">
         <v>107</v>
       </c>
@@ -4254,7 +4270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>109</v>
       </c>
@@ -4336,7 +4352,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>111</v>
       </c>
@@ -4422,7 +4438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>113</v>
       </c>
@@ -4574,7 +4590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>115</v>
       </c>
@@ -4677,7 +4693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>117</v>
       </c>
@@ -4772,7 +4788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>119</v>
       </c>
@@ -4858,7 +4874,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>121</v>
       </c>
@@ -4961,7 +4977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>123</v>
       </c>
@@ -5054,7 +5070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="14" t="s">
         <v>125</v>
       </c>
@@ -5140,7 +5156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="14" t="s">
         <v>127</v>
       </c>
@@ -5219,7 +5235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>129</v>
       </c>
@@ -5319,7 +5335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>131</v>
       </c>
@@ -5405,7 +5421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="14" t="s">
         <v>133</v>
       </c>
@@ -5492,7 +5508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="14" t="s">
         <v>135</v>
       </c>
@@ -5578,7 +5594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>137</v>
       </c>
@@ -5678,7 +5694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>139</v>
       </c>
@@ -5813,7 +5829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>141</v>
       </c>
@@ -5895,7 +5911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>143</v>
       </c>
@@ -5981,7 +5997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>145</v>
       </c>
@@ -6074,7 +6090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>147</v>
       </c>
@@ -6160,7 +6176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>149</v>
       </c>
@@ -6246,7 +6262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>151</v>
       </c>
@@ -6330,7 +6346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>153</v>
       </c>
@@ -6423,7 +6439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>155</v>
       </c>
@@ -6514,7 +6530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>157</v>
       </c>
@@ -6600,7 +6616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>159</v>
       </c>
@@ -6686,7 +6702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>161</v>
       </c>
@@ -6772,7 +6788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>163</v>
       </c>
@@ -6858,7 +6874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>165</v>
       </c>
@@ -6924,7 +6940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>167</v>
       </c>
@@ -6984,7 +7000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>169</v>
       </c>
@@ -7121,7 +7137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>171</v>
       </c>
@@ -7256,7 +7272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>173</v>
       </c>
@@ -7332,7 +7348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>175</v>
       </c>
@@ -7400,7 +7416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="14" t="s">
         <v>177</v>
       </c>
@@ -7480,7 +7496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>179</v>
       </c>
@@ -7543,7 +7559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="16" t="s">
         <v>181</v>
       </c>
@@ -7606,7 +7622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="14" t="s">
         <v>183</v>
       </c>
@@ -7690,7 +7706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="14" t="s">
         <v>185</v>
       </c>
@@ -7753,7 +7769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="14" t="s">
         <v>187</v>
       </c>
@@ -7816,7 +7832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="14" t="s">
         <v>189</v>
       </c>
@@ -7919,7 +7935,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="14" t="s">
         <v>191</v>
       </c>
@@ -8018,7 +8034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="14" t="s">
         <v>193</v>
       </c>
@@ -8081,7 +8097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="14" t="s">
         <v>195</v>
       </c>
@@ -8144,7 +8160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>197</v>
       </c>
@@ -8238,7 +8254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>199</v>
       </c>
@@ -8309,7 +8325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>201</v>
       </c>
@@ -8376,7 +8392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="14" t="s">
         <v>203</v>
       </c>
@@ -8455,7 +8471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>205</v>
       </c>
@@ -8530,7 +8546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>206</v>
       </c>
@@ -8624,7 +8640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>208</v>
       </c>
@@ -8693,7 +8709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="14" t="s">
         <v>210</v>
       </c>
@@ -8760,7 +8776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="14" t="s">
         <v>212</v>
       </c>
@@ -8858,7 +8874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
         <v>214</v>
       </c>
@@ -8929,7 +8945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="14" t="s">
         <v>216</v>
       </c>
@@ -8996,7 +9012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="14" t="s">
         <v>218</v>
       </c>
@@ -9068,7 +9084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
         <v>220</v>
       </c>
@@ -9179,7 +9195,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
         <v>222</v>
       </c>
@@ -9318,7 +9334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
         <v>224</v>
       </c>
@@ -9453,7 +9469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
         <v>226</v>
       </c>
@@ -9539,7 +9555,7 @@
       <c r="BH86" s="22"/>
       <c r="BI86" s="22"/>
     </row>
-    <row r="87" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="14" t="s">
         <v>228</v>
       </c>
@@ -9625,7 +9641,7 @@
       <c r="BH87" s="22"/>
       <c r="BI87" s="22"/>
     </row>
-    <row r="88" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
         <v>230</v>
       </c>
@@ -9685,7 +9701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
         <v>232</v>
       </c>
@@ -9751,7 +9767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
         <v>234</v>
       </c>
@@ -9817,7 +9833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="3" t="s">
         <v>236</v>
       </c>
@@ -9887,7 +9903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
         <v>238</v>
       </c>
@@ -9965,7 +9981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="14" t="s">
         <v>240</v>
       </c>
@@ -10031,7 +10047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
         <v>242</v>
       </c>
@@ -10111,7 +10127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
         <v>244</v>
       </c>
@@ -10197,7 +10213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
         <v>246</v>
       </c>
@@ -10268,7 +10284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>246</v>
       </c>
@@ -10346,7 +10362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="3" t="s">
         <v>249</v>
       </c>
@@ -10425,7 +10441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>251</v>
       </c>
@@ -10504,7 +10520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="14" t="s">
         <v>253</v>
       </c>
@@ -10590,7 +10606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="14" t="s">
         <v>255</v>
       </c>
@@ -10664,7 +10680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>257</v>
       </c>
@@ -10750,7 +10766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>259</v>
       </c>
@@ -10836,7 +10852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
         <v>261</v>
       </c>
@@ -10923,7 +10939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>263</v>
       </c>
@@ -10985,7 +11001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>265</v>
       </c>
@@ -11071,7 +11087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
         <v>267</v>
       </c>
@@ -11153,7 +11169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>269</v>
       </c>
@@ -11239,7 +11255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>271</v>
       </c>
@@ -11333,7 +11349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
         <v>273</v>
       </c>
@@ -11419,7 +11435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>275</v>
       </c>
@@ -11511,7 +11527,7 @@
       <c r="AY111" s="26"/>
       <c r="AZ111" s="26"/>
     </row>
-    <row r="112" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L112" t="s">
         <v>277</v>
       </c>
@@ -11574,7 +11590,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L113" t="s">
         <v>278</v>
       </c>
@@ -11634,7 +11650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L114" t="s">
         <v>279</v>
       </c>
@@ -11694,7 +11710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L115" t="s">
         <v>280</v>
       </c>
@@ -11754,7 +11770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L116" t="s">
         <v>281</v>
       </c>
@@ -11812,7 +11828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L117" t="s">
         <v>282</v>
       </c>
@@ -11869,7 +11885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L118" t="s">
         <v>283</v>
       </c>
@@ -11908,7 +11924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L119" t="s">
         <v>284</v>
       </c>
@@ -11959,7 +11975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L120" t="s">
         <v>285</v>
       </c>
@@ -12010,7 +12026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L121" t="s">
         <v>286</v>
       </c>
@@ -12071,7 +12087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L122" t="s">
         <v>287</v>
       </c>
@@ -12110,7 +12126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L123" t="s">
         <v>288</v>
       </c>
@@ -12177,7 +12193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L124" t="s">
         <v>289</v>
       </c>
@@ -12236,7 +12252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L125" t="s">
         <v>290</v>
       </c>
@@ -12329,7 +12345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L126" t="s">
         <v>291</v>
       </c>
@@ -12380,7 +12396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L127" t="s">
         <v>292</v>
       </c>
@@ -12443,7 +12459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B128" s="3"/>
       <c r="L128" t="s">
         <v>293</v>
@@ -12535,7 +12551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L129" t="s">
         <v>294</v>
       </c>
@@ -12668,7 +12684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L130" t="s">
         <v>295</v>
       </c>
@@ -12738,7 +12754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L131" t="s">
         <v>296</v>
       </c>
@@ -12781,7 +12797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L132" t="s">
         <v>297</v>
       </c>
@@ -12835,7 +12851,7 @@
       <c r="BH132" s="22"/>
       <c r="BI132" s="22"/>
     </row>
-    <row r="133" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L133" t="s">
         <v>298</v>
       </c>
@@ -12878,7 +12894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L134" t="s">
         <v>299</v>
       </c>
@@ -12921,7 +12937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L135" t="s">
         <v>300</v>
       </c>
@@ -13004,7 +13020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L136" t="s">
         <v>301</v>
       </c>
@@ -13047,7 +13063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L137" t="s">
         <v>302</v>
       </c>
@@ -13090,7 +13106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L138" t="s">
         <v>303</v>
       </c>
@@ -13133,7 +13149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L139" t="s">
         <v>304</v>
       </c>
@@ -13181,7 +13197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L140" t="s">
         <v>305</v>
       </c>
@@ -13223,7 +13239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L141" t="s">
         <v>306</v>
       </c>
@@ -13346,7 +13362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L142" t="s">
         <v>307</v>
       </c>
@@ -13451,7 +13467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L143" t="s">
         <v>308</v>
       </c>
@@ -13480,7 +13496,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L144" t="s">
         <v>309</v>
       </c>
@@ -13543,7 +13559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L145" t="s">
         <v>310</v>
       </c>
@@ -13607,7 +13623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L146" t="s">
         <v>311</v>
       </c>
@@ -13649,7 +13665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L147" t="s">
         <v>312</v>
       </c>
@@ -13719,7 +13735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L148" t="s">
         <v>313</v>
       </c>
@@ -13789,7 +13805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L149" t="s">
         <v>314</v>
       </c>
@@ -13866,7 +13882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L150" t="s">
         <v>315</v>
       </c>
@@ -13943,7 +13959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L151" t="s">
         <v>316</v>
       </c>
@@ -14055,7 +14071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L152" t="s">
         <v>317</v>
       </c>
@@ -14150,7 +14166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L153" t="s">
         <v>318</v>
       </c>
@@ -14242,7 +14258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L154" t="s">
         <v>319</v>
       </c>
@@ -14312,7 +14328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L155" t="s">
         <v>320</v>
       </c>
@@ -14394,7 +14410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L156" t="s">
         <v>321</v>
       </c>
@@ -14472,7 +14488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L157" t="s">
         <v>322</v>
       </c>
@@ -14568,7 +14584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L158" t="s">
         <v>323</v>
       </c>
@@ -14660,7 +14676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L159" t="s">
         <v>324</v>
       </c>
@@ -14707,7 +14723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L160" t="s">
         <v>325</v>
       </c>
@@ -14763,7 +14779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L161" t="s">
         <v>326</v>
       </c>
@@ -14828,7 +14844,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L162" t="s">
         <v>327</v>
       </c>
@@ -14866,7 +14882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L163" t="s">
         <v>328</v>
       </c>
@@ -14980,7 +14996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L164" t="s">
         <v>329</v>
       </c>
@@ -15072,7 +15088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L165" t="s">
         <v>330</v>
       </c>
@@ -15135,7 +15151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L166" t="s">
         <v>331</v>
       </c>
@@ -15177,7 +15193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L167" t="s">
         <v>332</v>
       </c>
@@ -15240,7 +15256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L168" t="s">
         <v>333</v>
       </c>
@@ -15339,7 +15355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L169" t="s">
         <v>334</v>
       </c>
@@ -15432,7 +15448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L170" t="s">
         <v>335</v>
       </c>
@@ -15537,7 +15553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L171" t="s">
         <v>336</v>
       </c>
@@ -15630,7 +15646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L172" t="s">
         <v>337</v>
       </c>
@@ -15711,7 +15727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L173" t="s">
         <v>338</v>
       </c>
@@ -15786,7 +15802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L174" t="s">
         <v>339</v>
       </c>
@@ -15825,7 +15841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L175" t="s">
         <v>340</v>
       </c>
@@ -15889,7 +15905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L176" t="s">
         <v>341</v>
       </c>
@@ -15957,7 +15973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L177" t="s">
         <v>342</v>
       </c>
@@ -16007,7 +16023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L178" t="s">
         <v>343</v>
       </c>
@@ -16071,7 +16087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L179" t="s">
         <v>344</v>
       </c>
@@ -16139,7 +16155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L180" t="s">
         <v>345</v>
       </c>
@@ -16214,7 +16230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L181" t="s">
         <v>346</v>
       </c>
@@ -16280,7 +16296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L182" t="s">
         <v>347</v>
       </c>
@@ -16344,7 +16360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L183" t="s">
         <v>348</v>
       </c>
@@ -16415,7 +16431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L184" t="s">
         <v>349</v>
       </c>
@@ -16490,7 +16506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L185" t="s">
         <v>350</v>
       </c>
@@ -16568,7 +16584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L186" t="s">
         <v>351</v>
       </c>
@@ -16620,7 +16636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L187" t="s">
         <v>352</v>
       </c>
@@ -16679,7 +16695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L188" t="s">
         <v>353</v>
       </c>
@@ -16761,7 +16777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L189" t="s">
         <v>354</v>
       </c>
@@ -16843,7 +16859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L190" t="s">
         <v>355</v>
       </c>
@@ -16907,7 +16923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L191" t="s">
         <v>356</v>
       </c>
@@ -16979,7 +16995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L192" t="s">
         <v>357</v>
       </c>
@@ -17043,7 +17059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L193" t="s">
         <v>358</v>
       </c>
@@ -17132,7 +17148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L194" t="s">
         <v>359</v>
       </c>
@@ -17202,7 +17218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L195" t="s">
         <v>360</v>
       </c>
@@ -17264,7 +17280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L196" t="s">
         <v>361</v>
       </c>
@@ -17335,7 +17351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L197" t="s">
         <v>362</v>
       </c>
@@ -17409,7 +17425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L198" t="s">
         <v>363</v>
       </c>
@@ -17533,7 +17549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L199" t="s">
         <v>364</v>
       </c>
@@ -17583,7 +17599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L200" t="s">
         <v>365</v>
       </c>
@@ -17626,7 +17642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L201" t="s">
         <v>366</v>
       </c>
@@ -17693,7 +17709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L202" t="s">
         <v>367</v>
       </c>
@@ -17761,7 +17777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L203" t="s">
         <v>368</v>
       </c>
@@ -17811,7 +17827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L204" t="s">
         <v>369</v>
       </c>
@@ -17879,7 +17895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L205" t="s">
         <v>370</v>
       </c>
@@ -17917,7 +17933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L206" t="s">
         <v>371</v>
       </c>
@@ -17960,7 +17976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L207" t="s">
         <v>372</v>
       </c>
@@ -18039,7 +18055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L208" t="s">
         <v>373</v>
       </c>
@@ -18149,7 +18165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L209" t="s">
         <v>374</v>
       </c>
@@ -18245,7 +18261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L210" t="s">
         <v>375</v>
       </c>
@@ -18295,7 +18311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L211" t="s">
         <v>376</v>
       </c>
@@ -18346,7 +18362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L212" t="s">
         <v>377</v>
       </c>
@@ -18462,7 +18478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L213" t="s">
         <v>378</v>
       </c>
@@ -18590,7 +18606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L214" t="s">
         <v>379</v>
       </c>
@@ -18632,7 +18648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L215" t="s">
         <v>380</v>
       </c>
@@ -18674,7 +18690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L216" t="s">
         <v>381</v>
       </c>
@@ -18716,7 +18732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L217" t="s">
         <v>382</v>
       </c>
@@ -18850,7 +18866,7 @@
       </c>
       <c r="BI217" s="22"/>
     </row>
-    <row r="218" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L218" t="s">
         <v>383</v>
       </c>
@@ -18893,7 +18909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L219" t="s">
         <v>384</v>
       </c>
@@ -18944,7 +18960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L220" t="s">
         <v>385</v>
       </c>
@@ -18995,7 +19011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L221" t="s">
         <v>386</v>
       </c>
@@ -19129,7 +19145,7 @@
       </c>
       <c r="BI221" s="22"/>
     </row>
-    <row r="222" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L222" t="s">
         <v>387</v>
       </c>
@@ -19263,7 +19279,7 @@
       </c>
       <c r="BI222" s="22"/>
     </row>
-    <row r="223" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L223" t="s">
         <v>388</v>
       </c>
@@ -19323,7 +19339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L224" t="s">
         <v>389</v>
       </c>
@@ -19382,7 +19398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L225" t="s">
         <v>390</v>
       </c>
@@ -19424,7 +19440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L226" t="s">
         <v>391</v>
       </c>
@@ -19516,7 +19532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L227" t="s">
         <v>392</v>
       </c>
@@ -19558,7 +19574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L228" t="s">
         <v>393</v>
       </c>
@@ -19609,7 +19625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L229" t="s">
         <v>394</v>
       </c>
@@ -19725,7 +19741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L230" t="s">
         <v>395</v>
       </c>
@@ -19818,971 +19834,1005 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L231" t="s">
+        <v>398</v>
+      </c>
+      <c r="M231">
+        <v>6</v>
+      </c>
+      <c r="N231">
+        <f>Table_2[[#This Row],[Pnom]]*1.35</f>
+        <v>8.1000000000000014</v>
+      </c>
+      <c r="O231">
+        <v>550</v>
+      </c>
+      <c r="P231">
+        <v>100</v>
+      </c>
       <c r="Q231" s="4"/>
       <c r="R231" s="4"/>
-    </row>
-    <row r="232" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S231">
+        <v>16</v>
+      </c>
+      <c r="T231">
+        <v>16</v>
+      </c>
+      <c r="AH231">
+        <v>12.5</v>
+      </c>
+      <c r="AI231">
+        <v>12.5</v>
+      </c>
+      <c r="AW231">
+        <v>1</v>
+      </c>
+      <c r="AX231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q232" s="15"/>
       <c r="R232" s="15"/>
     </row>
-    <row r="233" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q233" s="4"/>
       <c r="R233" s="4"/>
     </row>
-    <row r="234" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q234" s="15"/>
       <c r="R234" s="15"/>
     </row>
-    <row r="235" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q235" s="4"/>
       <c r="R235" s="4"/>
     </row>
-    <row r="236" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q236" s="15"/>
       <c r="R236" s="15"/>
     </row>
-    <row r="237" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q237" s="4"/>
       <c r="R237" s="4"/>
     </row>
-    <row r="238" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q238" s="15"/>
       <c r="R238" s="15"/>
     </row>
-    <row r="239" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q239" s="4"/>
       <c r="R239" s="4"/>
     </row>
-    <row r="240" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q240" s="15"/>
       <c r="R240" s="15"/>
     </row>
-    <row r="241" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q241" s="4"/>
       <c r="R241" s="4"/>
     </row>
-    <row r="242" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q242" s="15"/>
       <c r="R242" s="15"/>
     </row>
-    <row r="243" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q243" s="4"/>
       <c r="R243" s="4"/>
     </row>
-    <row r="244" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q244" s="15"/>
       <c r="R244" s="15"/>
     </row>
-    <row r="245" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q245" s="4"/>
       <c r="R245" s="4"/>
     </row>
-    <row r="246" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q246" s="15"/>
       <c r="R246" s="15"/>
     </row>
-    <row r="247" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q247" s="4"/>
       <c r="R247" s="4"/>
     </row>
-    <row r="248" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q248" s="15"/>
       <c r="R248" s="15"/>
     </row>
-    <row r="249" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q249" s="4"/>
       <c r="R249" s="4"/>
     </row>
-    <row r="250" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q250" s="15"/>
       <c r="R250" s="15"/>
     </row>
-    <row r="251" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q251" s="4"/>
       <c r="R251" s="4"/>
     </row>
-    <row r="252" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q252" s="15"/>
       <c r="R252" s="15"/>
     </row>
-    <row r="253" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q253" s="4"/>
       <c r="R253" s="4"/>
     </row>
-    <row r="254" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q254" s="15"/>
       <c r="R254" s="15"/>
     </row>
-    <row r="255" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q255" s="4"/>
       <c r="R255" s="4"/>
     </row>
-    <row r="256" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q256" s="15"/>
       <c r="R256" s="15"/>
     </row>
-    <row r="257" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q257" s="4"/>
       <c r="R257" s="4"/>
     </row>
-    <row r="258" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q258" s="15"/>
       <c r="R258" s="15"/>
     </row>
-    <row r="259" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q259" s="4"/>
       <c r="R259" s="4"/>
     </row>
-    <row r="260" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q260" s="15"/>
       <c r="R260" s="15"/>
     </row>
-    <row r="261" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q261" s="4"/>
       <c r="R261" s="4"/>
     </row>
-    <row r="262" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q262" s="15"/>
       <c r="R262" s="15"/>
     </row>
-    <row r="263" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q263" s="4"/>
       <c r="R263" s="4"/>
     </row>
-    <row r="264" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q264" s="15"/>
       <c r="R264" s="15"/>
     </row>
-    <row r="265" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q265" s="4"/>
       <c r="R265" s="4"/>
     </row>
-    <row r="266" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q266" s="15"/>
       <c r="R266" s="15"/>
     </row>
-    <row r="267" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q267" s="4"/>
       <c r="R267" s="4"/>
     </row>
-    <row r="268" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q268" s="15"/>
       <c r="R268" s="15"/>
     </row>
-    <row r="269" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q269" s="4"/>
       <c r="R269" s="4"/>
     </row>
-    <row r="270" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q270" s="15"/>
       <c r="R270" s="15"/>
     </row>
-    <row r="271" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q271" s="4"/>
       <c r="R271" s="4"/>
     </row>
-    <row r="272" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q272" s="15"/>
       <c r="R272" s="15"/>
     </row>
-    <row r="273" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q273" s="4"/>
       <c r="R273" s="4"/>
     </row>
-    <row r="274" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q274" s="15"/>
       <c r="R274" s="15"/>
     </row>
-    <row r="275" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q275" s="4"/>
       <c r="R275" s="4"/>
     </row>
-    <row r="276" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q276" s="15"/>
       <c r="R276" s="15"/>
     </row>
-    <row r="277" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q277" s="4"/>
       <c r="R277" s="4"/>
     </row>
-    <row r="278" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q278" s="15"/>
       <c r="R278" s="15"/>
     </row>
-    <row r="279" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q279" s="4"/>
       <c r="R279" s="4"/>
     </row>
-    <row r="280" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q280" s="15"/>
       <c r="R280" s="15"/>
     </row>
-    <row r="281" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q281" s="4"/>
       <c r="R281" s="4"/>
     </row>
-    <row r="282" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q282" s="15"/>
       <c r="R282" s="15"/>
     </row>
-    <row r="283" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q283" s="4"/>
       <c r="R283" s="4"/>
     </row>
-    <row r="284" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q284" s="15"/>
       <c r="R284" s="15"/>
     </row>
-    <row r="285" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q285" s="4"/>
       <c r="R285" s="4"/>
     </row>
-    <row r="286" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q286" s="15"/>
       <c r="R286" s="15"/>
     </row>
-    <row r="287" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q287" s="4"/>
       <c r="R287" s="4"/>
     </row>
-    <row r="288" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q288" s="15"/>
       <c r="R288" s="15"/>
     </row>
-    <row r="289" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q289" s="4"/>
       <c r="R289" s="4"/>
     </row>
-    <row r="290" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q290" s="15"/>
       <c r="R290" s="15"/>
     </row>
-    <row r="291" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q291" s="4"/>
       <c r="R291" s="4"/>
     </row>
-    <row r="292" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q292" s="15"/>
       <c r="R292" s="15"/>
     </row>
-    <row r="293" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q293" s="4"/>
       <c r="R293" s="4"/>
     </row>
-    <row r="294" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q294" s="15"/>
       <c r="R294" s="15"/>
     </row>
-    <row r="295" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q295" s="4"/>
       <c r="R295" s="4"/>
     </row>
-    <row r="296" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="G3:G208">
     <cfRule type="colorScale" priority="29">

--- a/calculo_mppt.xlsx
+++ b/calculo_mppt.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enzo.ferreira\Desktop\dimensionador-fotovoltaico-sigiloso\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabriel.menezes\Downloads\Repositório Dimensionamento\dimensionador-fotovoltaico-sigiloso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26676448-8BF2-481B-8D7A-14B5F5AE1981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F934BB4-052B-4299-84D2-A24C1B034FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-4695" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MPPT" sheetId="1" r:id="rId1"/>
@@ -100,11 +100,24 @@
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="399">
   <si>
     <t>Módulo</t>
   </si>
@@ -603,6 +616,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-100KTL-M2 </t>
     </r>
@@ -612,6 +626,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -631,6 +646,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-10K-LCO </t>
     </r>
@@ -640,6 +656,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -665,6 +682,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-15KTL-M5 </t>
     </r>
@@ -674,6 +692,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -699,6 +718,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-20KTL-M5 </t>
     </r>
@@ -708,6 +728,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -727,6 +748,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-250KTL-H1 </t>
     </r>
@@ -736,6 +758,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -755,6 +778,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-25KTL-M5 </t>
     </r>
@@ -764,6 +788,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -789,6 +814,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-3KTL-L1 </t>
     </r>
@@ -798,6 +824,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -832,6 +859,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-5KTL-L1 </t>
     </r>
@@ -841,6 +869,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -866,6 +895,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-6KTL-L1 </t>
     </r>
@@ -875,6 +905,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -906,6 +937,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-75KTL-M1 </t>
     </r>
@@ -915,6 +947,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -934,6 +967,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-8K-LCO </t>
     </r>
@@ -943,6 +977,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -1214,6 +1249,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Solis 75K 5G-PRO </t>
     </r>
@@ -1223,6 +1259,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>com 50%</t>
     </r>
@@ -1239,6 +1276,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Solis S5-GC 37,5K </t>
     </r>
@@ -1248,6 +1286,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>com 50%</t>
     </r>
@@ -1261,6 +1300,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Solis S5-GC 60K </t>
     </r>
@@ -1270,6 +1310,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>com 50%</t>
     </r>
@@ -1316,6 +1357,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Solis-75K-LV-5G-PRO </t>
     </r>
@@ -1325,6 +1367,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(C/ CONECTOR "Y")</t>
     </r>
@@ -1547,7 +1590,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1556,24 +1599,35 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color indexed="65"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="2"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1666,59 +1720,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2145,36 +2195,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:BK1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" customWidth="1"/>
-    <col min="2" max="2" width="61.28515625" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" customWidth="1"/>
-    <col min="5" max="5" width="7.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="1.7109375" customWidth="1"/>
-    <col min="12" max="12" width="39.7109375" customWidth="1"/>
-    <col min="13" max="13" width="7.140625" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" customWidth="1"/>
-    <col min="15" max="15" width="8.85546875" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="61.33203125" customWidth="1"/>
+    <col min="3" max="3" width="7.44140625" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" customWidth="1"/>
+    <col min="5" max="5" width="7.44140625" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="1.6640625" customWidth="1"/>
+    <col min="12" max="12" width="39.6640625" customWidth="1"/>
+    <col min="13" max="13" width="7.109375" customWidth="1"/>
+    <col min="14" max="14" width="11.109375" customWidth="1"/>
+    <col min="15" max="15" width="8.88671875" customWidth="1"/>
     <col min="16" max="16" width="8" customWidth="1"/>
-    <col min="17" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="7.28515625" customWidth="1"/>
-    <col min="20" max="32" width="6.7109375" customWidth="1"/>
-    <col min="33" max="34" width="8.7109375" customWidth="1"/>
-    <col min="35" max="47" width="6.7109375" customWidth="1"/>
-    <col min="48" max="48" width="8.7109375" customWidth="1"/>
-    <col min="49" max="61" width="4.28515625" customWidth="1"/>
-    <col min="62" max="63" width="8.7109375" customWidth="1"/>
+    <col min="17" max="18" width="8.6640625" customWidth="1"/>
+    <col min="19" max="19" width="7.33203125" customWidth="1"/>
+    <col min="20" max="32" width="6.6640625" customWidth="1"/>
+    <col min="33" max="34" width="8.6640625" customWidth="1"/>
+    <col min="35" max="47" width="6.6640625" customWidth="1"/>
+    <col min="48" max="48" width="8.6640625" customWidth="1"/>
+    <col min="49" max="61" width="4.33203125" customWidth="1"/>
+    <col min="62" max="63" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:63" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:63" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2359,7 +2409,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>390</v>
       </c>
@@ -2426,7 +2476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>391</v>
       </c>
@@ -2488,7 +2538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>263</v>
       </c>
@@ -2554,7 +2604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>77</v>
       </c>
@@ -2621,7 +2671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>79</v>
       </c>
@@ -2684,7 +2734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>81</v>
       </c>
@@ -2751,7 +2801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>83</v>
       </c>
@@ -2818,7 +2868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>85</v>
       </c>
@@ -2881,7 +2931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>87</v>
       </c>
@@ -2948,7 +2998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>89</v>
       </c>
@@ -3011,7 +3061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>91</v>
       </c>
@@ -3096,7 +3146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>93</v>
       </c>
@@ -3172,7 +3222,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>95</v>
       </c>
@@ -3244,7 +3294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:63" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>97</v>
       </c>
@@ -3314,7 +3364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:60" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:60" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B17" s="14" t="s">
         <v>99</v>
       </c>
@@ -3398,7 +3448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:60" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:60" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>101</v>
       </c>
@@ -3460,7 +3510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:60" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:60" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>103</v>
       </c>
@@ -3534,7 +3584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:60" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:60" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>105</v>
       </c>
@@ -3600,7 +3650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>107</v>
       </c>
@@ -3678,7 +3728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>109</v>
       </c>
@@ -3762,7 +3812,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>392</v>
       </c>
@@ -3882,7 +3932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>111</v>
       </c>
@@ -4024,7 +4074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>113</v>
       </c>
@@ -4166,7 +4216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>115</v>
       </c>
@@ -4252,7 +4302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="14" t="s">
         <v>117</v>
       </c>
@@ -4338,7 +4388,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="14" t="s">
         <v>119</v>
       </c>
@@ -4424,7 +4474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>121</v>
       </c>
@@ -4576,7 +4626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>123</v>
       </c>
@@ -4679,7 +4729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="14" t="s">
         <v>125</v>
       </c>
@@ -4774,7 +4824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="14" t="s">
         <v>127</v>
       </c>
@@ -4860,7 +4910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>129</v>
       </c>
@@ -4963,7 +5013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>131</v>
       </c>
@@ -5054,7 +5104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>393</v>
       </c>
@@ -5144,7 +5194,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>133</v>
       </c>
@@ -5219,7 +5269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>135</v>
       </c>
@@ -5319,7 +5369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>137</v>
       </c>
@@ -5405,7 +5455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>139</v>
       </c>
@@ -5441,7 +5491,7 @@
       <c r="O39">
         <v>600</v>
       </c>
-      <c r="P39" s="30">
+      <c r="P39">
         <v>110</v>
       </c>
       <c r="Q39" s="4"/>
@@ -5492,7 +5542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>141</v>
       </c>
@@ -5528,7 +5578,7 @@
       <c r="O40">
         <v>600</v>
       </c>
-      <c r="P40" s="30">
+      <c r="P40">
         <v>110</v>
       </c>
       <c r="Q40" s="7"/>
@@ -5552,7 +5602,7 @@
       <c r="AE40" s="11"/>
       <c r="AF40" s="11"/>
       <c r="AG40" s="12"/>
-      <c r="AH40" s="31">
+      <c r="AH40" s="11">
         <v>12</v>
       </c>
       <c r="AI40" s="11">
@@ -5578,7 +5628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>394</v>
       </c>
@@ -5614,7 +5664,7 @@
       <c r="O41">
         <v>1100</v>
       </c>
-      <c r="P41" s="30">
+      <c r="P41">
         <v>526</v>
       </c>
       <c r="Q41" s="4"/>
@@ -5642,7 +5692,7 @@
       <c r="AE41" s="11"/>
       <c r="AF41" s="11"/>
       <c r="AG41" s="12"/>
-      <c r="AH41" s="31">
+      <c r="AH41" s="11">
         <v>28.5</v>
       </c>
       <c r="AI41" s="11">
@@ -5678,7 +5728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>265</v>
       </c>
@@ -5718,7 +5768,7 @@
       <c r="O42">
         <v>1100</v>
       </c>
-      <c r="P42" s="30">
+      <c r="P42">
         <v>195</v>
       </c>
       <c r="Q42" s="15"/>
@@ -5756,7 +5806,7 @@
       <c r="AE42" s="11"/>
       <c r="AF42" s="11"/>
       <c r="AG42" s="12"/>
-      <c r="AH42" s="31">
+      <c r="AH42" s="11">
         <v>26</v>
       </c>
       <c r="AI42" s="11">
@@ -5791,16 +5841,16 @@
       <c r="AT42" s="11"/>
       <c r="AU42" s="11"/>
       <c r="AV42" s="12"/>
-      <c r="AW42" s="30">
-        <v>2</v>
-      </c>
-      <c r="AX42" s="30">
-        <v>2</v>
-      </c>
-      <c r="AY42" s="30">
-        <v>2</v>
-      </c>
-      <c r="AZ42" s="30">
+      <c r="AW42">
+        <v>2</v>
+      </c>
+      <c r="AX42">
+        <v>2</v>
+      </c>
+      <c r="AY42">
+        <v>2</v>
+      </c>
+      <c r="AZ42">
         <v>2</v>
       </c>
       <c r="BA42">
@@ -5819,7 +5869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>143</v>
       </c>
@@ -5903,7 +5953,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>145</v>
       </c>
@@ -5989,7 +6039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>147</v>
       </c>
@@ -6080,7 +6130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>149</v>
       </c>
@@ -6116,7 +6166,7 @@
       <c r="O46">
         <v>600</v>
       </c>
-      <c r="P46" s="30">
+      <c r="P46">
         <v>120</v>
       </c>
       <c r="Q46" s="7"/>
@@ -6140,7 +6190,7 @@
       <c r="AE46" s="11"/>
       <c r="AF46" s="11"/>
       <c r="AG46" s="12"/>
-      <c r="AH46" s="31">
+      <c r="AH46" s="11">
         <v>12.5</v>
       </c>
       <c r="AI46" s="11">
@@ -6166,7 +6216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>151</v>
       </c>
@@ -6202,7 +6252,7 @@
       <c r="O47">
         <v>600</v>
       </c>
-      <c r="P47" s="30">
+      <c r="P47">
         <v>100</v>
       </c>
       <c r="Q47" s="4"/>
@@ -6226,7 +6276,7 @@
       <c r="AE47" s="11"/>
       <c r="AF47" s="11"/>
       <c r="AG47" s="12"/>
-      <c r="AH47" s="31">
+      <c r="AH47" s="11">
         <v>13</v>
       </c>
       <c r="AI47" s="11">
@@ -6252,7 +6302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>153</v>
       </c>
@@ -6338,7 +6388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>155</v>
       </c>
@@ -6431,7 +6481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>157</v>
       </c>
@@ -6524,7 +6574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>159</v>
       </c>
@@ -6608,7 +6658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>161</v>
       </c>
@@ -6692,7 +6742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>163</v>
       </c>
@@ -6778,7 +6828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>165</v>
       </c>
@@ -6838,7 +6888,7 @@
       <c r="AE54" s="11"/>
       <c r="AF54" s="11"/>
       <c r="AG54" s="12"/>
-      <c r="AH54" s="31">
+      <c r="AH54" s="11">
         <v>12.5</v>
       </c>
       <c r="AI54" s="11">
@@ -6864,7 +6914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>167</v>
       </c>
@@ -6923,7 +6973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="14" t="s">
         <v>169</v>
       </c>
@@ -6989,7 +7039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>171</v>
       </c>
@@ -7051,7 +7101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="16" t="s">
         <v>173</v>
       </c>
@@ -7190,7 +7240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="14" t="s">
         <v>175</v>
       </c>
@@ -7325,7 +7375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="14" t="s">
         <v>177</v>
       </c>
@@ -7401,7 +7451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="14" t="s">
         <v>179</v>
       </c>
@@ -7473,7 +7523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="14" t="s">
         <v>181</v>
       </c>
@@ -7553,7 +7603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="14" t="s">
         <v>183</v>
       </c>
@@ -7616,7 +7666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="14" t="s">
         <v>185</v>
       </c>
@@ -7665,7 +7715,7 @@
         <v>40</v>
       </c>
       <c r="AG64" s="9"/>
-      <c r="AH64" s="30">
+      <c r="AH64">
         <v>30</v>
       </c>
       <c r="AI64">
@@ -7679,7 +7729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="14" t="s">
         <v>187</v>
       </c>
@@ -7763,7 +7813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>189</v>
       </c>
@@ -7812,7 +7862,7 @@
         <v>40</v>
       </c>
       <c r="AG66" s="9"/>
-      <c r="AH66" s="30">
+      <c r="AH66">
         <v>30</v>
       </c>
       <c r="AI66">
@@ -7826,7 +7876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>191</v>
       </c>
@@ -7875,7 +7925,7 @@
         <v>40</v>
       </c>
       <c r="AG67" s="9"/>
-      <c r="AH67" s="30">
+      <c r="AH67">
         <v>30</v>
       </c>
       <c r="AI67">
@@ -7889,7 +7939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>193</v>
       </c>
@@ -7992,7 +8042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="14" t="s">
         <v>195</v>
       </c>
@@ -8029,7 +8079,7 @@
       <c r="O69">
         <v>1500</v>
       </c>
-      <c r="P69" s="30">
+      <c r="P69">
         <v>550</v>
       </c>
       <c r="Q69" s="7"/>
@@ -8053,7 +8103,7 @@
         <v>115</v>
       </c>
       <c r="AG69" s="9"/>
-      <c r="AH69" s="30">
+      <c r="AH69">
         <v>65</v>
       </c>
       <c r="AI69">
@@ -8091,7 +8141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>197</v>
       </c>
@@ -8140,7 +8190,7 @@
         <v>40</v>
       </c>
       <c r="AG70" s="9"/>
-      <c r="AH70" s="30">
+      <c r="AH70">
         <v>30</v>
       </c>
       <c r="AI70">
@@ -8154,7 +8204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>198</v>
       </c>
@@ -8217,7 +8267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>200</v>
       </c>
@@ -8309,7 +8359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="14" t="s">
         <v>202</v>
       </c>
@@ -8380,7 +8430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="14" t="s">
         <v>204</v>
       </c>
@@ -8447,7 +8497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>206</v>
       </c>
@@ -8526,7 +8576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="14" t="s">
         <v>208</v>
       </c>
@@ -8601,7 +8651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="14" t="s">
         <v>210</v>
       </c>
@@ -8695,7 +8745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>212</v>
       </c>
@@ -8766,7 +8816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>214</v>
       </c>
@@ -8833,7 +8883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
         <v>216</v>
       </c>
@@ -8931,7 +8981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
         <v>218</v>
       </c>
@@ -9002,7 +9052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
         <v>389</v>
       </c>
@@ -9043,7 +9093,7 @@
       <c r="O82">
         <v>600</v>
       </c>
-      <c r="P82" s="30">
+      <c r="P82">
         <v>100</v>
       </c>
       <c r="Q82" s="4"/>
@@ -9059,18 +9109,12 @@
       <c r="AE82" s="20"/>
       <c r="AF82" s="20"/>
       <c r="AG82" s="21"/>
-      <c r="AH82" s="30">
+      <c r="AH82">
         <v>13.5</v>
       </c>
-      <c r="AI82" s="30">
+      <c r="AI82">
         <v>13.5</v>
       </c>
-      <c r="AJ82" s="30"/>
-      <c r="AK82" s="30"/>
-      <c r="AL82" s="30"/>
-      <c r="AM82" s="30"/>
-      <c r="AN82" s="30"/>
-      <c r="AO82" s="30"/>
       <c r="AV82" s="9"/>
       <c r="AW82">
         <v>1</v>
@@ -9079,7 +9123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="14" t="s">
         <v>220</v>
       </c>
@@ -9116,7 +9160,7 @@
       <c r="O83">
         <v>600</v>
       </c>
-      <c r="P83" s="30">
+      <c r="P83">
         <v>50</v>
       </c>
       <c r="Q83" s="7"/>
@@ -9131,7 +9175,7 @@
         <v>20</v>
       </c>
       <c r="AG83" s="6"/>
-      <c r="AH83" s="30">
+      <c r="AH83">
         <v>16</v>
       </c>
       <c r="AI83">
@@ -9151,7 +9195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
         <v>222</v>
       </c>
@@ -9262,7 +9306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
         <v>224</v>
       </c>
@@ -9401,7 +9445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
         <v>226</v>
       </c>
@@ -9438,7 +9482,7 @@
       <c r="O86">
         <v>1100</v>
       </c>
-      <c r="P86" s="30">
+      <c r="P86">
         <v>540</v>
       </c>
       <c r="Q86" s="4"/>
@@ -9474,7 +9518,7 @@
         <v>40</v>
       </c>
       <c r="AG86" s="9"/>
-      <c r="AH86" s="30">
+      <c r="AH86">
         <v>26</v>
       </c>
       <c r="AI86">
@@ -9536,7 +9580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="3" t="s">
         <v>228</v>
       </c>
@@ -9577,7 +9621,7 @@
       <c r="O87">
         <v>600</v>
       </c>
-      <c r="P87" s="30">
+      <c r="P87">
         <v>260</v>
       </c>
       <c r="Q87" s="7"/>
@@ -9596,7 +9640,7 @@
       <c r="AE87" s="11"/>
       <c r="AF87" s="11"/>
       <c r="AG87" s="12"/>
-      <c r="AH87" s="30">
+      <c r="AH87">
         <v>15</v>
       </c>
       <c r="AI87">
@@ -9626,7 +9670,7 @@
       <c r="BH87" s="22"/>
       <c r="BI87" s="22"/>
     </row>
-    <row r="88" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
         <v>395</v>
       </c>
@@ -9663,7 +9707,7 @@
       <c r="O88">
         <v>600</v>
       </c>
-      <c r="P88" s="30">
+      <c r="P88">
         <v>260</v>
       </c>
       <c r="Q88" s="4"/>
@@ -9682,7 +9726,7 @@
       <c r="AE88" s="11"/>
       <c r="AF88" s="11"/>
       <c r="AG88" s="12"/>
-      <c r="AH88" s="30">
+      <c r="AH88">
         <v>15</v>
       </c>
       <c r="AI88">
@@ -9712,7 +9756,7 @@
       <c r="BH88" s="22"/>
       <c r="BI88" s="22"/>
     </row>
-    <row r="89" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="3" t="s">
         <v>396</v>
       </c>
@@ -9776,7 +9820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
         <v>230</v>
       </c>
@@ -9842,7 +9886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="14" t="s">
         <v>232</v>
       </c>
@@ -9908,7 +9952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
         <v>234</v>
       </c>
@@ -9974,7 +10018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
         <v>236</v>
       </c>
@@ -10052,7 +10096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
         <v>238</v>
       </c>
@@ -10118,7 +10162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
         <v>238</v>
       </c>
@@ -10153,7 +10197,7 @@
       <c r="O95">
         <v>550</v>
       </c>
-      <c r="P95" s="30">
+      <c r="P95">
         <v>70</v>
       </c>
       <c r="Q95" s="7"/>
@@ -10175,16 +10219,16 @@
       <c r="AE95" s="11"/>
       <c r="AF95" s="11"/>
       <c r="AG95" s="12"/>
-      <c r="AH95" s="31">
+      <c r="AH95" s="11">
         <v>14</v>
       </c>
-      <c r="AI95" s="31"/>
-      <c r="AJ95" s="31"/>
-      <c r="AK95" s="31"/>
-      <c r="AL95" s="31"/>
-      <c r="AM95" s="31"/>
-      <c r="AN95" s="31"/>
-      <c r="AO95" s="31"/>
+      <c r="AI95" s="11"/>
+      <c r="AJ95" s="11"/>
+      <c r="AK95" s="11"/>
+      <c r="AL95" s="11"/>
+      <c r="AM95" s="11"/>
+      <c r="AN95" s="11"/>
+      <c r="AO95" s="11"/>
       <c r="AP95" s="11"/>
       <c r="AQ95" s="11"/>
       <c r="AR95" s="11"/>
@@ -10196,7 +10240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="3" t="s">
         <v>241</v>
       </c>
@@ -10232,7 +10276,7 @@
       <c r="O96">
         <v>550</v>
       </c>
-      <c r="P96" s="30">
+      <c r="P96">
         <v>90</v>
       </c>
       <c r="Q96" s="4"/>
@@ -10256,7 +10300,7 @@
       <c r="AE96" s="11"/>
       <c r="AF96" s="11"/>
       <c r="AG96" s="12"/>
-      <c r="AH96" s="31">
+      <c r="AH96" s="11">
         <v>26</v>
       </c>
       <c r="AI96" s="11">
@@ -10282,7 +10326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>397</v>
       </c>
@@ -10318,7 +10362,7 @@
       <c r="O97">
         <v>600</v>
       </c>
-      <c r="P97" s="30">
+      <c r="P97">
         <v>90</v>
       </c>
       <c r="Q97" s="7"/>
@@ -10333,7 +10377,7 @@
         <v>20</v>
       </c>
       <c r="AG97" s="9"/>
-      <c r="AH97" s="30">
+      <c r="AH97">
         <v>16</v>
       </c>
       <c r="AI97">
@@ -10353,7 +10397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>243</v>
       </c>
@@ -10390,7 +10434,7 @@
       <c r="O98">
         <v>550</v>
       </c>
-      <c r="P98" s="30">
+      <c r="P98">
         <v>70</v>
       </c>
       <c r="Q98" s="10"/>
@@ -10412,7 +10456,7 @@
       <c r="AE98" s="11"/>
       <c r="AF98" s="11"/>
       <c r="AG98" s="12"/>
-      <c r="AH98" s="31">
+      <c r="AH98" s="11">
         <v>14</v>
       </c>
       <c r="AI98" s="11"/>
@@ -10433,7 +10477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="14" t="s">
         <v>245</v>
       </c>
@@ -10469,7 +10513,7 @@
       <c r="O99">
         <v>600</v>
       </c>
-      <c r="P99" s="30">
+      <c r="P99">
         <v>90</v>
       </c>
       <c r="Q99" s="7"/>
@@ -10491,7 +10535,7 @@
       <c r="AE99" s="11"/>
       <c r="AF99" s="11"/>
       <c r="AG99" s="12"/>
-      <c r="AH99" s="31">
+      <c r="AH99" s="11">
         <v>12.5</v>
       </c>
       <c r="AI99" s="11"/>
@@ -10512,7 +10556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="14" t="s">
         <v>247</v>
       </c>
@@ -10548,7 +10592,7 @@
       <c r="O100">
         <v>500</v>
       </c>
-      <c r="P100" s="30">
+      <c r="P100">
         <v>70</v>
       </c>
       <c r="Q100" s="4"/>
@@ -10570,7 +10614,7 @@
       <c r="AE100" s="11"/>
       <c r="AF100" s="11"/>
       <c r="AG100" s="12"/>
-      <c r="AH100" s="31">
+      <c r="AH100" s="11">
         <v>13</v>
       </c>
       <c r="AI100" s="11"/>
@@ -10591,7 +10635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
         <v>249</v>
       </c>
@@ -10627,7 +10671,7 @@
       <c r="O101">
         <v>600</v>
       </c>
-      <c r="P101" s="30">
+      <c r="P101">
         <v>90</v>
       </c>
       <c r="Q101" s="24"/>
@@ -10651,7 +10695,7 @@
       <c r="AE101" s="11"/>
       <c r="AF101" s="11"/>
       <c r="AG101" s="12"/>
-      <c r="AH101" s="31">
+      <c r="AH101" s="11">
         <v>11</v>
       </c>
       <c r="AI101" s="11">
@@ -10677,7 +10721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>398</v>
       </c>
@@ -10711,7 +10755,7 @@
       <c r="O102">
         <v>600</v>
       </c>
-      <c r="P102" s="30">
+      <c r="P102">
         <v>90</v>
       </c>
       <c r="Q102" s="25"/>
@@ -10723,7 +10767,7 @@
         <v>20</v>
       </c>
       <c r="AG102" s="9"/>
-      <c r="AH102" s="31">
+      <c r="AH102" s="11">
         <v>16</v>
       </c>
       <c r="AI102" s="11">
@@ -10749,7 +10793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>251</v>
       </c>
@@ -10785,7 +10829,7 @@
       <c r="O103">
         <v>550</v>
       </c>
-      <c r="P103" s="30">
+      <c r="P103">
         <v>90</v>
       </c>
       <c r="Q103" s="7"/>
@@ -10809,7 +10853,7 @@
       <c r="AE103" s="11"/>
       <c r="AF103" s="11"/>
       <c r="AG103" s="12"/>
-      <c r="AH103" s="31">
+      <c r="AH103" s="11">
         <v>13</v>
       </c>
       <c r="AI103" s="11">
@@ -10835,7 +10879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
         <v>71</v>
       </c>
@@ -10871,7 +10915,7 @@
       <c r="O104">
         <v>600</v>
       </c>
-      <c r="P104" s="30">
+      <c r="P104">
         <v>90</v>
       </c>
       <c r="Q104" s="4"/>
@@ -10895,7 +10939,7 @@
       <c r="AE104" s="11"/>
       <c r="AF104" s="11"/>
       <c r="AG104" s="12"/>
-      <c r="AH104" s="31">
+      <c r="AH104" s="11">
         <v>11</v>
       </c>
       <c r="AI104" s="11">
@@ -10921,7 +10965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>73</v>
       </c>
@@ -10958,7 +11002,7 @@
       <c r="O105">
         <v>550</v>
       </c>
-      <c r="P105" s="30">
+      <c r="P105">
         <v>90</v>
       </c>
       <c r="Q105" s="7"/>
@@ -10982,7 +11026,7 @@
       <c r="AE105" s="11"/>
       <c r="AF105" s="11"/>
       <c r="AG105" s="12"/>
-      <c r="AH105" s="31">
+      <c r="AH105" s="11">
         <v>14</v>
       </c>
       <c r="AI105" s="11">
@@ -11008,7 +11052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>75</v>
       </c>
@@ -11044,7 +11088,7 @@
       <c r="O106">
         <v>600</v>
       </c>
-      <c r="P106" s="30">
+      <c r="P106">
         <v>90</v>
       </c>
       <c r="Q106" s="4"/>
@@ -11056,7 +11100,7 @@
         <v>20</v>
       </c>
       <c r="AG106" s="9"/>
-      <c r="AH106" s="31">
+      <c r="AH106" s="11">
         <v>16</v>
       </c>
       <c r="AI106" s="11">
@@ -11070,7 +11114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
         <v>253</v>
       </c>
@@ -11106,7 +11150,7 @@
       <c r="O107">
         <v>550</v>
       </c>
-      <c r="P107" s="30">
+      <c r="P107">
         <v>90</v>
       </c>
       <c r="Q107" s="7"/>
@@ -11130,7 +11174,7 @@
       <c r="AE107" s="11"/>
       <c r="AF107" s="11"/>
       <c r="AG107" s="12"/>
-      <c r="AH107" s="31">
+      <c r="AH107" s="11">
         <v>13</v>
       </c>
       <c r="AI107" s="11">
@@ -11156,7 +11200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>255</v>
       </c>
@@ -11197,7 +11241,7 @@
       </c>
       <c r="Q108" s="4"/>
       <c r="R108" s="4"/>
-      <c r="S108" s="29">
+      <c r="S108" s="3">
         <v>20</v>
       </c>
       <c r="T108">
@@ -11207,7 +11251,7 @@
         <v>20</v>
       </c>
       <c r="AG108" s="9"/>
-      <c r="AH108" s="31">
+      <c r="AH108" s="11">
         <v>16</v>
       </c>
       <c r="AI108" s="11">
@@ -11238,7 +11282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>257</v>
       </c>
@@ -11297,7 +11341,7 @@
       <c r="AD109" s="11"/>
       <c r="AE109" s="11"/>
       <c r="AF109" s="11"/>
-      <c r="AG109" s="31"/>
+      <c r="AG109" s="11"/>
       <c r="AH109" s="13">
         <v>26</v>
       </c>
@@ -11324,7 +11368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
         <v>259</v>
       </c>
@@ -11418,7 +11462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>261</v>
       </c>
@@ -11501,7 +11545,34 @@
       </c>
       <c r="AZ111" s="26"/>
     </row>
-    <row r="112" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B112" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="C112">
+        <v>710</v>
+      </c>
+      <c r="D112">
+        <v>48.6</v>
+      </c>
+      <c r="E112">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="F112">
+        <v>-0.23</v>
+      </c>
+      <c r="G112">
+        <v>17.41</v>
+      </c>
+      <c r="H112">
+        <v>18.420000000000002</v>
+      </c>
+      <c r="I112">
+        <v>209456</v>
+      </c>
+      <c r="J112" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="L112" t="s">
         <v>267</v>
       </c>
@@ -11514,7 +11585,7 @@
       <c r="O112">
         <v>1000</v>
       </c>
-      <c r="P112" s="30">
+      <c r="P112">
         <v>250</v>
       </c>
       <c r="Q112" s="4"/>
@@ -11538,7 +11609,7 @@
       <c r="AE112" s="11"/>
       <c r="AF112" s="11"/>
       <c r="AG112" s="12"/>
-      <c r="AH112" s="31">
+      <c r="AH112" s="11">
         <v>37.5</v>
       </c>
       <c r="AI112" s="11">
@@ -11557,16 +11628,14 @@
       <c r="AT112" s="11"/>
       <c r="AU112" s="11"/>
       <c r="AV112" s="12"/>
-      <c r="AW112" s="30">
+      <c r="AW112">
         <v>3</v>
       </c>
-      <c r="AX112" s="30">
+      <c r="AX112">
         <v>3</v>
       </c>
-      <c r="AY112" s="30"/>
-      <c r="AZ112" s="30"/>
-    </row>
-    <row r="113" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L113" t="s">
         <v>268</v>
       </c>
@@ -11579,7 +11648,7 @@
       <c r="O113">
         <v>1000</v>
       </c>
-      <c r="P113" s="30">
+      <c r="P113">
         <v>250</v>
       </c>
       <c r="Q113" s="15"/>
@@ -11603,7 +11672,7 @@
       <c r="AE113" s="11"/>
       <c r="AF113" s="11"/>
       <c r="AG113" s="12"/>
-      <c r="AH113" s="31">
+      <c r="AH113" s="11">
         <v>37.5</v>
       </c>
       <c r="AI113" s="11">
@@ -11629,7 +11698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L114" t="s">
         <v>269</v>
       </c>
@@ -11689,7 +11758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L115" t="s">
         <v>270</v>
       </c>
@@ -11711,7 +11780,7 @@
       <c r="R115" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="S115" s="31">
+      <c r="S115" s="11">
         <v>31.25</v>
       </c>
       <c r="T115" s="11"/>
@@ -11727,7 +11796,7 @@
       <c r="AD115" s="11"/>
       <c r="AE115" s="11"/>
       <c r="AF115" s="11"/>
-      <c r="AG115" s="31"/>
+      <c r="AG115" s="11"/>
       <c r="AH115" s="13">
         <v>25</v>
       </c>
@@ -11749,7 +11818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L116" t="s">
         <v>271</v>
       </c>
@@ -11771,7 +11840,7 @@
       <c r="R116" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="S116" s="30">
+      <c r="S116">
         <v>60</v>
       </c>
       <c r="T116">
@@ -11783,7 +11852,6 @@
       <c r="V116">
         <v>60</v>
       </c>
-      <c r="AG116" s="30"/>
       <c r="AH116" s="5">
         <v>48</v>
       </c>
@@ -11810,7 +11878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L117" t="s">
         <v>272</v>
       </c>
@@ -11823,7 +11891,7 @@
       <c r="O117">
         <v>800</v>
       </c>
-      <c r="P117" s="30">
+      <c r="P117">
         <v>180</v>
       </c>
       <c r="Q117" s="15"/>
@@ -11843,7 +11911,7 @@
         <v>60</v>
       </c>
       <c r="AG117" s="6"/>
-      <c r="AH117" s="30">
+      <c r="AH117">
         <v>48</v>
       </c>
       <c r="AI117">
@@ -11869,7 +11937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L118" t="s">
         <v>273</v>
       </c>
@@ -11882,7 +11950,7 @@
       <c r="O118">
         <v>1100</v>
       </c>
-      <c r="P118" s="30">
+      <c r="P118">
         <v>180</v>
       </c>
       <c r="Q118" s="4"/>
@@ -11900,7 +11968,7 @@
         <v>50</v>
       </c>
       <c r="AG118" s="6"/>
-      <c r="AH118" s="30">
+      <c r="AH118">
         <v>40</v>
       </c>
       <c r="AI118">
@@ -11926,7 +11994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L119" t="s">
         <v>274</v>
       </c>
@@ -11939,7 +12007,7 @@
       <c r="O119">
         <v>550</v>
       </c>
-      <c r="P119" s="30">
+      <c r="P119">
         <v>80</v>
       </c>
       <c r="Q119" s="15"/>
@@ -11951,7 +12019,7 @@
         <v>20</v>
       </c>
       <c r="AG119" s="6"/>
-      <c r="AH119" s="30">
+      <c r="AH119">
         <v>16</v>
       </c>
       <c r="AI119">
@@ -11965,7 +12033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L120" t="s">
         <v>275</v>
       </c>
@@ -11978,7 +12046,7 @@
       <c r="O120">
         <v>800</v>
       </c>
-      <c r="P120" s="30">
+      <c r="P120">
         <v>200</v>
       </c>
       <c r="Q120" s="4"/>
@@ -11990,7 +12058,7 @@
         <v>40</v>
       </c>
       <c r="AG120" s="9"/>
-      <c r="AH120" s="31">
+      <c r="AH120" s="11">
         <v>32</v>
       </c>
       <c r="AI120" s="11">
@@ -12016,7 +12084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L121" t="s">
         <v>276</v>
       </c>
@@ -12029,7 +12097,7 @@
       <c r="O121">
         <v>1100</v>
       </c>
-      <c r="P121" s="30">
+      <c r="P121">
         <v>200</v>
       </c>
       <c r="Q121" s="15"/>
@@ -12041,7 +12109,7 @@
         <v>40</v>
       </c>
       <c r="AG121" s="9"/>
-      <c r="AH121" s="31">
+      <c r="AH121" s="11">
         <v>32</v>
       </c>
       <c r="AI121" s="11">
@@ -12067,7 +12135,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L122" t="s">
         <v>277</v>
       </c>
@@ -12128,7 +12196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L123" t="s">
         <v>278</v>
       </c>
@@ -12141,7 +12209,7 @@
       <c r="O123">
         <v>1100</v>
       </c>
-      <c r="P123" s="30">
+      <c r="P123">
         <v>200</v>
       </c>
       <c r="Q123" s="15"/>
@@ -12152,7 +12220,7 @@
       <c r="T123">
         <v>40</v>
       </c>
-      <c r="AG123" s="29"/>
+      <c r="AG123" s="3"/>
       <c r="AH123" s="5">
         <v>32</v>
       </c>
@@ -12167,7 +12235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L124" t="s">
         <v>279</v>
       </c>
@@ -12180,7 +12248,7 @@
       <c r="O124">
         <v>800</v>
       </c>
-      <c r="P124" s="30">
+      <c r="P124">
         <v>160</v>
       </c>
       <c r="Q124" s="4"/>
@@ -12198,7 +12266,7 @@
         <v>25</v>
       </c>
       <c r="AG124" s="9"/>
-      <c r="AH124" s="31">
+      <c r="AH124" s="11">
         <v>40</v>
       </c>
       <c r="AI124" s="11">
@@ -12234,7 +12302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L125" t="s">
         <v>280</v>
       </c>
@@ -12247,7 +12315,7 @@
       <c r="O125">
         <v>1100</v>
       </c>
-      <c r="P125" s="30">
+      <c r="P125">
         <v>160</v>
       </c>
       <c r="Q125" s="15"/>
@@ -12262,7 +12330,7 @@
         <v>40</v>
       </c>
       <c r="AG125" s="9"/>
-      <c r="AH125" s="31">
+      <c r="AH125" s="11">
         <v>40</v>
       </c>
       <c r="AI125" s="11">
@@ -12293,7 +12361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L126" t="s">
         <v>281</v>
       </c>
@@ -12306,7 +12374,7 @@
       <c r="O126">
         <v>800</v>
       </c>
-      <c r="P126" s="30">
+      <c r="P126">
         <v>160</v>
       </c>
       <c r="Q126" s="4"/>
@@ -12336,7 +12404,7 @@
         <v>50</v>
       </c>
       <c r="AG126" s="9"/>
-      <c r="AH126" s="30">
+      <c r="AH126">
         <v>40</v>
       </c>
       <c r="AI126">
@@ -12386,7 +12454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L127" t="s">
         <v>282</v>
       </c>
@@ -12399,7 +12467,7 @@
       <c r="O127">
         <v>1100</v>
       </c>
-      <c r="P127" s="30">
+      <c r="P127">
         <v>200</v>
       </c>
       <c r="Q127" s="15"/>
@@ -12411,7 +12479,7 @@
         <v>30</v>
       </c>
       <c r="AG127" s="9"/>
-      <c r="AH127" s="31">
+      <c r="AH127" s="11">
         <v>25</v>
       </c>
       <c r="AI127" s="11">
@@ -12437,7 +12505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B128" s="3"/>
       <c r="L128" t="s">
         <v>283</v>
@@ -12451,7 +12519,7 @@
       <c r="O128">
         <v>1000</v>
       </c>
-      <c r="P128" s="30">
+      <c r="P128">
         <v>390</v>
       </c>
       <c r="Q128" s="4"/>
@@ -12475,7 +12543,7 @@
       <c r="AE128" s="11"/>
       <c r="AF128" s="11"/>
       <c r="AG128" s="12"/>
-      <c r="AH128" s="31">
+      <c r="AH128" s="11">
         <v>33</v>
       </c>
       <c r="AI128" s="11">
@@ -12501,7 +12569,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L129" t="s">
         <v>284</v>
       </c>
@@ -12514,7 +12582,7 @@
       <c r="O129">
         <v>1000</v>
       </c>
-      <c r="P129" s="30">
+      <c r="P129">
         <v>188</v>
       </c>
       <c r="Q129" s="15"/>
@@ -12545,7 +12613,7 @@
       <c r="AD129" s="11"/>
       <c r="AE129" s="11"/>
       <c r="AF129" s="11"/>
-      <c r="AG129" s="31"/>
+      <c r="AG129" s="11"/>
       <c r="AH129" s="13">
         <v>20</v>
       </c>
@@ -12592,7 +12660,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L130" t="s">
         <v>285</v>
       </c>
@@ -12605,7 +12673,7 @@
       <c r="O130">
         <v>1100</v>
       </c>
-      <c r="P130" s="29">
+      <c r="P130" s="3">
         <v>500</v>
       </c>
       <c r="Q130" s="4"/>
@@ -12725,7 +12793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L131" t="s">
         <v>286</v>
       </c>
@@ -12738,7 +12806,7 @@
       <c r="O131">
         <v>1000</v>
       </c>
-      <c r="P131" s="29">
+      <c r="P131" s="3">
         <v>430</v>
       </c>
       <c r="Q131" s="15"/>
@@ -12795,7 +12863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L132" t="s">
         <v>287</v>
       </c>
@@ -12813,7 +12881,7 @@
       </c>
       <c r="Q132" s="4"/>
       <c r="R132" s="4"/>
-      <c r="S132" s="30">
+      <c r="S132">
         <v>40</v>
       </c>
       <c r="T132">
@@ -12838,7 +12906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L133" t="s">
         <v>288</v>
       </c>
@@ -12851,7 +12919,7 @@
       <c r="O133">
         <v>1000</v>
       </c>
-      <c r="P133" s="29">
+      <c r="P133" s="3">
         <v>200</v>
       </c>
       <c r="Q133" s="15"/>
@@ -12892,7 +12960,7 @@
       <c r="BH133" s="22"/>
       <c r="BI133" s="22"/>
     </row>
-    <row r="134" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L134" t="s">
         <v>289</v>
       </c>
@@ -12921,7 +12989,7 @@
       <c r="AE134" s="11"/>
       <c r="AF134" s="11"/>
       <c r="AG134" s="12"/>
-      <c r="AH134" s="30">
+      <c r="AH134">
         <v>16</v>
       </c>
       <c r="AI134">
@@ -12935,7 +13003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L135" t="s">
         <v>290</v>
       </c>
@@ -12978,7 +13046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L136" t="s">
         <v>291</v>
       </c>
@@ -13061,7 +13129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L137" t="s">
         <v>292</v>
       </c>
@@ -13104,7 +13172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L138" t="s">
         <v>293</v>
       </c>
@@ -13147,7 +13215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L139" t="s">
         <v>294</v>
       </c>
@@ -13169,13 +13237,12 @@
       <c r="R139" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="S139" s="30">
+      <c r="S139">
         <v>50</v>
       </c>
       <c r="T139">
         <v>50</v>
       </c>
-      <c r="AG139" s="30"/>
       <c r="AH139" s="5">
         <v>36</v>
       </c>
@@ -13196,7 +13263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L140" t="s">
         <v>295</v>
       </c>
@@ -13218,25 +13285,18 @@
       <c r="R140" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="S140" s="30">
+      <c r="S140">
         <v>50</v>
       </c>
       <c r="T140">
         <v>50</v>
       </c>
-      <c r="AG140" s="30"/>
       <c r="AH140" s="5">
         <v>36</v>
       </c>
-      <c r="AI140" s="30">
+      <c r="AI140">
         <v>36</v>
       </c>
-      <c r="AJ140" s="30"/>
-      <c r="AK140" s="30"/>
-      <c r="AL140" s="30"/>
-      <c r="AM140" s="30"/>
-      <c r="AN140" s="30"/>
-      <c r="AO140" s="30"/>
       <c r="AV140" s="6"/>
       <c r="AW140">
         <v>2</v>
@@ -13245,7 +13305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L141" t="s">
         <v>296</v>
       </c>
@@ -13267,13 +13327,12 @@
       <c r="R141" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="S141" s="30">
+      <c r="S141">
         <v>20</v>
       </c>
       <c r="T141">
         <v>20</v>
       </c>
-      <c r="AG141" s="30"/>
       <c r="AH141" s="5">
         <v>16</v>
       </c>
@@ -13288,7 +13347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L142" t="s">
         <v>297</v>
       </c>
@@ -13310,7 +13369,7 @@
       <c r="R142" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="S142" s="31">
+      <c r="S142" s="11">
         <v>40</v>
       </c>
       <c r="T142" s="11">
@@ -13344,7 +13403,7 @@
       <c r="AD142" s="11"/>
       <c r="AE142" s="11"/>
       <c r="AF142" s="11"/>
-      <c r="AG142" s="31"/>
+      <c r="AG142" s="11"/>
       <c r="AH142" s="13">
         <v>26</v>
       </c>
@@ -13411,7 +13470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L143" t="s">
         <v>298</v>
       </c>
@@ -13429,7 +13488,7 @@
       </c>
       <c r="Q143" s="15"/>
       <c r="R143" s="15"/>
-      <c r="S143" s="31">
+      <c r="S143" s="11">
         <v>50</v>
       </c>
       <c r="T143" s="11">
@@ -13459,7 +13518,7 @@
       <c r="AD143" s="11"/>
       <c r="AE143" s="11"/>
       <c r="AF143" s="11"/>
-      <c r="AG143" s="31"/>
+      <c r="AG143" s="11"/>
       <c r="AH143" s="13">
         <v>36</v>
       </c>
@@ -13516,7 +13575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L144" t="s">
         <v>299</v>
       </c>
@@ -13534,7 +13593,7 @@
       </c>
       <c r="Q144" s="4"/>
       <c r="R144" s="4"/>
-      <c r="S144" s="30">
+      <c r="S144">
         <v>300</v>
       </c>
       <c r="AH144" s="5">
@@ -13552,7 +13611,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="145" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L145" t="s">
         <v>300</v>
       </c>
@@ -13570,7 +13629,7 @@
       </c>
       <c r="Q145" s="15"/>
       <c r="R145" s="15"/>
-      <c r="S145" s="31">
+      <c r="S145" s="11">
         <v>34.299999999999997</v>
       </c>
       <c r="T145" s="11">
@@ -13592,15 +13651,15 @@
       <c r="AH145" s="13">
         <v>22</v>
       </c>
-      <c r="AI145" s="31">
+      <c r="AI145" s="11">
         <v>22</v>
       </c>
-      <c r="AJ145" s="31"/>
-      <c r="AK145" s="31"/>
-      <c r="AL145" s="31"/>
-      <c r="AM145" s="31"/>
-      <c r="AN145" s="31"/>
-      <c r="AO145" s="31"/>
+      <c r="AJ145" s="11"/>
+      <c r="AK145" s="11"/>
+      <c r="AL145" s="11"/>
+      <c r="AM145" s="11"/>
+      <c r="AN145" s="11"/>
+      <c r="AO145" s="11"/>
       <c r="AP145" s="11"/>
       <c r="AQ145" s="11"/>
       <c r="AR145" s="11"/>
@@ -13615,7 +13674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L146" t="s">
         <v>301</v>
       </c>
@@ -13634,7 +13693,7 @@
       </c>
       <c r="Q146" s="4"/>
       <c r="R146" s="4"/>
-      <c r="S146" s="31">
+      <c r="S146" s="11">
         <v>19.5</v>
       </c>
       <c r="T146" s="11">
@@ -13679,7 +13738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L147" t="s">
         <v>302</v>
       </c>
@@ -13701,13 +13760,12 @@
       <c r="R147" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="S147" s="30">
+      <c r="S147">
         <v>19.5</v>
       </c>
       <c r="T147">
         <v>30</v>
       </c>
-      <c r="AG147" s="30"/>
       <c r="AH147" s="5">
         <v>12.5</v>
       </c>
@@ -13722,7 +13780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L148" t="s">
         <v>303</v>
       </c>
@@ -13740,7 +13798,7 @@
       </c>
       <c r="Q148" s="4"/>
       <c r="R148" s="4"/>
-      <c r="S148" s="31">
+      <c r="S148" s="11">
         <v>40</v>
       </c>
       <c r="T148" s="11">
@@ -13792,7 +13850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L149" t="s">
         <v>304</v>
       </c>
@@ -13810,7 +13868,7 @@
       </c>
       <c r="Q149" s="15"/>
       <c r="R149" s="15"/>
-      <c r="S149" s="31">
+      <c r="S149" s="11">
         <v>40</v>
       </c>
       <c r="T149" s="11">
@@ -13862,7 +13920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L150" t="s">
         <v>305</v>
       </c>
@@ -13880,7 +13938,7 @@
       </c>
       <c r="Q150" s="4"/>
       <c r="R150" s="4"/>
-      <c r="S150" s="31">
+      <c r="S150" s="11">
         <v>44.5</v>
       </c>
       <c r="T150" s="11">
@@ -13939,7 +13997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L151" t="s">
         <v>306</v>
       </c>
@@ -13957,7 +14015,7 @@
       </c>
       <c r="Q151" s="15"/>
       <c r="R151" s="15"/>
-      <c r="S151" s="31">
+      <c r="S151" s="11">
         <v>44.5</v>
       </c>
       <c r="T151" s="11">
@@ -14016,7 +14074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L152" t="s">
         <v>307</v>
       </c>
@@ -14034,7 +14092,7 @@
       </c>
       <c r="Q152" s="4"/>
       <c r="R152" s="4"/>
-      <c r="S152" s="31">
+      <c r="S152" s="11">
         <v>40</v>
       </c>
       <c r="T152" s="11">
@@ -14128,7 +14186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L153" t="s">
         <v>308</v>
       </c>
@@ -14150,7 +14208,7 @@
       <c r="R153" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="S153" s="31">
+      <c r="S153" s="11">
         <v>50</v>
       </c>
       <c r="T153" s="11">
@@ -14176,7 +14234,7 @@
       <c r="AD153" s="11"/>
       <c r="AE153" s="11"/>
       <c r="AF153" s="11"/>
-      <c r="AG153" s="31"/>
+      <c r="AG153" s="11"/>
       <c r="AH153" s="13">
         <v>40</v>
       </c>
@@ -14223,7 +14281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L154" t="s">
         <v>309</v>
       </c>
@@ -14242,7 +14300,7 @@
       </c>
       <c r="Q154" s="4"/>
       <c r="R154" s="4"/>
-      <c r="S154" s="31">
+      <c r="S154" s="11">
         <v>50</v>
       </c>
       <c r="T154" s="11">
@@ -14315,7 +14373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L155" t="s">
         <v>310</v>
       </c>
@@ -14333,7 +14391,7 @@
       </c>
       <c r="Q155" s="15"/>
       <c r="R155" s="15"/>
-      <c r="S155" s="31">
+      <c r="S155" s="11">
         <v>15.6</v>
       </c>
       <c r="T155" s="11">
@@ -14385,7 +14443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L156" t="s">
         <v>311</v>
       </c>
@@ -14408,7 +14466,7 @@
       <c r="R156" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="S156" s="31">
+      <c r="S156" s="11">
         <v>40</v>
       </c>
       <c r="T156" s="11">
@@ -14430,7 +14488,7 @@
       <c r="AD156" s="11"/>
       <c r="AE156" s="11"/>
       <c r="AF156" s="11"/>
-      <c r="AG156" s="31"/>
+      <c r="AG156" s="11"/>
       <c r="AH156" s="13">
         <v>32</v>
       </c>
@@ -14467,7 +14525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L157" t="s">
         <v>312</v>
       </c>
@@ -14486,7 +14544,7 @@
       </c>
       <c r="Q157" s="15"/>
       <c r="R157" s="15"/>
-      <c r="S157" s="31">
+      <c r="S157" s="11">
         <v>40</v>
       </c>
       <c r="T157" s="11">
@@ -14545,7 +14603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L158" t="s">
         <v>313</v>
       </c>
@@ -14568,7 +14626,7 @@
       <c r="R158" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="S158" s="31">
+      <c r="S158" s="11">
         <v>40</v>
       </c>
       <c r="T158" s="11">
@@ -14594,7 +14652,7 @@
       <c r="AD158" s="11"/>
       <c r="AE158" s="11"/>
       <c r="AF158" s="11"/>
-      <c r="AG158" s="31"/>
+      <c r="AG158" s="11"/>
       <c r="AH158" s="13">
         <v>32</v>
       </c>
@@ -14641,7 +14699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L159" t="s">
         <v>314</v>
       </c>
@@ -14660,7 +14718,7 @@
       </c>
       <c r="Q159" s="15"/>
       <c r="R159" s="15"/>
-      <c r="S159" s="31">
+      <c r="S159" s="11">
         <v>40</v>
       </c>
       <c r="T159" s="11">
@@ -14733,7 +14791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L160" t="s">
         <v>315</v>
       </c>
@@ -14751,7 +14809,7 @@
       </c>
       <c r="Q160" s="4"/>
       <c r="R160" s="4"/>
-      <c r="S160" s="30">
+      <c r="S160">
         <v>40</v>
       </c>
       <c r="T160">
@@ -14780,7 +14838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L161" t="s">
         <v>316</v>
       </c>
@@ -14798,7 +14856,7 @@
       </c>
       <c r="Q161" s="15"/>
       <c r="R161" s="15"/>
-      <c r="S161" s="30">
+      <c r="S161">
         <v>40</v>
       </c>
       <c r="T161">
@@ -14836,7 +14894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L162" t="s">
         <v>317</v>
       </c>
@@ -14854,7 +14912,7 @@
       </c>
       <c r="Q162" s="4"/>
       <c r="R162" s="4"/>
-      <c r="S162" s="30">
+      <c r="S162">
         <v>40</v>
       </c>
       <c r="T162">
@@ -14901,7 +14959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L163" t="s">
         <v>318</v>
       </c>
@@ -14919,7 +14977,7 @@
       </c>
       <c r="Q163" s="15"/>
       <c r="R163" s="15"/>
-      <c r="S163" s="30">
+      <c r="S163">
         <v>40</v>
       </c>
       <c r="T163">
@@ -14939,7 +14997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L164" t="s">
         <v>319</v>
       </c>
@@ -14961,7 +15019,7 @@
       <c r="R164" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="S164" s="30">
+      <c r="S164">
         <v>50</v>
       </c>
       <c r="T164">
@@ -14991,7 +15049,6 @@
       <c r="AB164">
         <v>50</v>
       </c>
-      <c r="AG164" s="30"/>
       <c r="AH164" s="5">
         <v>42</v>
       </c>
@@ -15054,7 +15111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L165" t="s">
         <v>320</v>
       </c>
@@ -15072,7 +15129,7 @@
       </c>
       <c r="Q165" s="15"/>
       <c r="R165" s="15"/>
-      <c r="S165" s="29">
+      <c r="S165" s="3">
         <v>50</v>
       </c>
       <c r="T165">
@@ -15146,7 +15203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L166" t="s">
         <v>321</v>
       </c>
@@ -15164,7 +15221,7 @@
       </c>
       <c r="Q166" s="4"/>
       <c r="R166" s="4"/>
-      <c r="S166" s="31">
+      <c r="S166" s="11">
         <v>22</v>
       </c>
       <c r="T166" s="11">
@@ -15209,7 +15266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L167" t="s">
         <v>322</v>
       </c>
@@ -15231,13 +15288,12 @@
       <c r="R167" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="S167" s="29">
+      <c r="S167" s="3">
         <v>22</v>
       </c>
       <c r="T167">
         <v>22</v>
       </c>
-      <c r="AG167" s="30"/>
       <c r="AH167" s="8">
         <v>16</v>
       </c>
@@ -15252,7 +15308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L168" t="s">
         <v>323</v>
       </c>
@@ -15270,7 +15326,7 @@
       </c>
       <c r="Q168" s="4"/>
       <c r="R168" s="4"/>
-      <c r="S168" s="31">
+      <c r="S168" s="11">
         <v>17.2</v>
       </c>
       <c r="T168" s="11">
@@ -15315,7 +15371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L169" t="s">
         <v>324</v>
       </c>
@@ -15333,7 +15389,7 @@
       </c>
       <c r="Q169" s="15"/>
       <c r="R169" s="15"/>
-      <c r="S169" s="29">
+      <c r="S169" s="3">
         <v>50</v>
       </c>
       <c r="T169">
@@ -15414,7 +15470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L170" t="s">
         <v>325</v>
       </c>
@@ -15432,7 +15488,7 @@
       </c>
       <c r="Q170" s="4"/>
       <c r="R170" s="4"/>
-      <c r="S170" s="29">
+      <c r="S170" s="3">
         <v>50</v>
       </c>
       <c r="T170">
@@ -15507,7 +15563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L171" t="s">
         <v>326</v>
       </c>
@@ -15525,7 +15581,7 @@
       </c>
       <c r="Q171" s="15"/>
       <c r="R171" s="15"/>
-      <c r="S171" s="31">
+      <c r="S171" s="11">
         <v>50</v>
       </c>
       <c r="T171" s="11">
@@ -15612,7 +15668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L172" t="s">
         <v>327</v>
       </c>
@@ -15630,7 +15686,7 @@
       </c>
       <c r="Q172" s="4"/>
       <c r="R172" s="4"/>
-      <c r="S172" s="29">
+      <c r="S172" s="3">
         <v>50</v>
       </c>
       <c r="T172">
@@ -15705,7 +15761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L173" t="s">
         <v>328</v>
       </c>
@@ -15728,7 +15784,7 @@
       <c r="R173" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="S173" s="30">
+      <c r="S173">
         <v>48</v>
       </c>
       <c r="T173">
@@ -15746,7 +15802,6 @@
       <c r="X173">
         <v>48</v>
       </c>
-      <c r="AG173" s="30"/>
       <c r="AH173" s="8">
         <v>32</v>
       </c>
@@ -15787,7 +15842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L174" t="s">
         <v>329</v>
       </c>
@@ -15810,7 +15865,7 @@
       <c r="R174" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="S174" s="30">
+      <c r="S174">
         <v>28</v>
       </c>
       <c r="T174">
@@ -15830,7 +15885,7 @@
       <c r="AD174" s="11"/>
       <c r="AE174" s="11"/>
       <c r="AF174" s="11"/>
-      <c r="AG174" s="31"/>
+      <c r="AG174" s="11"/>
       <c r="AH174" s="13">
         <v>20</v>
       </c>
@@ -15862,7 +15917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L175" t="s">
         <v>330</v>
       </c>
@@ -15881,7 +15936,7 @@
       </c>
       <c r="Q175" s="15"/>
       <c r="R175" s="15"/>
-      <c r="S175" s="30">
+      <c r="S175">
         <v>48</v>
       </c>
       <c r="T175">
@@ -15901,7 +15956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L176" t="s">
         <v>331</v>
       </c>
@@ -15920,7 +15975,7 @@
       </c>
       <c r="Q176" s="4"/>
       <c r="R176" s="4"/>
-      <c r="S176" s="31">
+      <c r="S176" s="11">
         <v>48</v>
       </c>
       <c r="T176" s="11">
@@ -15965,7 +16020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L177" t="s">
         <v>332</v>
       </c>
@@ -15988,7 +16043,7 @@
       <c r="R177" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="S177" s="31">
+      <c r="S177" s="11">
         <v>60</v>
       </c>
       <c r="T177" s="11">
@@ -16006,7 +16061,7 @@
       <c r="AD177" s="11"/>
       <c r="AE177" s="11"/>
       <c r="AF177" s="11"/>
-      <c r="AG177" s="31"/>
+      <c r="AG177" s="11"/>
       <c r="AH177" s="13">
         <v>40</v>
       </c>
@@ -16033,7 +16088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L178" t="s">
         <v>333</v>
       </c>
@@ -16051,7 +16106,7 @@
       </c>
       <c r="Q178" s="4"/>
       <c r="R178" s="4"/>
-      <c r="S178" s="30">
+      <c r="S178">
         <v>48</v>
       </c>
       <c r="T178">
@@ -16083,7 +16138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L179" t="s">
         <v>334</v>
       </c>
@@ -16097,7 +16152,7 @@
       <c r="O179">
         <v>950</v>
       </c>
-      <c r="P179" s="29">
+      <c r="P179" s="3">
         <v>150</v>
       </c>
       <c r="Q179" s="15"/>
@@ -16121,7 +16176,7 @@
       <c r="AE179" s="20"/>
       <c r="AF179" s="20"/>
       <c r="AG179" s="21"/>
-      <c r="AH179" s="31">
+      <c r="AH179" s="11">
         <v>32</v>
       </c>
       <c r="AI179" s="11">
@@ -16147,7 +16202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L180" t="s">
         <v>335</v>
       </c>
@@ -16215,7 +16270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L181" t="s">
         <v>336</v>
       </c>
@@ -16290,7 +16345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L182" t="s">
         <v>337</v>
       </c>
@@ -16356,7 +16411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L183" t="s">
         <v>338</v>
       </c>
@@ -16393,7 +16448,7 @@
       <c r="AD183" s="11"/>
       <c r="AE183" s="11"/>
       <c r="AF183" s="11"/>
-      <c r="AG183" s="31"/>
+      <c r="AG183" s="11"/>
       <c r="AH183" s="11">
         <v>40</v>
       </c>
@@ -16412,7 +16467,7 @@
       <c r="AS183" s="11"/>
       <c r="AT183" s="11"/>
       <c r="AU183" s="11"/>
-      <c r="AV183" s="31"/>
+      <c r="AV183" s="11"/>
       <c r="AW183">
         <v>2</v>
       </c>
@@ -16420,7 +16475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L184" t="s">
         <v>339</v>
       </c>
@@ -16491,7 +16546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L185" t="s">
         <v>340</v>
       </c>
@@ -16534,7 +16589,7 @@
       <c r="AD185" s="11"/>
       <c r="AE185" s="11"/>
       <c r="AF185" s="11"/>
-      <c r="AG185" s="31"/>
+      <c r="AG185" s="11"/>
       <c r="AH185" s="11">
         <v>32</v>
       </c>
@@ -16555,7 +16610,7 @@
       <c r="AS185" s="11"/>
       <c r="AT185" s="11"/>
       <c r="AU185" s="11"/>
-      <c r="AV185" s="31"/>
+      <c r="AV185" s="11"/>
       <c r="AW185">
         <v>2</v>
       </c>
@@ -16566,7 +16621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L186" t="s">
         <v>341</v>
       </c>
@@ -16644,7 +16699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L187" t="s">
         <v>342</v>
       </c>
@@ -16676,7 +16731,6 @@
       <c r="U187">
         <v>60</v>
       </c>
-      <c r="AG187" s="30"/>
       <c r="AH187" s="3">
         <v>32</v>
       </c>
@@ -16686,7 +16740,7 @@
       <c r="AJ187">
         <v>40</v>
       </c>
-      <c r="AV187" s="29"/>
+      <c r="AV187" s="3"/>
       <c r="AW187">
         <v>2</v>
       </c>
@@ -16697,7 +16751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L188" t="s">
         <v>343</v>
       </c>
@@ -16756,7 +16810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L189" t="s">
         <v>344</v>
       </c>
@@ -16801,7 +16855,7 @@
       <c r="AD189" s="11"/>
       <c r="AE189" s="11"/>
       <c r="AF189" s="11"/>
-      <c r="AG189" s="31"/>
+      <c r="AG189" s="11"/>
       <c r="AH189" s="11">
         <v>40</v>
       </c>
@@ -16824,7 +16878,7 @@
       <c r="AS189" s="11"/>
       <c r="AT189" s="11"/>
       <c r="AU189" s="11"/>
-      <c r="AV189" s="31"/>
+      <c r="AV189" s="11"/>
       <c r="AW189">
         <v>2</v>
       </c>
@@ -16838,7 +16892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L190" t="s">
         <v>345</v>
       </c>
@@ -16883,7 +16937,7 @@
       <c r="AD190" s="11"/>
       <c r="AE190" s="11"/>
       <c r="AF190" s="11"/>
-      <c r="AG190" s="31"/>
+      <c r="AG190" s="11"/>
       <c r="AH190" s="11">
         <v>40</v>
       </c>
@@ -16906,7 +16960,7 @@
       <c r="AS190" s="11"/>
       <c r="AT190" s="11"/>
       <c r="AU190" s="11"/>
-      <c r="AV190" s="31"/>
+      <c r="AV190" s="11"/>
       <c r="AW190">
         <v>2</v>
       </c>
@@ -16920,7 +16974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L191" t="s">
         <v>346</v>
       </c>
@@ -16984,7 +17038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="12:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L192" t="s">
         <v>347</v>
       </c>
@@ -17056,7 +17110,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L193" t="s">
         <v>348</v>
       </c>
@@ -17120,7 +17174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L194" t="s">
         <v>349</v>
       </c>
@@ -17167,7 +17221,7 @@
       <c r="AD194" s="11"/>
       <c r="AE194" s="11"/>
       <c r="AF194" s="11"/>
-      <c r="AG194" s="31"/>
+      <c r="AG194" s="11"/>
       <c r="AH194" s="11">
         <v>32</v>
       </c>
@@ -17192,7 +17246,7 @@
       <c r="AS194" s="11"/>
       <c r="AT194" s="11"/>
       <c r="AU194" s="11"/>
-      <c r="AV194" s="31"/>
+      <c r="AV194" s="11"/>
       <c r="AW194">
         <v>2</v>
       </c>
@@ -17209,7 +17263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L195" t="s">
         <v>350</v>
       </c>
@@ -17251,7 +17305,7 @@
       <c r="AD195" s="11"/>
       <c r="AE195" s="11"/>
       <c r="AF195" s="11"/>
-      <c r="AG195" s="31"/>
+      <c r="AG195" s="11"/>
       <c r="AH195" s="11">
         <v>16</v>
       </c>
@@ -17272,7 +17326,7 @@
       <c r="AS195" s="11"/>
       <c r="AT195" s="11"/>
       <c r="AU195" s="11"/>
-      <c r="AV195" s="31"/>
+      <c r="AV195" s="11"/>
       <c r="AW195">
         <v>1</v>
       </c>
@@ -17283,7 +17337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L196" t="s">
         <v>351</v>
       </c>
@@ -17314,7 +17368,6 @@
       <c r="U196">
         <v>22.5</v>
       </c>
-      <c r="AG196" s="30"/>
       <c r="AH196" s="11">
         <v>16</v>
       </c>
@@ -17335,7 +17388,7 @@
       <c r="AS196" s="11"/>
       <c r="AT196" s="11"/>
       <c r="AU196" s="11"/>
-      <c r="AV196" s="31"/>
+      <c r="AV196" s="11"/>
       <c r="AW196">
         <v>1</v>
       </c>
@@ -17346,7 +17399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L197" t="s">
         <v>352</v>
       </c>
@@ -17417,7 +17470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L198" t="s">
         <v>353</v>
       </c>
@@ -17459,7 +17512,7 @@
       <c r="AD198" s="11"/>
       <c r="AE198" s="11"/>
       <c r="AF198" s="11"/>
-      <c r="AG198" s="31"/>
+      <c r="AG198" s="11"/>
       <c r="AH198" s="11">
         <v>20</v>
       </c>
@@ -17480,7 +17533,7 @@
       <c r="AS198" s="11"/>
       <c r="AT198" s="11"/>
       <c r="AU198" s="11"/>
-      <c r="AV198" s="31"/>
+      <c r="AV198" s="11"/>
       <c r="AW198">
         <v>1</v>
       </c>
@@ -17491,7 +17544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L199" t="s">
         <v>354</v>
       </c>
@@ -17548,7 +17601,7 @@
       <c r="AD199" s="11"/>
       <c r="AE199" s="11"/>
       <c r="AF199" s="11"/>
-      <c r="AG199" s="31"/>
+      <c r="AG199" s="11"/>
       <c r="AH199" s="11">
         <v>32</v>
       </c>
@@ -17583,7 +17636,7 @@
       <c r="AS199" s="11"/>
       <c r="AT199" s="11"/>
       <c r="AU199" s="11"/>
-      <c r="AV199" s="31"/>
+      <c r="AV199" s="11"/>
       <c r="AW199">
         <v>2</v>
       </c>
@@ -17615,7 +17668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L200" t="s">
         <v>355</v>
       </c>
@@ -17665,7 +17718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L201" t="s">
         <v>356</v>
       </c>
@@ -17694,14 +17747,13 @@
       <c r="T201">
         <v>24</v>
       </c>
-      <c r="AG201" s="30"/>
       <c r="AH201" s="3">
         <v>16</v>
       </c>
       <c r="AI201">
         <v>16</v>
       </c>
-      <c r="AV201" s="29"/>
+      <c r="AV201" s="3"/>
       <c r="AW201">
         <v>1</v>
       </c>
@@ -17709,7 +17761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L202" t="s">
         <v>357</v>
       </c>
@@ -17776,7 +17828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L203" t="s">
         <v>358</v>
       </c>
@@ -17817,7 +17869,7 @@
       <c r="AD203" s="11"/>
       <c r="AE203" s="11"/>
       <c r="AF203" s="11"/>
-      <c r="AG203" s="31"/>
+      <c r="AG203" s="11"/>
       <c r="AH203" s="11">
         <v>16</v>
       </c>
@@ -17836,7 +17888,7 @@
       <c r="AS203" s="11"/>
       <c r="AT203" s="11"/>
       <c r="AU203" s="11"/>
-      <c r="AV203" s="31"/>
+      <c r="AV203" s="11"/>
       <c r="AW203">
         <v>1</v>
       </c>
@@ -17844,7 +17896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L204" t="s">
         <v>359</v>
       </c>
@@ -17894,7 +17946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L205" t="s">
         <v>360</v>
       </c>
@@ -17935,7 +17987,7 @@
       <c r="AD205" s="11"/>
       <c r="AE205" s="11"/>
       <c r="AF205" s="11"/>
-      <c r="AG205" s="31"/>
+      <c r="AG205" s="11"/>
       <c r="AH205" s="11">
         <v>16</v>
       </c>
@@ -17954,7 +18006,7 @@
       <c r="AS205" s="11"/>
       <c r="AT205" s="11"/>
       <c r="AU205" s="11"/>
-      <c r="AV205" s="31"/>
+      <c r="AV205" s="11"/>
       <c r="AW205">
         <v>1</v>
       </c>
@@ -17962,7 +18014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L206" t="s">
         <v>361</v>
       </c>
@@ -18000,7 +18052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L207" t="s">
         <v>362</v>
       </c>
@@ -18029,14 +18081,13 @@
       <c r="T207">
         <v>24</v>
       </c>
-      <c r="AG207" s="30"/>
       <c r="AH207" s="3">
         <v>16</v>
       </c>
       <c r="AI207">
         <v>16</v>
       </c>
-      <c r="AV207" s="29"/>
+      <c r="AV207" s="3"/>
       <c r="AW207">
         <v>1</v>
       </c>
@@ -18044,7 +18095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="12:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L208" t="s">
         <v>363</v>
       </c>
@@ -18082,7 +18133,6 @@
       <c r="W208">
         <v>48</v>
       </c>
-      <c r="AG208" s="30"/>
       <c r="AH208" s="11">
         <v>40</v>
       </c>
@@ -18107,7 +18157,7 @@
       <c r="AS208" s="11"/>
       <c r="AT208" s="11"/>
       <c r="AU208" s="11"/>
-      <c r="AV208" s="31"/>
+      <c r="AV208" s="11"/>
       <c r="AW208">
         <v>2</v>
       </c>
@@ -18124,7 +18174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L209" t="s">
         <v>364</v>
       </c>
@@ -18177,7 +18227,7 @@
       <c r="AD209" s="11"/>
       <c r="AE209" s="11"/>
       <c r="AF209" s="11"/>
-      <c r="AG209" s="31"/>
+      <c r="AG209" s="11"/>
       <c r="AH209" s="11">
         <v>32</v>
       </c>
@@ -18208,7 +18258,7 @@
       <c r="AS209" s="11"/>
       <c r="AT209" s="11"/>
       <c r="AU209" s="11"/>
-      <c r="AV209" s="31"/>
+      <c r="AV209" s="11"/>
       <c r="AW209">
         <v>2</v>
       </c>
@@ -18234,7 +18284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L210" t="s">
         <v>365</v>
       </c>
@@ -18280,7 +18330,6 @@
       <c r="Z210">
         <v>50</v>
       </c>
-      <c r="AG210" s="30"/>
       <c r="AH210" s="3">
         <v>40</v>
       </c>
@@ -18305,7 +18354,7 @@
       <c r="AO210">
         <v>40</v>
       </c>
-      <c r="AV210" s="29"/>
+      <c r="AV210" s="3"/>
       <c r="AW210">
         <v>2</v>
       </c>
@@ -18331,7 +18380,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L211" t="s">
         <v>366</v>
       </c>
@@ -18381,7 +18430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L212" t="s">
         <v>367</v>
       </c>
@@ -18413,7 +18462,6 @@
       <c r="U212">
         <v>25</v>
       </c>
-      <c r="AG212" s="30"/>
       <c r="AH212">
         <v>20</v>
       </c>
@@ -18423,7 +18471,6 @@
       <c r="AJ212">
         <v>20</v>
       </c>
-      <c r="AV212" s="30"/>
       <c r="AW212">
         <v>1</v>
       </c>
@@ -18434,7 +18481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L213" t="s">
         <v>368</v>
       </c>
@@ -18488,7 +18535,7 @@
       <c r="AD213" s="11"/>
       <c r="AE213" s="11"/>
       <c r="AF213" s="11"/>
-      <c r="AG213" s="31"/>
+      <c r="AG213" s="11"/>
       <c r="AH213" s="11">
         <v>26</v>
       </c>
@@ -18521,7 +18568,7 @@
       <c r="AS213" s="11"/>
       <c r="AT213" s="11"/>
       <c r="AU213" s="11"/>
-      <c r="AV213" s="31"/>
+      <c r="AV213" s="11"/>
       <c r="AW213">
         <v>2</v>
       </c>
@@ -18550,7 +18597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L214" t="s">
         <v>369</v>
       </c>
@@ -18678,7 +18725,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L215" t="s">
         <v>370</v>
       </c>
@@ -18707,14 +18754,12 @@
       <c r="T215">
         <v>20</v>
       </c>
-      <c r="AG215" s="30"/>
       <c r="AH215">
         <v>32</v>
       </c>
       <c r="AI215">
         <v>16</v>
       </c>
-      <c r="AV215" s="30"/>
       <c r="AW215">
         <v>2</v>
       </c>
@@ -18722,7 +18767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L216" t="s">
         <v>371</v>
       </c>
@@ -18751,14 +18796,12 @@
       <c r="T216">
         <v>40</v>
       </c>
-      <c r="AG216" s="30"/>
       <c r="AH216">
         <v>32</v>
       </c>
       <c r="AI216">
         <v>32</v>
       </c>
-      <c r="AV216" s="30"/>
       <c r="AW216">
         <v>2</v>
       </c>
@@ -18766,7 +18809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L217" t="s">
         <v>372</v>
       </c>
@@ -18795,14 +18838,12 @@
       <c r="T217">
         <v>40</v>
       </c>
-      <c r="AG217" s="30"/>
       <c r="AH217">
         <v>32</v>
       </c>
       <c r="AI217">
         <v>32</v>
       </c>
-      <c r="AV217" s="30"/>
       <c r="AW217">
         <v>2</v>
       </c>
@@ -18810,7 +18851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L218" t="s">
         <v>373</v>
       </c>
@@ -18944,7 +18985,7 @@
       </c>
       <c r="BI218" s="22"/>
     </row>
-    <row r="219" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L219" t="s">
         <v>374</v>
       </c>
@@ -18962,7 +19003,7 @@
       </c>
       <c r="Q219" s="15"/>
       <c r="R219" s="15"/>
-      <c r="S219" s="30">
+      <c r="S219">
         <v>40</v>
       </c>
       <c r="T219">
@@ -18987,7 +19028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L220" t="s">
         <v>375</v>
       </c>
@@ -19010,7 +19051,7 @@
       <c r="R220" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="S220" s="30">
+      <c r="S220">
         <v>40</v>
       </c>
       <c r="T220">
@@ -19019,7 +19060,6 @@
       <c r="U220">
         <v>40</v>
       </c>
-      <c r="AG220" s="30"/>
       <c r="AH220">
         <v>30</v>
       </c>
@@ -19029,7 +19069,6 @@
       <c r="AJ220">
         <v>30</v>
       </c>
-      <c r="AV220" s="30"/>
       <c r="AW220">
         <v>2</v>
       </c>
@@ -19040,7 +19079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L221" t="s">
         <v>376</v>
       </c>
@@ -19063,7 +19102,7 @@
       <c r="R221" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="S221" s="30">
+      <c r="S221">
         <v>40</v>
       </c>
       <c r="T221">
@@ -19072,7 +19111,6 @@
       <c r="U221">
         <v>40</v>
       </c>
-      <c r="AG221" s="30"/>
       <c r="AH221">
         <v>30</v>
       </c>
@@ -19082,7 +19120,6 @@
       <c r="AJ221">
         <v>30</v>
       </c>
-      <c r="AV221" s="30"/>
       <c r="AW221">
         <v>2</v>
       </c>
@@ -19093,7 +19130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L222" t="s">
         <v>377</v>
       </c>
@@ -19227,7 +19264,7 @@
       </c>
       <c r="BI222" s="22"/>
     </row>
-    <row r="223" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L223" t="s">
         <v>378</v>
       </c>
@@ -19361,7 +19398,7 @@
       </c>
       <c r="BI223" s="22"/>
     </row>
-    <row r="224" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="12:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L224" t="s">
         <v>379</v>
       </c>
@@ -19384,7 +19421,7 @@
       <c r="R224" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="S224" s="30">
+      <c r="S224">
         <v>40</v>
       </c>
       <c r="T224">
@@ -19396,7 +19433,6 @@
       <c r="V224">
         <v>40</v>
       </c>
-      <c r="AG224" s="30"/>
       <c r="AH224">
         <v>30</v>
       </c>
@@ -19409,7 +19445,6 @@
       <c r="AK224">
         <v>30</v>
       </c>
-      <c r="AV224" s="30"/>
       <c r="AW224">
         <v>2</v>
       </c>
@@ -19423,7 +19458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L225" t="s">
         <v>380</v>
       </c>
@@ -19445,7 +19480,7 @@
       <c r="R225" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="S225" s="30">
+      <c r="S225">
         <v>40</v>
       </c>
       <c r="T225">
@@ -19457,7 +19492,6 @@
       <c r="V225">
         <v>40</v>
       </c>
-      <c r="AG225" s="30"/>
       <c r="AH225">
         <v>30</v>
       </c>
@@ -19470,7 +19504,6 @@
       <c r="AK225">
         <v>30</v>
       </c>
-      <c r="AV225" s="30"/>
       <c r="AW225">
         <v>2</v>
       </c>
@@ -19484,7 +19517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L226" t="s">
         <v>381</v>
       </c>
@@ -19507,20 +19540,18 @@
       <c r="R226" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="S226" s="30">
+      <c r="S226">
         <v>25</v>
       </c>
       <c r="T226">
         <v>25</v>
       </c>
-      <c r="AG226" s="30"/>
       <c r="AH226">
         <v>20</v>
       </c>
       <c r="AI226">
         <v>20</v>
       </c>
-      <c r="AV226" s="30"/>
       <c r="AW226">
         <v>1</v>
       </c>
@@ -19528,7 +19559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L227" t="s">
         <v>382</v>
       </c>
@@ -19620,7 +19651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L228" t="s">
         <v>383</v>
       </c>
@@ -19643,20 +19674,18 @@
       <c r="R228" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="S228" s="30">
+      <c r="S228">
         <v>25</v>
       </c>
       <c r="T228">
         <v>25</v>
       </c>
-      <c r="AG228" s="30"/>
       <c r="AH228">
         <v>20</v>
       </c>
       <c r="AI228">
         <v>20</v>
       </c>
-      <c r="AV228" s="30"/>
       <c r="AW228">
         <v>1</v>
       </c>
@@ -19664,7 +19693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L229" t="s">
         <v>384</v>
       </c>
@@ -19687,7 +19716,7 @@
       <c r="R229" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="S229" s="30">
+      <c r="S229">
         <v>25</v>
       </c>
       <c r="T229">
@@ -19696,7 +19725,6 @@
       <c r="U229">
         <v>25</v>
       </c>
-      <c r="AG229" s="30"/>
       <c r="AH229">
         <v>20</v>
       </c>
@@ -19706,7 +19734,6 @@
       <c r="AJ229">
         <v>20</v>
       </c>
-      <c r="AV229" s="30"/>
       <c r="AW229">
         <v>1</v>
       </c>
@@ -19717,7 +19744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L230" t="s">
         <v>385</v>
       </c>
@@ -19833,7 +19860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L231" t="s">
         <v>386</v>
       </c>
@@ -19851,7 +19878,7 @@
       </c>
       <c r="Q231" s="15"/>
       <c r="R231" s="15"/>
-      <c r="S231" s="30">
+      <c r="S231">
         <v>40</v>
       </c>
       <c r="T231">
@@ -19875,7 +19902,6 @@
       <c r="Z231">
         <v>40</v>
       </c>
-      <c r="AG231" s="30"/>
       <c r="AH231">
         <v>30</v>
       </c>
@@ -19900,7 +19926,6 @@
       <c r="AO231">
         <v>30</v>
       </c>
-      <c r="AV231" s="30"/>
       <c r="AW231">
         <v>2</v>
       </c>
@@ -19926,967 +19951,967 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q232" s="15"/>
       <c r="R232" s="15"/>
     </row>
-    <row r="233" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q233" s="4"/>
       <c r="R233" s="4"/>
     </row>
-    <row r="234" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q234" s="15"/>
       <c r="R234" s="15"/>
     </row>
-    <row r="235" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q235" s="4"/>
       <c r="R235" s="4"/>
     </row>
-    <row r="236" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q236" s="15"/>
       <c r="R236" s="15"/>
     </row>
-    <row r="237" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q237" s="4"/>
       <c r="R237" s="4"/>
     </row>
-    <row r="238" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q238" s="15"/>
       <c r="R238" s="15"/>
     </row>
-    <row r="239" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q239" s="4"/>
       <c r="R239" s="4"/>
     </row>
-    <row r="240" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q240" s="15"/>
       <c r="R240" s="15"/>
     </row>
-    <row r="241" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q241" s="4"/>
       <c r="R241" s="4"/>
     </row>
-    <row r="242" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q242" s="15"/>
       <c r="R242" s="15"/>
     </row>
-    <row r="243" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q243" s="4"/>
       <c r="R243" s="4"/>
     </row>
-    <row r="244" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q244" s="15"/>
       <c r="R244" s="15"/>
     </row>
-    <row r="245" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q245" s="4"/>
       <c r="R245" s="4"/>
     </row>
-    <row r="246" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q246" s="15"/>
       <c r="R246" s="15"/>
     </row>
-    <row r="247" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q247" s="4"/>
       <c r="R247" s="4"/>
     </row>
-    <row r="248" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q248" s="15"/>
       <c r="R248" s="15"/>
     </row>
-    <row r="249" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q249" s="4"/>
       <c r="R249" s="4"/>
     </row>
-    <row r="250" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q250" s="15"/>
       <c r="R250" s="15"/>
     </row>
-    <row r="251" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q251" s="4"/>
       <c r="R251" s="4"/>
     </row>
-    <row r="252" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q252" s="15"/>
       <c r="R252" s="15"/>
     </row>
-    <row r="253" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q253" s="4"/>
       <c r="R253" s="4"/>
     </row>
-    <row r="254" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q254" s="15"/>
       <c r="R254" s="15"/>
     </row>
-    <row r="255" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q255" s="4"/>
       <c r="R255" s="4"/>
     </row>
-    <row r="256" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q256" s="15"/>
       <c r="R256" s="15"/>
     </row>
-    <row r="257" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q257" s="4"/>
       <c r="R257" s="4"/>
     </row>
-    <row r="258" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q258" s="15"/>
       <c r="R258" s="15"/>
     </row>
-    <row r="259" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q259" s="4"/>
       <c r="R259" s="4"/>
     </row>
-    <row r="260" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q260" s="15"/>
       <c r="R260" s="15"/>
     </row>
-    <row r="261" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q261" s="4"/>
       <c r="R261" s="4"/>
     </row>
-    <row r="262" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q262" s="15"/>
       <c r="R262" s="15"/>
     </row>
-    <row r="263" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q263" s="4"/>
       <c r="R263" s="4"/>
     </row>
-    <row r="264" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q264" s="15"/>
       <c r="R264" s="15"/>
     </row>
-    <row r="265" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q265" s="4"/>
       <c r="R265" s="4"/>
     </row>
-    <row r="266" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q266" s="15"/>
       <c r="R266" s="15"/>
     </row>
-    <row r="267" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q267" s="4"/>
       <c r="R267" s="4"/>
     </row>
-    <row r="268" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q268" s="15"/>
       <c r="R268" s="15"/>
     </row>
-    <row r="269" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q269" s="4"/>
       <c r="R269" s="4"/>
     </row>
-    <row r="270" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q270" s="15"/>
       <c r="R270" s="15"/>
     </row>
-    <row r="271" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q271" s="4"/>
       <c r="R271" s="4"/>
     </row>
-    <row r="272" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q272" s="15"/>
       <c r="R272" s="15"/>
     </row>
-    <row r="273" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q273" s="4"/>
       <c r="R273" s="4"/>
     </row>
-    <row r="274" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q274" s="15"/>
       <c r="R274" s="15"/>
     </row>
-    <row r="275" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q275" s="4"/>
       <c r="R275" s="4"/>
     </row>
-    <row r="276" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q276" s="15"/>
       <c r="R276" s="15"/>
     </row>
-    <row r="277" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q277" s="4"/>
       <c r="R277" s="4"/>
     </row>
-    <row r="278" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q278" s="15"/>
       <c r="R278" s="15"/>
     </row>
-    <row r="279" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q279" s="4"/>
       <c r="R279" s="4"/>
     </row>
-    <row r="280" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q280" s="15"/>
       <c r="R280" s="15"/>
     </row>
-    <row r="281" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q281" s="4"/>
       <c r="R281" s="4"/>
     </row>
-    <row r="282" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q282" s="15"/>
       <c r="R282" s="15"/>
     </row>
-    <row r="283" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q283" s="4"/>
       <c r="R283" s="4"/>
     </row>
-    <row r="284" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q284" s="15"/>
       <c r="R284" s="15"/>
     </row>
-    <row r="285" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q285" s="4"/>
       <c r="R285" s="4"/>
     </row>
-    <row r="286" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q286" s="15"/>
       <c r="R286" s="15"/>
     </row>
-    <row r="287" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q287" s="4"/>
       <c r="R287" s="4"/>
     </row>
-    <row r="288" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q288" s="15"/>
       <c r="R288" s="15"/>
     </row>
-    <row r="289" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q289" s="4"/>
       <c r="R289" s="4"/>
     </row>
-    <row r="290" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q290" s="15"/>
       <c r="R290" s="15"/>
     </row>
-    <row r="291" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q291" s="4"/>
       <c r="R291" s="4"/>
     </row>
-    <row r="292" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q292" s="15"/>
       <c r="R292" s="15"/>
     </row>
-    <row r="293" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q293" s="4"/>
       <c r="R293" s="4"/>
     </row>
-    <row r="294" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q294" s="15"/>
       <c r="R294" s="15"/>
     </row>
-    <row r="295" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q295" s="4"/>
       <c r="R295" s="4"/>
     </row>
-    <row r="296" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" spans="17:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="G3:G208">
     <cfRule type="colorScale" priority="29">
@@ -20928,11 +20953,11 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157500000008" bottom="0.78740157500000008" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <tableParts count="2">
-    <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
--- a/calculo_mppt.xlsx
+++ b/calculo_mppt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enzo.ferreira\Desktop\dimensionador-fotovoltaico-sigiloso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211A1C91-F660-4B36-B9E3-A35A52CD6B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA894103-B550-469E-99B7-262CC8F22CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-4695" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="414">
   <si>
     <t>Módulo</t>
   </si>
@@ -1580,6 +1580,12 @@
   </si>
   <si>
     <t>Hanersun 710W - HN21N-66HT710W</t>
+  </si>
+  <si>
+    <t>BYD 610 BF TC AL 35 (BYD610TUI66T)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229366	</t>
   </si>
 </sst>
 </file>
@@ -12033,6 +12039,33 @@
       </c>
     </row>
     <row r="115" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C115" s="1">
+        <v>610</v>
+      </c>
+      <c r="D115" s="1">
+        <v>48.94</v>
+      </c>
+      <c r="E115" s="1">
+        <v>41.22</v>
+      </c>
+      <c r="F115" s="1">
+        <v>-0.25</v>
+      </c>
+      <c r="G115" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="H115" s="1">
+        <v>15.44</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="L115" s="1" t="s">
         <v>270</v>
       </c>

--- a/calculo_mppt.xlsx
+++ b/calculo_mppt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enzo.ferreira\Desktop\dimensionador-fotovoltaico-sigiloso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA894103-B550-469E-99B7-262CC8F22CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A0302A-995D-4F30-969A-58985044C99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-4695" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="421">
   <si>
     <t>Módulo</t>
   </si>
@@ -1586,6 +1586,27 @@
   </si>
   <si>
     <t xml:space="preserve">229366	</t>
+  </si>
+  <si>
+    <t>SUNGROW 40KW T380 (SG40CX-P2) AFCI G</t>
+  </si>
+  <si>
+    <t>KEHUA 50KW T380 ON (SPI50K-B) G</t>
+  </si>
+  <si>
+    <t>KEHUA 100KW T380 ON (SPI100K-B) G</t>
+  </si>
+  <si>
+    <t>NANSEN 50KW T380 (ASN-50TL-G2) G</t>
+  </si>
+  <si>
+    <t>SUNGROW 40KW T380 (SG40CX-P2) G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206206	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206195	</t>
   </si>
 </sst>
 </file>
@@ -2777,30 +2798,30 @@
     </row>
     <row r="5" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="C5" s="1">
-        <v>605</v>
-      </c>
-      <c r="D5" s="1">
-        <v>47.39</v>
-      </c>
-      <c r="E5" s="1">
-        <v>39.799999999999997</v>
+        <v>396</v>
+      </c>
+      <c r="C5" s="4">
+        <v>620</v>
+      </c>
+      <c r="D5" s="4">
+        <v>47.98</v>
+      </c>
+      <c r="E5" s="4">
+        <v>40.39</v>
       </c>
       <c r="F5" s="4">
         <v>-0.25</v>
       </c>
-      <c r="G5" s="1">
-        <v>15.2</v>
-      </c>
-      <c r="H5" s="1">
-        <v>16.16</v>
-      </c>
-      <c r="I5" s="1">
-        <v>228604</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="G5" s="4">
+        <v>15.35</v>
+      </c>
+      <c r="H5" s="4">
+        <v>16.3</v>
+      </c>
+      <c r="I5" s="4">
+        <v>179728</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>62</v>
       </c>
       <c r="L5" s="1" t="s">
@@ -2846,31 +2867,31 @@
       </c>
     </row>
     <row r="6" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="C6" s="4">
-        <v>620</v>
-      </c>
-      <c r="D6" s="4">
-        <v>47.98</v>
-      </c>
-      <c r="E6" s="4">
-        <v>40.39</v>
-      </c>
-      <c r="F6" s="4">
-        <v>-0.25</v>
-      </c>
-      <c r="G6" s="4">
-        <v>15.35</v>
-      </c>
-      <c r="H6" s="4">
-        <v>16.3</v>
-      </c>
-      <c r="I6" s="4">
-        <v>179728</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="B6" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C6" s="1">
+        <v>610</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="F6" s="1">
+        <v>-0.24</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>62</v>
       </c>
       <c r="L6" s="1" t="s">
@@ -2918,28 +2939,28 @@
     </row>
     <row r="7" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C7" s="1">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F7" s="1">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>62</v>
@@ -2985,28 +3006,28 @@
     </row>
     <row r="8" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="C8" s="1">
-        <v>620</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>407</v>
+        <v>610</v>
+      </c>
+      <c r="D8" s="1">
+        <v>48.94</v>
+      </c>
+      <c r="E8" s="1">
+        <v>41.22</v>
       </c>
       <c r="F8" s="1">
         <v>-0.25</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>410</v>
+      <c r="G8" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="H8" s="1">
+        <v>15.44</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>62</v>
@@ -3126,29 +3147,29 @@
       </c>
     </row>
     <row r="10" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
-        <v>265</v>
+      <c r="B10" s="4" t="s">
+        <v>228</v>
       </c>
       <c r="C10" s="1">
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="D10" s="1">
-        <v>48.34</v>
+        <v>47.39</v>
       </c>
       <c r="E10" s="1">
-        <v>40.479999999999997</v>
-      </c>
-      <c r="F10" s="1">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="F10" s="4">
         <v>-0.25</v>
       </c>
       <c r="G10" s="1">
-        <v>15.33</v>
+        <v>15.2</v>
       </c>
       <c r="H10" s="1">
-        <v>16.21</v>
+        <v>16.16</v>
       </c>
       <c r="I10" s="1">
-        <v>213692</v>
+        <v>228604</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>69</v>
@@ -3191,28 +3212,29 @@
     </row>
     <row r="11" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C11" s="4">
-        <v>530</v>
-      </c>
-      <c r="D11" s="4">
-        <v>46.3</v>
-      </c>
-      <c r="E11" s="4">
-        <v>38.799999999999997</v>
-      </c>
-      <c r="F11" s="4">
-        <v>-0.28000000000000003</v>
-      </c>
-      <c r="G11" s="4">
-        <v>13.67</v>
-      </c>
-      <c r="H11" s="4">
-        <v>14.49</v>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+        <v>265</v>
+      </c>
+      <c r="C11" s="1">
+        <v>620</v>
+      </c>
+      <c r="D11" s="1">
+        <v>48.34</v>
+      </c>
+      <c r="E11" s="1">
+        <v>40.479999999999997</v>
+      </c>
+      <c r="F11" s="1">
+        <v>-0.25</v>
+      </c>
+      <c r="G11" s="1">
+        <v>15.33</v>
+      </c>
+      <c r="H11" s="1">
+        <v>16.21</v>
+      </c>
+      <c r="I11" s="1">
+        <v>213692</v>
+      </c>
       <c r="L11" s="1" t="s">
         <v>70</v>
       </c>
@@ -3258,25 +3280,25 @@
     </row>
     <row r="12" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C12" s="4">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="D12" s="4">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="E12" s="4">
-        <v>39</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="F12" s="4">
         <v>-0.28000000000000003</v>
       </c>
       <c r="G12" s="4">
-        <v>13.71</v>
+        <v>13.67</v>
       </c>
       <c r="H12" s="4">
-        <v>14.45</v>
+        <v>14.49</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -3321,25 +3343,25 @@
     </row>
     <row r="13" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>263</v>
+        <v>391</v>
       </c>
       <c r="C13" s="4">
-        <v>640</v>
+        <v>535</v>
       </c>
       <c r="D13" s="4">
-        <v>57.4</v>
+        <v>46.5</v>
       </c>
       <c r="E13" s="4">
-        <v>48.71</v>
+        <v>39</v>
       </c>
       <c r="F13" s="4">
-        <v>-0.24</v>
+        <v>-0.28000000000000003</v>
       </c>
       <c r="G13" s="4">
-        <v>13.14</v>
+        <v>13.71</v>
       </c>
       <c r="H13" s="4">
-        <v>13.98</v>
+        <v>14.45</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -3406,25 +3428,25 @@
     </row>
     <row r="14" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="1">
-        <v>550</v>
-      </c>
-      <c r="D14" s="1">
-        <v>49.8</v>
-      </c>
-      <c r="E14" s="1">
-        <v>42.16</v>
-      </c>
-      <c r="F14" s="1">
-        <v>-0.28999999999999998</v>
+        <v>263</v>
+      </c>
+      <c r="C14" s="4">
+        <v>640</v>
+      </c>
+      <c r="D14" s="4">
+        <v>57.4</v>
+      </c>
+      <c r="E14" s="4">
+        <v>48.71</v>
+      </c>
+      <c r="F14" s="4">
+        <v>-0.24</v>
       </c>
       <c r="G14" s="4">
-        <v>13.05</v>
+        <v>13.14</v>
       </c>
       <c r="H14" s="4">
-        <v>13.94</v>
+        <v>13.98</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
@@ -3482,25 +3504,25 @@
     </row>
     <row r="15" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C15" s="1">
-        <v>370</v>
+        <v>550</v>
       </c>
       <c r="D15" s="1">
-        <v>47.4</v>
+        <v>49.8</v>
       </c>
       <c r="E15" s="1">
-        <v>40</v>
+        <v>42.16</v>
       </c>
       <c r="F15" s="1">
         <v>-0.28999999999999998</v>
       </c>
       <c r="G15" s="4">
-        <v>9.26</v>
+        <v>13.05</v>
       </c>
       <c r="H15" s="4">
-        <v>9.83</v>
+        <v>13.94</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -3554,25 +3576,25 @@
     </row>
     <row r="16" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C16" s="1">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="D16" s="1">
-        <v>47.2</v>
+        <v>47.4</v>
       </c>
       <c r="E16" s="1">
-        <v>38.700000000000003</v>
+        <v>40</v>
       </c>
       <c r="F16" s="1">
-        <v>-0.28000000000000003</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="G16" s="4">
-        <v>10.34</v>
+        <v>9.26</v>
       </c>
       <c r="H16" s="4">
-        <v>10.9</v>
+        <v>9.83</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
@@ -3624,25 +3646,25 @@
     </row>
     <row r="17" spans="2:60" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C17" s="1">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D17" s="1">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="E17" s="1">
-        <v>38.9</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="F17" s="1">
         <v>-0.28000000000000003</v>
       </c>
       <c r="G17" s="4">
-        <v>10.42</v>
+        <v>10.34</v>
       </c>
       <c r="H17" s="4">
-        <v>10.98</v>
+        <v>10.9</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
@@ -3708,25 +3730,25 @@
     </row>
     <row r="18" spans="2:60" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C18" s="1">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="D18" s="1">
-        <v>48</v>
+        <v>47.4</v>
       </c>
       <c r="E18" s="1">
-        <v>39.5</v>
+        <v>38.9</v>
       </c>
       <c r="F18" s="1">
         <v>-0.28000000000000003</v>
       </c>
       <c r="G18" s="4">
-        <v>10.64</v>
+        <v>10.42</v>
       </c>
       <c r="H18" s="4">
-        <v>11.26</v>
+        <v>10.98</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
@@ -3774,25 +3796,25 @@
     </row>
     <row r="19" spans="2:60" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C19" s="1">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D19" s="1">
-        <v>52.9</v>
+        <v>48</v>
       </c>
       <c r="E19" s="1">
-        <v>40.5</v>
+        <v>39.5</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.27</v>
+        <v>-0.28000000000000003</v>
       </c>
       <c r="G19" s="4">
-        <v>9.82</v>
+        <v>10.64</v>
       </c>
       <c r="H19" s="4">
-        <v>10.46</v>
+        <v>11.26</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
@@ -3848,25 +3870,25 @@
     </row>
     <row r="20" spans="2:60" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C20" s="1">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D20" s="1">
-        <v>53.1</v>
+        <v>52.9</v>
       </c>
       <c r="E20" s="1">
-        <v>40.700000000000003</v>
+        <v>40.5</v>
       </c>
       <c r="F20" s="1">
         <v>-0.27</v>
       </c>
       <c r="G20" s="4">
-        <v>9.89</v>
+        <v>9.82</v>
       </c>
       <c r="H20" s="4">
-        <v>10.52</v>
+        <v>10.46</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
@@ -3914,25 +3936,25 @@
     </row>
     <row r="21" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C21" s="1">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D21" s="1">
-        <v>48.9</v>
+        <v>53.1</v>
       </c>
       <c r="E21" s="1">
-        <v>40.9</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="F21" s="1">
         <v>-0.27</v>
       </c>
       <c r="G21" s="4">
-        <v>10.89</v>
+        <v>9.89</v>
       </c>
       <c r="H21" s="4">
-        <v>11.54</v>
+        <v>10.52</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
@@ -3992,25 +4014,25 @@
     </row>
     <row r="22" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C22" s="1">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="D22" s="1">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="E22" s="1">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="F22" s="1">
         <v>-0.27</v>
       </c>
       <c r="G22" s="4">
-        <v>10.96</v>
+        <v>10.89</v>
       </c>
       <c r="H22" s="4">
-        <v>11.6</v>
+        <v>11.54</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -4076,25 +4098,25 @@
     </row>
     <row r="23" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C23" s="1">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D23" s="1">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="E23" s="1">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="F23" s="1">
         <v>-0.27</v>
       </c>
       <c r="G23" s="4">
-        <v>11.02</v>
+        <v>10.96</v>
       </c>
       <c r="H23" s="4">
-        <v>11.66</v>
+        <v>11.6</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
@@ -4196,25 +4218,25 @@
     </row>
     <row r="24" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C24" s="1">
-        <v>535</v>
+        <v>455</v>
       </c>
       <c r="D24" s="1">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="E24" s="1">
-        <v>40.799999999999997</v>
+        <v>41.3</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="G24" s="4">
-        <v>13.02</v>
+        <v>11.02</v>
       </c>
       <c r="H24" s="4">
-        <v>13.85</v>
+        <v>11.66</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
@@ -4337,26 +4359,26 @@
       </c>
     </row>
     <row r="25" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="14" t="s">
-        <v>99</v>
+      <c r="B25" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="C25" s="1">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="D25" s="1">
-        <v>49.8</v>
+        <v>49</v>
       </c>
       <c r="E25" s="1">
-        <v>41.93</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="F25" s="1">
-        <v>-0.28000000000000003</v>
+        <v>-0.26</v>
       </c>
       <c r="G25" s="4">
-        <v>13.12</v>
+        <v>13.02</v>
       </c>
       <c r="H25" s="4">
-        <v>13.88</v>
+        <v>13.85</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
@@ -4479,23 +4501,27 @@
       </c>
     </row>
     <row r="26" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
-        <v>101</v>
+      <c r="B26" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="C26" s="1">
         <v>550</v>
       </c>
       <c r="D26" s="1">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
       <c r="E26" s="1">
-        <v>41.7</v>
+        <v>41.93</v>
       </c>
       <c r="F26" s="1">
-        <v>-0.26</v>
-      </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="G26" s="4">
+        <v>13.12</v>
+      </c>
+      <c r="H26" s="4">
+        <v>13.88</v>
+      </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
       <c r="L26" s="1" t="s">
@@ -4562,26 +4588,22 @@
     </row>
     <row r="27" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C27" s="1">
         <v>550</v>
       </c>
       <c r="D27" s="1">
-        <v>50.2</v>
+        <v>49.6</v>
       </c>
       <c r="E27" s="1">
-        <v>42.4</v>
+        <v>41.7</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.31</v>
-      </c>
-      <c r="G27" s="4">
-        <v>12.97</v>
-      </c>
-      <c r="H27" s="4">
-        <v>13.78</v>
-      </c>
+        <v>-0.26</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="L27" s="1" t="s">
@@ -4648,25 +4670,25 @@
     </row>
     <row r="28" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" s="4">
-        <v>610</v>
-      </c>
-      <c r="D28" s="4">
-        <v>48.2</v>
-      </c>
-      <c r="E28" s="4">
-        <v>40.9</v>
-      </c>
-      <c r="F28" s="4">
-        <v>-0.25</v>
+        <v>103</v>
+      </c>
+      <c r="C28" s="1">
+        <v>550</v>
+      </c>
+      <c r="D28" s="1">
+        <v>50.2</v>
+      </c>
+      <c r="E28" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="F28" s="1">
+        <v>-0.31</v>
       </c>
       <c r="G28" s="4">
-        <v>14.91</v>
+        <v>12.97</v>
       </c>
       <c r="H28" s="4">
-        <v>15.88</v>
+        <v>13.78</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -4733,26 +4755,26 @@
       </c>
     </row>
     <row r="29" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="4" t="s">
-        <v>107</v>
+      <c r="B29" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C29" s="4">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="D29" s="4">
-        <v>50.26</v>
+        <v>48.2</v>
       </c>
       <c r="E29" s="4">
-        <v>42.14</v>
+        <v>40.9</v>
       </c>
       <c r="F29" s="4">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="G29" s="4">
-        <v>16.61</v>
+        <v>14.91</v>
       </c>
       <c r="H29" s="4">
-        <v>17.39</v>
+        <v>15.88</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
@@ -4885,26 +4907,26 @@
       </c>
     </row>
     <row r="30" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
-        <v>109</v>
+      <c r="B30" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="C30" s="4">
         <v>700</v>
       </c>
       <c r="D30" s="4">
-        <v>49.73</v>
+        <v>50.26</v>
       </c>
       <c r="E30" s="4">
-        <v>41.81</v>
+        <v>42.14</v>
       </c>
       <c r="F30" s="4">
         <v>-0.24</v>
       </c>
       <c r="G30" s="4">
-        <v>16.75</v>
+        <v>16.61</v>
       </c>
       <c r="H30" s="4">
-        <v>17.78</v>
+        <v>17.39</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -4989,25 +5011,25 @@
     </row>
     <row r="31" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>392</v>
+        <v>109</v>
       </c>
       <c r="C31" s="4">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="D31" s="4">
-        <v>48</v>
+        <v>49.73</v>
       </c>
       <c r="E31" s="4">
-        <v>40.4</v>
+        <v>41.81</v>
       </c>
       <c r="F31" s="4">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="G31" s="4">
-        <v>17.57</v>
+        <v>16.75</v>
       </c>
       <c r="H31" s="4">
-        <v>18.61</v>
+        <v>17.78</v>
       </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
@@ -5084,25 +5106,25 @@
     </row>
     <row r="32" spans="2:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" s="1">
-        <v>440</v>
-      </c>
-      <c r="D32" s="1">
-        <v>49</v>
-      </c>
-      <c r="E32" s="1">
-        <v>41.81</v>
-      </c>
-      <c r="F32" s="1">
-        <v>-0.31</v>
+        <v>392</v>
+      </c>
+      <c r="C32" s="4">
+        <v>710</v>
+      </c>
+      <c r="D32" s="4">
+        <v>48</v>
+      </c>
+      <c r="E32" s="4">
+        <v>40.4</v>
+      </c>
+      <c r="F32" s="4">
+        <v>-0.25</v>
       </c>
       <c r="G32" s="4">
-        <v>10.52</v>
+        <v>17.57</v>
       </c>
       <c r="H32" s="4">
-        <v>11.29</v>
+        <v>18.61</v>
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -5170,25 +5192,25 @@
     </row>
     <row r="33" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C33" s="1">
-        <v>540</v>
+        <v>440</v>
       </c>
       <c r="D33" s="1">
-        <v>49.8</v>
+        <v>49</v>
       </c>
       <c r="E33" s="1">
-        <v>42</v>
+        <v>41.81</v>
       </c>
       <c r="F33" s="1">
         <v>-0.31</v>
       </c>
       <c r="G33" s="4">
-        <v>12.86</v>
+        <v>10.52</v>
       </c>
       <c r="H33" s="4">
-        <v>13.66</v>
+        <v>11.29</v>
       </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
@@ -5273,25 +5295,25 @@
     </row>
     <row r="34" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C34" s="1">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="D34" s="1">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="E34" s="1">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="F34" s="1">
         <v>-0.31</v>
       </c>
       <c r="G34" s="4">
-        <v>12.91</v>
+        <v>12.86</v>
       </c>
       <c r="H34" s="4">
-        <v>13.72</v>
+        <v>13.66</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
@@ -5365,26 +5387,26 @@
       </c>
     </row>
     <row r="35" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="14" t="s">
-        <v>117</v>
+      <c r="B35" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C35" s="1">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="D35" s="1">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="E35" s="1">
-        <v>42.6</v>
+        <v>42.2</v>
       </c>
       <c r="F35" s="1">
         <v>-0.31</v>
       </c>
       <c r="G35" s="4">
-        <v>13.03</v>
+        <v>12.91</v>
       </c>
       <c r="H35" s="4">
-        <v>13.84</v>
+        <v>13.72</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -5452,25 +5474,25 @@
     </row>
     <row r="36" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C36" s="1">
-        <v>450</v>
+        <v>555</v>
       </c>
       <c r="D36" s="1">
-        <v>49.3</v>
+        <v>50.4</v>
       </c>
       <c r="E36" s="1">
-        <v>42.1</v>
+        <v>42.6</v>
       </c>
       <c r="F36" s="1">
         <v>-0.31</v>
       </c>
       <c r="G36" s="4">
-        <v>10.69</v>
+        <v>13.03</v>
       </c>
       <c r="H36" s="4">
-        <v>11.35</v>
+        <v>13.84</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
@@ -5530,26 +5552,26 @@
       </c>
     </row>
     <row r="37" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="1" t="s">
-        <v>121</v>
+      <c r="B37" s="14" t="s">
+        <v>119</v>
       </c>
       <c r="C37" s="1">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="D37" s="1">
-        <v>47.2</v>
+        <v>49.3</v>
       </c>
       <c r="E37" s="1">
-        <v>38.4</v>
+        <v>42.1</v>
       </c>
       <c r="F37" s="1">
         <v>-0.31</v>
       </c>
       <c r="G37" s="4">
-        <v>9.3800000000000008</v>
+        <v>10.69</v>
       </c>
       <c r="H37" s="4">
-        <v>9.7799999999999994</v>
+        <v>11.35</v>
       </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
@@ -5631,25 +5653,25 @@
     </row>
     <row r="38" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C38" s="1">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="D38" s="1">
-        <v>51.4</v>
+        <v>47.2</v>
       </c>
       <c r="E38" s="1">
-        <v>42</v>
+        <v>38.4</v>
       </c>
       <c r="F38" s="1">
         <v>-0.31</v>
       </c>
       <c r="G38" s="4">
-        <v>9.35</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="H38" s="4">
-        <v>9.8699999999999992</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
@@ -5716,26 +5738,26 @@
       </c>
     </row>
     <row r="39" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="14" t="s">
-        <v>125</v>
+      <c r="B39" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="C39" s="1">
-        <v>560</v>
+        <v>400</v>
       </c>
       <c r="D39" s="1">
-        <v>50.19</v>
+        <v>51.4</v>
       </c>
       <c r="E39" s="1">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.246</v>
+        <v>-0.31</v>
       </c>
       <c r="G39" s="4">
-        <v>13.4</v>
+        <v>9.35</v>
       </c>
       <c r="H39" s="4">
-        <v>14.25</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
@@ -5804,25 +5826,25 @@
     </row>
     <row r="40" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C40" s="1">
-        <v>585</v>
+        <v>560</v>
       </c>
       <c r="D40" s="1">
-        <v>52.7</v>
+        <v>50.19</v>
       </c>
       <c r="E40" s="1">
-        <v>44.04</v>
+        <v>41.8</v>
       </c>
       <c r="F40" s="1">
-        <v>-0.25</v>
+        <v>-0.246</v>
       </c>
       <c r="G40" s="4">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="H40" s="4">
-        <v>14.05</v>
+        <v>14.25</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -5889,26 +5911,26 @@
       </c>
     </row>
     <row r="41" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C41" s="4">
-        <v>610</v>
-      </c>
-      <c r="D41" s="4">
-        <v>48.74</v>
-      </c>
-      <c r="E41" s="4">
-        <v>40.56</v>
-      </c>
-      <c r="F41" s="4">
-        <v>-0.24</v>
+      <c r="B41" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="1">
+        <v>585</v>
+      </c>
+      <c r="D41" s="1">
+        <v>52.7</v>
+      </c>
+      <c r="E41" s="1">
+        <v>44.04</v>
+      </c>
+      <c r="F41" s="1">
+        <v>-0.25</v>
       </c>
       <c r="G41" s="4">
-        <v>15.04</v>
+        <v>13.3</v>
       </c>
       <c r="H41" s="4">
-        <v>15.93</v>
+        <v>14.05</v>
       </c>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
@@ -5990,26 +6012,28 @@
     </row>
     <row r="42" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C42" s="1">
-        <v>590</v>
-      </c>
-      <c r="D42" s="1">
-        <v>52.9</v>
-      </c>
-      <c r="E42" s="1">
-        <v>44.15</v>
-      </c>
-      <c r="F42" s="1">
-        <v>-0.25900000000000001</v>
-      </c>
-      <c r="G42" s="1">
-        <v>13.37</v>
-      </c>
-      <c r="H42" s="1">
-        <v>14.03</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="C42" s="4">
+        <v>610</v>
+      </c>
+      <c r="D42" s="4">
+        <v>48.74</v>
+      </c>
+      <c r="E42" s="4">
+        <v>40.56</v>
+      </c>
+      <c r="F42" s="4">
+        <v>-0.24</v>
+      </c>
+      <c r="G42" s="4">
+        <v>15.04</v>
+      </c>
+      <c r="H42" s="4">
+        <v>15.93</v>
+      </c>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
       <c r="L42" s="1" t="s">
         <v>132</v>
       </c>
@@ -6125,24 +6149,26 @@
     </row>
     <row r="43" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C43" s="1">
-        <v>375</v>
+        <v>590</v>
       </c>
       <c r="D43" s="1">
-        <v>47.43</v>
+        <v>52.9</v>
       </c>
       <c r="E43" s="1">
-        <v>38.869999999999997</v>
+        <v>44.15</v>
       </c>
       <c r="F43" s="1">
-        <v>-0.3</v>
-      </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
+        <v>-0.25900000000000001</v>
+      </c>
+      <c r="G43" s="1">
+        <v>13.37</v>
+      </c>
+      <c r="H43" s="1">
+        <v>14.03</v>
+      </c>
       <c r="L43" s="1" t="s">
         <v>134</v>
       </c>
@@ -6207,26 +6233,22 @@
     </row>
     <row r="44" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C44" s="1">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="D44" s="1">
-        <v>48.93</v>
+        <v>47.43</v>
       </c>
       <c r="E44" s="1">
-        <v>40.61</v>
+        <v>38.869999999999997</v>
       </c>
       <c r="F44" s="1">
         <v>-0.3</v>
       </c>
-      <c r="G44" s="4">
-        <v>9.85</v>
-      </c>
-      <c r="H44" s="4">
-        <v>10.36</v>
-      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="L44" s="1" t="s">
@@ -6293,25 +6315,25 @@
     </row>
     <row r="45" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C45" s="4">
-        <v>700</v>
-      </c>
-      <c r="D45" s="4">
-        <v>50.42</v>
-      </c>
-      <c r="E45" s="4">
-        <v>42.41</v>
-      </c>
-      <c r="F45" s="4">
-        <v>-0.24</v>
+        <v>135</v>
+      </c>
+      <c r="C45" s="1">
+        <v>400</v>
+      </c>
+      <c r="D45" s="1">
+        <v>48.93</v>
+      </c>
+      <c r="E45" s="1">
+        <v>40.61</v>
+      </c>
+      <c r="F45" s="1">
+        <v>-0.3</v>
       </c>
       <c r="G45" s="4">
-        <v>16.510000000000002</v>
+        <v>9.85</v>
       </c>
       <c r="H45" s="4">
-        <v>17.63</v>
+        <v>10.36</v>
       </c>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
@@ -6386,25 +6408,25 @@
     </row>
     <row r="46" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C46" s="4">
-        <v>570</v>
+        <v>700</v>
       </c>
       <c r="D46" s="4">
-        <v>51.07</v>
+        <v>50.42</v>
       </c>
       <c r="E46" s="4">
-        <v>42.29</v>
+        <v>42.41</v>
       </c>
       <c r="F46" s="4">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="G46" s="4">
-        <v>13.48</v>
+        <v>16.510000000000002</v>
       </c>
       <c r="H46" s="4">
-        <v>14.25</v>
+        <v>17.63</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
@@ -6472,25 +6494,25 @@
     </row>
     <row r="47" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C47" s="4">
-        <v>585</v>
-      </c>
-      <c r="D47" s="1">
-        <v>51.67</v>
+        <v>570</v>
+      </c>
+      <c r="D47" s="4">
+        <v>51.07</v>
       </c>
       <c r="E47" s="4">
-        <v>42.74</v>
+        <v>42.29</v>
       </c>
       <c r="F47" s="4">
         <v>-0.25</v>
       </c>
       <c r="G47" s="4">
-        <v>13.69</v>
+        <v>13.48</v>
       </c>
       <c r="H47" s="4">
-        <v>14.43</v>
+        <v>14.25</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
@@ -6558,25 +6580,25 @@
     </row>
     <row r="48" spans="2:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>394</v>
+        <v>141</v>
       </c>
       <c r="C48" s="4">
-        <v>615</v>
-      </c>
-      <c r="D48" s="4">
-        <v>48.17</v>
+        <v>585</v>
+      </c>
+      <c r="D48" s="1">
+        <v>51.67</v>
       </c>
       <c r="E48" s="4">
-        <v>40.35</v>
+        <v>42.74</v>
       </c>
       <c r="F48" s="4">
         <v>-0.25</v>
       </c>
       <c r="G48" s="4">
-        <v>15.25</v>
+        <v>13.69</v>
       </c>
       <c r="H48" s="4">
-        <v>16.14</v>
+        <v>14.43</v>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
@@ -6644,26 +6666,28 @@
     </row>
     <row r="49" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C49" s="1">
-        <v>590</v>
-      </c>
-      <c r="D49" s="1">
-        <v>52.49</v>
-      </c>
-      <c r="E49" s="1">
-        <v>44.21</v>
-      </c>
-      <c r="F49" s="1">
+        <v>394</v>
+      </c>
+      <c r="C49" s="4">
+        <v>615</v>
+      </c>
+      <c r="D49" s="4">
+        <v>48.17</v>
+      </c>
+      <c r="E49" s="4">
+        <v>40.35</v>
+      </c>
+      <c r="F49" s="4">
         <v>-0.25</v>
       </c>
-      <c r="G49" s="1">
-        <v>13.35</v>
-      </c>
-      <c r="H49" s="1">
-        <v>14.05</v>
-      </c>
+      <c r="G49" s="4">
+        <v>15.25</v>
+      </c>
+      <c r="H49" s="4">
+        <v>16.14</v>
+      </c>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
       <c r="L49" s="1" t="s">
         <v>146</v>
       </c>
@@ -6735,28 +6759,26 @@
     </row>
     <row r="50" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C50" s="4">
-        <v>585</v>
-      </c>
-      <c r="D50" s="4">
-        <v>51.6</v>
-      </c>
-      <c r="E50" s="4">
-        <v>43.4</v>
-      </c>
-      <c r="F50" s="4">
-        <v>-0.26</v>
-      </c>
-      <c r="G50" s="4">
-        <v>13.48</v>
-      </c>
-      <c r="H50" s="4">
-        <v>14.29</v>
-      </c>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
+        <v>143</v>
+      </c>
+      <c r="C50" s="1">
+        <v>590</v>
+      </c>
+      <c r="D50" s="1">
+        <v>52.49</v>
+      </c>
+      <c r="E50" s="1">
+        <v>44.21</v>
+      </c>
+      <c r="F50" s="1">
+        <v>-0.25</v>
+      </c>
+      <c r="G50" s="1">
+        <v>13.35</v>
+      </c>
+      <c r="H50" s="1">
+        <v>14.05</v>
+      </c>
       <c r="L50" s="1" t="s">
         <v>148</v>
       </c>
@@ -6828,26 +6850,28 @@
     </row>
     <row r="51" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C51" s="1">
-        <v>610</v>
-      </c>
-      <c r="D51" s="1">
-        <v>48.72</v>
-      </c>
-      <c r="E51" s="1">
-        <v>40.590000000000003</v>
-      </c>
-      <c r="F51" s="1">
-        <v>-0.23</v>
-      </c>
-      <c r="G51" s="1">
-        <v>15.03</v>
-      </c>
-      <c r="H51" s="1">
-        <v>15.94</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="C51" s="4">
+        <v>585</v>
+      </c>
+      <c r="D51" s="4">
+        <v>51.6</v>
+      </c>
+      <c r="E51" s="4">
+        <v>43.4</v>
+      </c>
+      <c r="F51" s="4">
+        <v>-0.26</v>
+      </c>
+      <c r="G51" s="4">
+        <v>13.48</v>
+      </c>
+      <c r="H51" s="4">
+        <v>14.29</v>
+      </c>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
       <c r="L51" s="1" t="s">
         <v>150</v>
       </c>
@@ -6912,28 +6936,26 @@
     </row>
     <row r="52" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C52" s="4">
-        <v>670</v>
-      </c>
-      <c r="D52" s="4">
-        <v>45.8</v>
-      </c>
-      <c r="E52" s="4">
-        <v>38.700000000000003</v>
-      </c>
-      <c r="F52" s="4">
-        <v>-0.27400000000000002</v>
-      </c>
-      <c r="G52" s="4">
-        <v>17.32</v>
-      </c>
-      <c r="H52" s="4">
-        <v>18.55</v>
-      </c>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
+        <v>147</v>
+      </c>
+      <c r="C52" s="1">
+        <v>610</v>
+      </c>
+      <c r="D52" s="1">
+        <v>48.72</v>
+      </c>
+      <c r="E52" s="1">
+        <v>40.590000000000003</v>
+      </c>
+      <c r="F52" s="1">
+        <v>-0.23</v>
+      </c>
+      <c r="G52" s="1">
+        <v>15.03</v>
+      </c>
+      <c r="H52" s="1">
+        <v>15.94</v>
+      </c>
       <c r="L52" s="1" t="s">
         <v>152</v>
       </c>
@@ -6998,25 +7020,25 @@
     </row>
     <row r="53" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C53" s="4">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="D53" s="4">
-        <v>47.8</v>
+        <v>45.8</v>
       </c>
       <c r="E53" s="4">
-        <v>40</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="F53" s="4">
-        <v>-0.23</v>
+        <v>-0.27400000000000002</v>
       </c>
       <c r="G53" s="4">
-        <v>17.25</v>
+        <v>17.32</v>
       </c>
       <c r="H53" s="4">
-        <v>18.260000000000002</v>
+        <v>18.55</v>
       </c>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -7084,25 +7106,25 @@
     </row>
     <row r="54" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C54" s="4">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="D54" s="4">
-        <v>49.77</v>
+        <v>47.8</v>
       </c>
       <c r="E54" s="4">
-        <v>41.78</v>
+        <v>40</v>
       </c>
       <c r="F54" s="4">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="G54" s="4">
-        <v>16.760000000000002</v>
+        <v>17.25</v>
       </c>
       <c r="H54" s="4">
-        <v>17.809999999999999</v>
+        <v>18.260000000000002</v>
       </c>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
@@ -7170,25 +7192,25 @@
     </row>
     <row r="55" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C55" s="4">
         <v>700</v>
       </c>
       <c r="D55" s="4">
-        <v>48.2</v>
+        <v>49.77</v>
       </c>
       <c r="E55" s="4">
-        <v>40.4</v>
+        <v>41.78</v>
       </c>
       <c r="F55" s="4">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="G55" s="4">
-        <v>17.329999999999998</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="H55" s="4">
-        <v>18.34</v>
+        <v>17.809999999999999</v>
       </c>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
@@ -7233,25 +7255,25 @@
     </row>
     <row r="56" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C56" s="4">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="D56" s="4">
-        <v>52.55</v>
+        <v>48.2</v>
       </c>
       <c r="E56" s="4">
-        <v>44.54</v>
+        <v>40.4</v>
       </c>
       <c r="F56" s="4">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="G56" s="4">
-        <v>13.48</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="H56" s="4">
-        <v>14.25</v>
+        <v>18.34</v>
       </c>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
@@ -7299,26 +7321,28 @@
     </row>
     <row r="57" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C57" s="1">
-        <v>610</v>
-      </c>
-      <c r="D57" s="1">
-        <v>48.5</v>
-      </c>
-      <c r="E57" s="1">
-        <v>40.5</v>
-      </c>
-      <c r="F57" s="1">
+        <v>157</v>
+      </c>
+      <c r="C57" s="4">
+        <v>600</v>
+      </c>
+      <c r="D57" s="4">
+        <v>52.55</v>
+      </c>
+      <c r="E57" s="4">
+        <v>44.54</v>
+      </c>
+      <c r="F57" s="4">
         <v>-0.24</v>
       </c>
-      <c r="G57" s="1">
-        <v>15.07</v>
-      </c>
-      <c r="H57" s="1">
-        <v>15.88</v>
-      </c>
+      <c r="G57" s="4">
+        <v>13.48</v>
+      </c>
+      <c r="H57" s="4">
+        <v>14.25</v>
+      </c>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
       <c r="L57" s="1" t="s">
         <v>160</v>
       </c>
@@ -7359,25 +7383,25 @@
     </row>
     <row r="58" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C58" s="1">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="D58" s="1">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="E58" s="1">
-        <v>40.700000000000003</v>
+        <v>40.5</v>
       </c>
       <c r="F58" s="1">
         <v>-0.24</v>
       </c>
       <c r="G58" s="1">
-        <v>15.12</v>
+        <v>15.07</v>
       </c>
       <c r="H58" s="1">
-        <v>15.92</v>
+        <v>15.88</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>162</v>
@@ -7496,28 +7520,26 @@
     </row>
     <row r="59" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C59" s="4">
-        <v>700</v>
-      </c>
-      <c r="D59" s="4">
-        <v>50</v>
-      </c>
-      <c r="E59" s="4">
-        <v>42.1</v>
-      </c>
-      <c r="F59" s="4">
+        <v>161</v>
+      </c>
+      <c r="C59" s="1">
+        <v>615</v>
+      </c>
+      <c r="D59" s="1">
+        <v>48.7</v>
+      </c>
+      <c r="E59" s="1">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="F59" s="1">
         <v>-0.24</v>
       </c>
-      <c r="G59" s="4">
-        <v>16.63</v>
-      </c>
-      <c r="H59" s="4">
-        <v>17.37</v>
-      </c>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
+      <c r="G59" s="1">
+        <v>15.12</v>
+      </c>
+      <c r="H59" s="1">
+        <v>15.92</v>
+      </c>
       <c r="L59" s="1" t="s">
         <v>164</v>
       </c>
@@ -7631,25 +7653,25 @@
     </row>
     <row r="60" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C60" s="1">
-        <v>560</v>
-      </c>
-      <c r="D60" s="1">
-        <v>51.1</v>
-      </c>
-      <c r="E60" s="1">
-        <v>42.4</v>
-      </c>
-      <c r="F60" s="1">
-        <v>-0.26200000000000001</v>
+        <v>163</v>
+      </c>
+      <c r="C60" s="4">
+        <v>700</v>
+      </c>
+      <c r="D60" s="4">
+        <v>50</v>
+      </c>
+      <c r="E60" s="4">
+        <v>42.1</v>
+      </c>
+      <c r="F60" s="4">
+        <v>-0.24</v>
       </c>
       <c r="G60" s="4">
-        <v>13.21</v>
+        <v>16.63</v>
       </c>
       <c r="H60" s="4">
-        <v>13.95</v>
+        <v>17.37</v>
       </c>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
@@ -7707,22 +7729,26 @@
     </row>
     <row r="61" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C61" s="1">
-        <v>310</v>
+        <v>560</v>
       </c>
       <c r="D61" s="1">
-        <v>45.9</v>
+        <v>51.1</v>
       </c>
       <c r="E61" s="1">
-        <v>37</v>
+        <v>42.4</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.31</v>
-      </c>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
+        <v>-0.26200000000000001</v>
+      </c>
+      <c r="G61" s="4">
+        <v>13.21</v>
+      </c>
+      <c r="H61" s="4">
+        <v>13.95</v>
+      </c>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
       <c r="L61" s="1" t="s">
@@ -7774,27 +7800,23 @@
       </c>
     </row>
     <row r="62" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="14" t="s">
-        <v>169</v>
+      <c r="B62" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="C62" s="1">
-        <v>585</v>
+        <v>310</v>
       </c>
       <c r="D62" s="1">
-        <v>51.22</v>
+        <v>45.9</v>
       </c>
       <c r="E62" s="1">
-        <v>42.55</v>
+        <v>37</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.25</v>
-      </c>
-      <c r="G62" s="4">
-        <v>13.74</v>
-      </c>
-      <c r="H62" s="4">
-        <v>14.53</v>
-      </c>
+        <v>-0.31</v>
+      </c>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
       <c r="L62" s="1" t="s">
@@ -7854,26 +7876,26 @@
       </c>
     </row>
     <row r="63" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="1" t="s">
-        <v>171</v>
+      <c r="B63" s="14" t="s">
+        <v>169</v>
       </c>
       <c r="C63" s="1">
-        <v>460</v>
+        <v>585</v>
       </c>
       <c r="D63" s="1">
-        <v>41.8</v>
+        <v>51.22</v>
       </c>
       <c r="E63" s="1">
-        <v>35.200000000000003</v>
+        <v>42.55</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.28000000000000003</v>
+        <v>-0.25</v>
       </c>
       <c r="G63" s="4">
-        <v>13.08</v>
+        <v>13.74</v>
       </c>
       <c r="H63" s="4">
-        <v>13.78</v>
+        <v>14.53</v>
       </c>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
@@ -7917,26 +7939,26 @@
       </c>
     </row>
     <row r="64" spans="2:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="17" t="s">
-        <v>173</v>
+      <c r="B64" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="C64" s="1">
-        <v>550</v>
+        <v>460</v>
       </c>
       <c r="D64" s="1">
-        <v>49.8</v>
+        <v>41.8</v>
       </c>
       <c r="E64" s="1">
-        <v>41.6</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="F64" s="1">
         <v>-0.28000000000000003</v>
       </c>
       <c r="G64" s="4">
-        <v>13.23</v>
+        <v>13.08</v>
       </c>
       <c r="H64" s="4">
-        <v>13.99</v>
+        <v>13.78</v>
       </c>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
@@ -7980,26 +8002,26 @@
       </c>
     </row>
     <row r="65" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="14" t="s">
-        <v>175</v>
+      <c r="B65" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="C65" s="1">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="D65" s="1">
-        <v>50.2</v>
+        <v>49.8</v>
       </c>
       <c r="E65" s="1">
-        <v>42</v>
+        <v>41.6</v>
       </c>
       <c r="F65" s="1">
         <v>-0.28000000000000003</v>
       </c>
       <c r="G65" s="4">
-        <v>13.33</v>
+        <v>13.23</v>
       </c>
       <c r="H65" s="4">
-        <v>14.11</v>
+        <v>13.99</v>
       </c>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
@@ -8065,25 +8087,25 @@
     </row>
     <row r="66" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C66" s="1">
         <v>560</v>
       </c>
       <c r="D66" s="1">
-        <v>47.42</v>
+        <v>50.2</v>
       </c>
       <c r="E66" s="1">
-        <v>39.51</v>
+        <v>42</v>
       </c>
       <c r="F66" s="1">
-        <v>-0.25</v>
+        <v>-0.28000000000000003</v>
       </c>
       <c r="G66" s="4">
-        <v>14.17</v>
+        <v>13.33</v>
       </c>
       <c r="H66" s="4">
-        <v>15</v>
+        <v>14.11</v>
       </c>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
@@ -8128,25 +8150,25 @@
     </row>
     <row r="67" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C67" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="D67" s="1">
-        <v>51.51</v>
+        <v>47.42</v>
       </c>
       <c r="E67" s="1">
-        <v>42.9</v>
+        <v>39.51</v>
       </c>
       <c r="F67" s="1">
         <v>-0.25</v>
       </c>
       <c r="G67" s="4">
-        <v>13.52</v>
+        <v>14.17</v>
       </c>
       <c r="H67" s="4">
-        <v>14.08</v>
+        <v>15</v>
       </c>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
@@ -8191,25 +8213,25 @@
     </row>
     <row r="68" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C68" s="1">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="D68" s="1">
-        <v>48.42</v>
+        <v>51.51</v>
       </c>
       <c r="E68" s="1">
-        <v>40.51</v>
+        <v>42.9</v>
       </c>
       <c r="F68" s="1">
         <v>-0.25</v>
       </c>
       <c r="G68" s="4">
-        <v>14.44</v>
+        <v>13.52</v>
       </c>
       <c r="H68" s="4">
-        <v>15.27</v>
+        <v>14.08</v>
       </c>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
@@ -8294,25 +8316,25 @@
     </row>
     <row r="69" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C69" s="1">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D69" s="1">
-        <v>53.7</v>
+        <v>48.42</v>
       </c>
       <c r="E69" s="1">
-        <v>44.8</v>
+        <v>40.51</v>
       </c>
       <c r="F69" s="1">
-        <v>-0.28000000000000003</v>
+        <v>-0.25</v>
       </c>
       <c r="G69" s="4">
-        <v>13.17</v>
+        <v>14.44</v>
       </c>
       <c r="H69" s="4">
-        <v>13.94</v>
+        <v>15.27</v>
       </c>
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
@@ -8393,25 +8415,25 @@
     </row>
     <row r="70" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C70" s="1">
         <v>590</v>
       </c>
       <c r="D70" s="1">
-        <v>48.62</v>
+        <v>53.7</v>
       </c>
       <c r="E70" s="1">
-        <v>40.72</v>
+        <v>44.8</v>
       </c>
       <c r="F70" s="1">
-        <v>-0.25</v>
+        <v>-0.28000000000000003</v>
       </c>
       <c r="G70" s="4">
-        <v>14.94</v>
+        <v>13.17</v>
       </c>
       <c r="H70" s="4">
-        <v>15.32</v>
+        <v>13.94</v>
       </c>
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
@@ -8456,25 +8478,25 @@
     </row>
     <row r="71" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C71" s="1">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="D71" s="1">
-        <v>52</v>
+        <v>48.62</v>
       </c>
       <c r="E71" s="1">
-        <v>43.5</v>
+        <v>40.72</v>
       </c>
       <c r="F71" s="1">
         <v>-0.25</v>
       </c>
       <c r="G71" s="4">
-        <v>13.68</v>
+        <v>14.94</v>
       </c>
       <c r="H71" s="4">
-        <v>14.26</v>
+        <v>15.32</v>
       </c>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
@@ -8518,26 +8540,26 @@
       </c>
     </row>
     <row r="72" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C72" s="4">
-        <v>610</v>
-      </c>
-      <c r="D72" s="4">
-        <v>49.05</v>
-      </c>
-      <c r="E72" s="4">
-        <v>40.659999999999997</v>
-      </c>
-      <c r="F72" s="4">
+      <c r="B72" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C72" s="1">
+        <v>595</v>
+      </c>
+      <c r="D72" s="1">
+        <v>52</v>
+      </c>
+      <c r="E72" s="1">
+        <v>43.5</v>
+      </c>
+      <c r="F72" s="1">
         <v>-0.25</v>
       </c>
       <c r="G72" s="4">
-        <v>15</v>
+        <v>13.68</v>
       </c>
       <c r="H72" s="4">
-        <v>15.84</v>
+        <v>14.26</v>
       </c>
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
@@ -8613,7 +8635,7 @@
     </row>
     <row r="73" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C73" s="4">
         <v>610</v>
@@ -8684,25 +8706,25 @@
     </row>
     <row r="74" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C74" s="1">
-        <v>650</v>
-      </c>
-      <c r="D74" s="1">
-        <v>45.58</v>
-      </c>
-      <c r="E74" s="1">
-        <v>37.61</v>
-      </c>
-      <c r="F74" s="1">
-        <v>-0.28000000000000003</v>
+        <v>191</v>
+      </c>
+      <c r="C74" s="4">
+        <v>610</v>
+      </c>
+      <c r="D74" s="4">
+        <v>49.05</v>
+      </c>
+      <c r="E74" s="4">
+        <v>40.659999999999997</v>
+      </c>
+      <c r="F74" s="4">
+        <v>-0.25</v>
       </c>
       <c r="G74" s="4">
-        <v>17.28</v>
+        <v>15</v>
       </c>
       <c r="H74" s="4">
-        <v>18.16</v>
+        <v>15.84</v>
       </c>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
@@ -8750,26 +8772,26 @@
       </c>
     </row>
     <row r="75" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="14" t="s">
-        <v>195</v>
+      <c r="B75" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="C75" s="1">
-        <v>665</v>
-      </c>
-      <c r="D75" s="4">
-        <v>46.18</v>
+        <v>650</v>
+      </c>
+      <c r="D75" s="1">
+        <v>45.58</v>
       </c>
       <c r="E75" s="1">
-        <v>38.21</v>
+        <v>37.61</v>
       </c>
       <c r="F75" s="1">
-        <v>-0.25</v>
+        <v>-0.28000000000000003</v>
       </c>
       <c r="G75" s="4">
-        <v>17.399999999999999</v>
+        <v>17.28</v>
       </c>
       <c r="H75" s="4">
-        <v>18.309999999999999</v>
+        <v>18.16</v>
       </c>
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
@@ -8829,26 +8851,26 @@
       </c>
     </row>
     <row r="76" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C76" s="4">
-        <v>670</v>
+      <c r="B76" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C76" s="1">
+        <v>665</v>
       </c>
       <c r="D76" s="4">
-        <v>46.38</v>
-      </c>
-      <c r="E76" s="4">
-        <v>38.409999999999997</v>
-      </c>
-      <c r="F76" s="4">
+        <v>46.18</v>
+      </c>
+      <c r="E76" s="1">
+        <v>38.21</v>
+      </c>
+      <c r="F76" s="1">
         <v>-0.25</v>
       </c>
       <c r="G76" s="4">
-        <v>17.440000000000001</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="H76" s="4">
-        <v>18.36</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
@@ -8905,25 +8927,25 @@
     </row>
     <row r="77" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C77" s="4">
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="D77" s="4">
-        <v>48.2</v>
+        <v>46.38</v>
       </c>
       <c r="E77" s="4">
-        <v>40.200000000000003</v>
+        <v>38.409999999999997</v>
       </c>
       <c r="F77" s="4">
         <v>-0.25</v>
       </c>
       <c r="G77" s="4">
-        <v>17.41</v>
+        <v>17.440000000000001</v>
       </c>
       <c r="H77" s="4">
-        <v>18.48</v>
+        <v>18.36</v>
       </c>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
@@ -8999,26 +9021,28 @@
     </row>
     <row r="78" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C78" s="1">
-        <v>570</v>
-      </c>
-      <c r="D78" s="1">
-        <v>47.82</v>
-      </c>
-      <c r="E78" s="1">
-        <v>39.909999999999997</v>
-      </c>
-      <c r="F78" s="1">
+        <v>198</v>
+      </c>
+      <c r="C78" s="4">
+        <v>700</v>
+      </c>
+      <c r="D78" s="4">
+        <v>48.2</v>
+      </c>
+      <c r="E78" s="4">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="F78" s="4">
         <v>-0.25</v>
       </c>
-      <c r="G78" s="1">
-        <v>14.28</v>
-      </c>
-      <c r="H78" s="1">
-        <v>15.12</v>
-      </c>
+      <c r="G78" s="4">
+        <v>17.41</v>
+      </c>
+      <c r="H78" s="4">
+        <v>18.48</v>
+      </c>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
       <c r="L78" s="1" t="s">
         <v>201</v>
       </c>
@@ -9067,29 +9091,27 @@
       </c>
     </row>
     <row r="79" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="14" t="s">
-        <v>202</v>
+      <c r="B79" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="C79" s="1">
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="D79" s="1">
-        <v>48.42</v>
+        <v>47.82</v>
       </c>
       <c r="E79" s="1">
-        <v>40.51</v>
+        <v>39.909999999999997</v>
       </c>
       <c r="F79" s="1">
         <v>-0.25</v>
       </c>
-      <c r="G79" s="4">
-        <v>14.44</v>
-      </c>
-      <c r="H79" s="4">
-        <v>15.27</v>
-      </c>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
+      <c r="G79" s="1">
+        <v>14.28</v>
+      </c>
+      <c r="H79" s="1">
+        <v>15.12</v>
+      </c>
       <c r="L79" s="1" t="s">
         <v>203</v>
       </c>
@@ -9135,25 +9157,25 @@
     </row>
     <row r="80" spans="2:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="C80" s="4">
-        <v>620</v>
-      </c>
-      <c r="D80" s="4">
-        <v>52.09</v>
-      </c>
-      <c r="E80" s="4">
-        <v>43.48</v>
-      </c>
-      <c r="F80" s="4">
+        <v>202</v>
+      </c>
+      <c r="C80" s="1">
+        <v>585</v>
+      </c>
+      <c r="D80" s="1">
+        <v>48.42</v>
+      </c>
+      <c r="E80" s="1">
+        <v>40.51</v>
+      </c>
+      <c r="F80" s="1">
         <v>-0.25</v>
       </c>
       <c r="G80" s="4">
-        <v>14.26</v>
+        <v>14.44</v>
       </c>
       <c r="H80" s="4">
-        <v>15.09</v>
+        <v>15.27</v>
       </c>
       <c r="I80" s="4"/>
       <c r="J80" s="4"/>
@@ -9232,26 +9254,26 @@
       </c>
     </row>
     <row r="81" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="1" t="s">
-        <v>206</v>
+      <c r="B81" s="14" t="s">
+        <v>204</v>
       </c>
       <c r="C81" s="4">
         <v>620</v>
       </c>
       <c r="D81" s="4">
-        <v>49.55</v>
+        <v>52.09</v>
       </c>
       <c r="E81" s="4">
-        <v>41.06</v>
+        <v>43.48</v>
       </c>
       <c r="F81" s="4">
         <v>-0.25</v>
       </c>
       <c r="G81" s="4">
-        <v>15.1</v>
+        <v>14.26</v>
       </c>
       <c r="H81" s="4">
-        <v>15.93</v>
+        <v>15.09</v>
       </c>
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
@@ -9303,8 +9325,8 @@
       </c>
     </row>
     <row r="82" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="14" t="s">
-        <v>208</v>
+      <c r="B82" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="C82" s="4">
         <v>620</v>
@@ -9371,25 +9393,25 @@
     </row>
     <row r="83" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="C83" s="1">
-        <v>690</v>
-      </c>
-      <c r="D83" s="1">
-        <v>47.8</v>
-      </c>
-      <c r="E83" s="1">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="F83" s="1">
+        <v>208</v>
+      </c>
+      <c r="C83" s="4">
+        <v>620</v>
+      </c>
+      <c r="D83" s="4">
+        <v>49.55</v>
+      </c>
+      <c r="E83" s="4">
+        <v>41.06</v>
+      </c>
+      <c r="F83" s="4">
         <v>-0.25</v>
       </c>
       <c r="G83" s="4">
-        <v>17.34</v>
+        <v>15.1</v>
       </c>
       <c r="H83" s="4">
-        <v>18.3</v>
+        <v>15.93</v>
       </c>
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
@@ -9442,26 +9464,26 @@
       </c>
     </row>
     <row r="84" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C84" s="4">
-        <v>445</v>
-      </c>
-      <c r="D84" s="4">
-        <v>49.4</v>
-      </c>
-      <c r="E84" s="4">
-        <v>41.2</v>
-      </c>
-      <c r="F84" s="4">
-        <v>-0.28399999999999997</v>
+      <c r="B84" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="C84" s="1">
+        <v>690</v>
+      </c>
+      <c r="D84" s="1">
+        <v>47.8</v>
+      </c>
+      <c r="E84" s="1">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="F84" s="1">
+        <v>-0.25</v>
       </c>
       <c r="G84" s="4">
-        <v>10.8</v>
+        <v>17.34</v>
       </c>
       <c r="H84" s="4">
-        <v>11.52</v>
+        <v>18.3</v>
       </c>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
@@ -9554,25 +9576,25 @@
     </row>
     <row r="85" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C85" s="4">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="D85" s="4">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
       <c r="E85" s="4">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="F85" s="4">
         <v>-0.28399999999999997</v>
       </c>
       <c r="G85" s="4">
-        <v>10.87</v>
+        <v>10.8</v>
       </c>
       <c r="H85" s="4">
-        <v>11.58</v>
+        <v>11.52</v>
       </c>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
@@ -9693,25 +9715,25 @@
     </row>
     <row r="86" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C86" s="4">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D86" s="4">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="E86" s="4">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="F86" s="4">
         <v>-0.28399999999999997</v>
       </c>
       <c r="G86" s="4">
-        <v>10.93</v>
+        <v>10.87</v>
       </c>
       <c r="H86" s="4">
-        <v>11.65</v>
+        <v>11.58</v>
       </c>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
@@ -9828,25 +9850,25 @@
     </row>
     <row r="87" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C87" s="1">
-        <v>440</v>
-      </c>
-      <c r="D87" s="1">
-        <v>49.6</v>
-      </c>
-      <c r="E87" s="1">
-        <v>41</v>
-      </c>
-      <c r="F87" s="1">
-        <v>-0.28599999999999998</v>
+        <v>216</v>
+      </c>
+      <c r="C87" s="4">
+        <v>455</v>
+      </c>
+      <c r="D87" s="4">
+        <v>49.8</v>
+      </c>
+      <c r="E87" s="4">
+        <v>41.6</v>
+      </c>
+      <c r="F87" s="4">
+        <v>-0.28399999999999997</v>
       </c>
       <c r="G87" s="4">
-        <v>10.74</v>
+        <v>10.93</v>
       </c>
       <c r="H87" s="4">
-        <v>11.33</v>
+        <v>11.65</v>
       </c>
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
@@ -9913,26 +9935,26 @@
       <c r="BI87" s="22"/>
     </row>
     <row r="88" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
-        <v>220</v>
+      <c r="B88" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="C88" s="1">
-        <v>555</v>
+        <v>440</v>
       </c>
       <c r="D88" s="1">
-        <v>50.3</v>
+        <v>49.6</v>
       </c>
       <c r="E88" s="1">
-        <v>42.27</v>
+        <v>41</v>
       </c>
       <c r="F88" s="1">
-        <v>-0.28499999999999998</v>
+        <v>-0.28599999999999998</v>
       </c>
       <c r="G88" s="4">
-        <v>13.13</v>
+        <v>10.74</v>
       </c>
       <c r="H88" s="4">
-        <v>14.1</v>
+        <v>11.33</v>
       </c>
       <c r="I88" s="4"/>
       <c r="J88" s="4"/>
@@ -9999,26 +10021,26 @@
       <c r="BI88" s="22"/>
     </row>
     <row r="89" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C89" s="4">
-        <v>610</v>
-      </c>
-      <c r="D89" s="4">
-        <v>48.63</v>
-      </c>
-      <c r="E89" s="4">
-        <v>40.56</v>
-      </c>
-      <c r="F89" s="4">
-        <v>-0.26</v>
+      <c r="B89" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="C89" s="1">
+        <v>555</v>
+      </c>
+      <c r="D89" s="1">
+        <v>50.3</v>
+      </c>
+      <c r="E89" s="1">
+        <v>42.27</v>
+      </c>
+      <c r="F89" s="1">
+        <v>-0.28499999999999998</v>
       </c>
       <c r="G89" s="4">
-        <v>15.04</v>
+        <v>13.13</v>
       </c>
       <c r="H89" s="4">
-        <v>16.010000000000002</v>
+        <v>14.1</v>
       </c>
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
@@ -10060,25 +10082,25 @@
     </row>
     <row r="90" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C90" s="4">
         <v>610</v>
       </c>
       <c r="D90" s="4">
-        <v>52.55</v>
+        <v>48.63</v>
       </c>
       <c r="E90" s="4">
-        <v>44.11</v>
-      </c>
-      <c r="F90" s="1">
-        <v>-0.25</v>
+        <v>40.56</v>
+      </c>
+      <c r="F90" s="4">
+        <v>-0.26</v>
       </c>
       <c r="G90" s="4">
-        <v>13.83</v>
+        <v>15.04</v>
       </c>
       <c r="H90" s="4">
-        <v>14.69</v>
+        <v>16.010000000000002</v>
       </c>
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
@@ -10126,25 +10148,25 @@
     </row>
     <row r="91" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C91" s="1">
-        <v>460</v>
-      </c>
-      <c r="D91" s="1">
-        <v>41.8</v>
-      </c>
-      <c r="E91" s="1">
-        <v>35.11</v>
+        <v>224</v>
+      </c>
+      <c r="C91" s="4">
+        <v>610</v>
+      </c>
+      <c r="D91" s="4">
+        <v>52.55</v>
+      </c>
+      <c r="E91" s="4">
+        <v>44.11</v>
       </c>
       <c r="F91" s="1">
-        <v>-0.28000000000000003</v>
+        <v>-0.25</v>
       </c>
       <c r="G91" s="4">
-        <v>13.11</v>
+        <v>13.83</v>
       </c>
       <c r="H91" s="4">
-        <v>13.93</v>
+        <v>14.69</v>
       </c>
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
@@ -10192,25 +10214,25 @@
     </row>
     <row r="92" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="C92" s="4">
-        <v>620</v>
-      </c>
-      <c r="D92" s="4">
-        <v>47.98</v>
-      </c>
-      <c r="E92" s="4">
-        <v>40.39</v>
-      </c>
-      <c r="F92" s="4">
-        <v>-0.25</v>
+        <v>226</v>
+      </c>
+      <c r="C92" s="1">
+        <v>460</v>
+      </c>
+      <c r="D92" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="E92" s="1">
+        <v>35.11</v>
+      </c>
+      <c r="F92" s="1">
+        <v>-0.28000000000000003</v>
       </c>
       <c r="G92" s="4">
-        <v>15.35</v>
+        <v>13.11</v>
       </c>
       <c r="H92" s="4">
-        <v>16.3</v>
+        <v>13.93</v>
       </c>
       <c r="I92" s="4"/>
       <c r="J92" s="4"/>
@@ -10258,25 +10280,25 @@
     </row>
     <row r="93" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="1" t="s">
-        <v>230</v>
+        <v>395</v>
       </c>
       <c r="C93" s="4">
-        <v>700</v>
-      </c>
-      <c r="D93" s="1">
-        <v>49.77</v>
-      </c>
-      <c r="E93" s="1">
-        <v>41.78</v>
+        <v>620</v>
+      </c>
+      <c r="D93" s="4">
+        <v>47.98</v>
+      </c>
+      <c r="E93" s="4">
+        <v>40.39</v>
       </c>
       <c r="F93" s="4">
-        <v>-0.22</v>
+        <v>-0.25</v>
       </c>
       <c r="G93" s="4">
-        <v>16.760000000000002</v>
+        <v>15.35</v>
       </c>
       <c r="H93" s="4">
-        <v>17.809999999999999</v>
+        <v>16.3</v>
       </c>
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
@@ -10335,26 +10357,26 @@
       </c>
     </row>
     <row r="94" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="C94" s="1">
-        <v>560</v>
+      <c r="B94" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C94" s="4">
+        <v>700</v>
       </c>
       <c r="D94" s="1">
-        <v>50.1</v>
+        <v>49.77</v>
       </c>
       <c r="E94" s="1">
-        <v>42.25</v>
-      </c>
-      <c r="F94" s="1">
-        <v>-0.27</v>
+        <v>41.78</v>
+      </c>
+      <c r="F94" s="4">
+        <v>-0.22</v>
       </c>
       <c r="G94" s="4">
-        <v>13.25</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="H94" s="4">
-        <v>14.01</v>
+        <v>17.809999999999999</v>
       </c>
       <c r="I94" s="4"/>
       <c r="J94" s="4"/>
@@ -10401,26 +10423,26 @@
       </c>
     </row>
     <row r="95" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="1" t="s">
-        <v>234</v>
+      <c r="B95" s="14" t="s">
+        <v>232</v>
       </c>
       <c r="C95" s="1">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="D95" s="1">
-        <v>49.75</v>
+        <v>50.1</v>
       </c>
       <c r="E95" s="1">
-        <v>41.8</v>
+        <v>42.25</v>
       </c>
       <c r="F95" s="1">
-        <v>-0.32</v>
+        <v>-0.27</v>
       </c>
       <c r="G95" s="4">
-        <v>13.04</v>
+        <v>13.25</v>
       </c>
       <c r="H95" s="4">
-        <v>13.93</v>
+        <v>14.01</v>
       </c>
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
@@ -10482,25 +10504,25 @@
     </row>
     <row r="96" spans="2:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C96" s="4">
-        <v>700</v>
+        <v>234</v>
+      </c>
+      <c r="C96" s="1">
+        <v>545</v>
       </c>
       <c r="D96" s="1">
-        <v>49.83</v>
+        <v>49.75</v>
       </c>
       <c r="E96" s="1">
-        <v>41.78</v>
-      </c>
-      <c r="F96" s="4">
-        <v>-0.22</v>
+        <v>41.8</v>
+      </c>
+      <c r="F96" s="1">
+        <v>-0.32</v>
       </c>
       <c r="G96" s="4">
-        <v>16.77</v>
+        <v>13.04</v>
       </c>
       <c r="H96" s="4">
-        <v>17.82</v>
+        <v>13.93</v>
       </c>
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
@@ -10568,25 +10590,25 @@
     </row>
     <row r="97" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C97" s="4">
-        <v>570</v>
-      </c>
-      <c r="D97" s="4">
-        <v>51.07</v>
-      </c>
-      <c r="E97" s="4">
-        <v>42.29</v>
+        <v>700</v>
+      </c>
+      <c r="D97" s="1">
+        <v>49.83</v>
+      </c>
+      <c r="E97" s="1">
+        <v>41.78</v>
       </c>
       <c r="F97" s="4">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="G97" s="4">
-        <v>13.48</v>
+        <v>16.77</v>
       </c>
       <c r="H97" s="4">
-        <v>14.25</v>
+        <v>17.82</v>
       </c>
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
@@ -10641,24 +10663,26 @@
       <c r="B98" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C98" s="1">
+      <c r="C98" s="4">
         <v>570</v>
       </c>
-      <c r="D98" s="1">
+      <c r="D98" s="4">
         <v>51.07</v>
       </c>
-      <c r="E98" s="1">
+      <c r="E98" s="4">
         <v>42.29</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98" s="4">
         <v>-0.25</v>
       </c>
-      <c r="G98" s="1">
+      <c r="G98" s="4">
         <v>13.48</v>
       </c>
-      <c r="H98" s="1">
+      <c r="H98" s="4">
         <v>14.25</v>
       </c>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
       <c r="L98" s="1" t="s">
         <v>240</v>
       </c>
@@ -10716,29 +10740,27 @@
       </c>
     </row>
     <row r="99" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C99" s="4">
-        <v>585</v>
-      </c>
-      <c r="D99" s="4">
-        <v>51.5</v>
-      </c>
-      <c r="E99" s="4">
-        <v>43.27</v>
-      </c>
-      <c r="F99" s="4">
+      <c r="B99" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C99" s="1">
+        <v>570</v>
+      </c>
+      <c r="D99" s="1">
+        <v>51.07</v>
+      </c>
+      <c r="E99" s="1">
+        <v>42.29</v>
+      </c>
+      <c r="F99" s="1">
         <v>-0.25</v>
       </c>
-      <c r="G99" s="4">
-        <v>13.52</v>
-      </c>
-      <c r="H99" s="4">
-        <v>14.45</v>
-      </c>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
+      <c r="G99" s="1">
+        <v>13.48</v>
+      </c>
+      <c r="H99" s="1">
+        <v>14.25</v>
+      </c>
       <c r="L99" s="1" t="s">
         <v>242</v>
       </c>
@@ -10795,26 +10817,26 @@
       </c>
     </row>
     <row r="100" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="1" t="s">
-        <v>397</v>
+      <c r="B100" s="4" t="s">
+        <v>241</v>
       </c>
       <c r="C100" s="4">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="D100" s="4">
-        <v>49</v>
+        <v>51.5</v>
       </c>
       <c r="E100" s="4">
-        <v>40.799999999999997</v>
+        <v>43.27</v>
       </c>
       <c r="F100" s="4">
         <v>-0.25</v>
       </c>
       <c r="G100" s="4">
-        <v>14.96</v>
+        <v>13.52</v>
       </c>
       <c r="H100" s="4">
-        <v>15.86</v>
+        <v>14.45</v>
       </c>
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
@@ -10875,25 +10897,25 @@
     </row>
     <row r="101" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="1" t="s">
-        <v>243</v>
+        <v>397</v>
       </c>
       <c r="C101" s="4">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="D101" s="4">
-        <v>49.77</v>
+        <v>49</v>
       </c>
       <c r="E101" s="4">
-        <v>41.78</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="F101" s="4">
         <v>-0.25</v>
       </c>
       <c r="G101" s="4">
-        <v>16.760000000000002</v>
+        <v>14.96</v>
       </c>
       <c r="H101" s="4">
-        <v>17.809999999999999</v>
+        <v>15.86</v>
       </c>
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
@@ -10960,29 +10982,29 @@
       </c>
     </row>
     <row r="102" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="14" t="s">
-        <v>245</v>
+      <c r="B102" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="C102" s="4">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="D102" s="4">
-        <v>49.9</v>
+        <v>49.77</v>
       </c>
       <c r="E102" s="4">
-        <v>41.96</v>
+        <v>41.78</v>
       </c>
       <c r="F102" s="4">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="G102" s="4">
-        <v>13.11</v>
-      </c>
-      <c r="H102" s="23">
-        <v>14</v>
-      </c>
-      <c r="I102" s="23"/>
-      <c r="J102" s="23"/>
+        <v>16.760000000000002</v>
+      </c>
+      <c r="H102" s="4">
+        <v>17.809999999999999</v>
+      </c>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
       <c r="L102" s="1" t="s">
         <v>248</v>
       </c>
@@ -11035,7 +11057,7 @@
     </row>
     <row r="103" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C103" s="4">
         <v>550</v>
@@ -11120,29 +11142,29 @@
       </c>
     </row>
     <row r="104" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C104" s="1">
-        <v>560</v>
-      </c>
-      <c r="D104" s="1">
-        <v>51.1</v>
-      </c>
-      <c r="E104" s="1">
-        <v>42.4</v>
-      </c>
-      <c r="F104" s="1">
+      <c r="B104" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="C104" s="4">
+        <v>550</v>
+      </c>
+      <c r="D104" s="4">
+        <v>49.9</v>
+      </c>
+      <c r="E104" s="4">
+        <v>41.96</v>
+      </c>
+      <c r="F104" s="4">
         <v>-0.26</v>
       </c>
       <c r="G104" s="4">
-        <v>13.21</v>
-      </c>
-      <c r="H104" s="4">
-        <v>13.95</v>
-      </c>
-      <c r="I104" s="4"/>
-      <c r="J104" s="4"/>
+        <v>13.11</v>
+      </c>
+      <c r="H104" s="23">
+        <v>14</v>
+      </c>
+      <c r="I104" s="23"/>
+      <c r="J104" s="23"/>
       <c r="L104" s="1" t="s">
         <v>252</v>
       </c>
@@ -11207,26 +11229,28 @@
     </row>
     <row r="105" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="1" t="s">
-        <v>398</v>
+        <v>249</v>
       </c>
       <c r="C105" s="1">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="D105" s="1">
-        <v>54.63</v>
+        <v>51.1</v>
       </c>
       <c r="E105" s="1">
-        <v>44.3</v>
+        <v>42.4</v>
       </c>
       <c r="F105" s="1">
         <v>-0.26</v>
       </c>
-      <c r="G105" s="1">
-        <v>13.17</v>
-      </c>
-      <c r="H105" s="1">
-        <v>13.81</v>
-      </c>
+      <c r="G105" s="4">
+        <v>13.21</v>
+      </c>
+      <c r="H105" s="4">
+        <v>13.95</v>
+      </c>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
       <c r="L105" s="1" t="s">
         <v>254</v>
       </c>
@@ -11292,28 +11316,26 @@
     </row>
     <row r="106" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="1" t="s">
-        <v>251</v>
+        <v>398</v>
       </c>
       <c r="C106" s="1">
-        <v>505</v>
+        <v>590</v>
       </c>
       <c r="D106" s="1">
-        <v>45.52</v>
+        <v>54.63</v>
       </c>
       <c r="E106" s="1">
-        <v>37.479999999999997</v>
+        <v>44.3</v>
       </c>
       <c r="F106" s="1">
-        <v>-0.28000000000000003</v>
-      </c>
-      <c r="G106" s="4">
-        <v>13.48</v>
-      </c>
-      <c r="H106" s="4">
-        <v>13.92</v>
-      </c>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
+        <v>-0.26</v>
+      </c>
+      <c r="G106" s="1">
+        <v>13.17</v>
+      </c>
+      <c r="H106" s="1">
+        <v>13.81</v>
+      </c>
       <c r="L106" s="1" t="s">
         <v>256</v>
       </c>
@@ -11354,25 +11376,25 @@
     </row>
     <row r="107" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C107" s="4">
-        <v>615</v>
-      </c>
-      <c r="D107" s="4">
-        <v>48.5</v>
-      </c>
-      <c r="E107" s="4">
-        <v>40.590000000000003</v>
-      </c>
-      <c r="F107" s="4">
-        <v>-0.24</v>
+        <v>251</v>
+      </c>
+      <c r="C107" s="1">
+        <v>505</v>
+      </c>
+      <c r="D107" s="1">
+        <v>45.52</v>
+      </c>
+      <c r="E107" s="1">
+        <v>37.479999999999997</v>
+      </c>
+      <c r="F107" s="1">
+        <v>-0.28000000000000003</v>
       </c>
       <c r="G107" s="4">
-        <v>15.08</v>
+        <v>13.48</v>
       </c>
       <c r="H107" s="4">
-        <v>16</v>
+        <v>13.92</v>
       </c>
       <c r="I107" s="4"/>
       <c r="J107" s="4"/>
@@ -11440,25 +11462,25 @@
     </row>
     <row r="108" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C108" s="4">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="D108" s="4">
         <v>48.5</v>
       </c>
       <c r="E108" s="4">
-        <v>40.24</v>
+        <v>40.590000000000003</v>
       </c>
       <c r="F108" s="4">
         <v>-0.24</v>
       </c>
       <c r="G108" s="4">
-        <v>15.41</v>
+        <v>15.08</v>
       </c>
       <c r="H108" s="4">
-        <v>16.260000000000002</v>
+        <v>16</v>
       </c>
       <c r="I108" s="4"/>
       <c r="J108" s="4"/>
@@ -11522,25 +11544,25 @@
     </row>
     <row r="109" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C109" s="4">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="D109" s="4">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="E109" s="4">
-        <v>40.46</v>
+        <v>40.24</v>
       </c>
       <c r="F109" s="4">
         <v>-0.24</v>
       </c>
       <c r="G109" s="4">
-        <v>15.45</v>
+        <v>15.41</v>
       </c>
       <c r="H109" s="4">
-        <v>16.32</v>
+        <v>16.260000000000002</v>
       </c>
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
@@ -11608,25 +11630,25 @@
     </row>
     <row r="110" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C110" s="1">
-        <v>450</v>
-      </c>
-      <c r="D110" s="1">
-        <v>49.75</v>
-      </c>
-      <c r="E110" s="1">
-        <v>41</v>
-      </c>
-      <c r="F110" s="1">
-        <v>-0.33</v>
+        <v>75</v>
+      </c>
+      <c r="C110" s="4">
+        <v>625</v>
+      </c>
+      <c r="D110" s="4">
+        <v>48.7</v>
+      </c>
+      <c r="E110" s="4">
+        <v>40.46</v>
+      </c>
+      <c r="F110" s="4">
+        <v>-0.24</v>
       </c>
       <c r="G110" s="4">
-        <v>10.98</v>
+        <v>15.45</v>
       </c>
       <c r="H110" s="4">
-        <v>11.55</v>
+        <v>16.32</v>
       </c>
       <c r="I110" s="4"/>
       <c r="J110" s="4"/>
@@ -11702,25 +11724,25 @@
     </row>
     <row r="111" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C111" s="1">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="D111" s="1">
-        <v>50</v>
+        <v>49.75</v>
       </c>
       <c r="E111" s="1">
-        <v>41.9</v>
+        <v>41</v>
       </c>
       <c r="F111" s="1">
-        <v>-0.28999999999999998</v>
+        <v>-0.33</v>
       </c>
       <c r="G111" s="4">
-        <v>13.13</v>
+        <v>10.98</v>
       </c>
       <c r="H111" s="4">
-        <v>13.75</v>
+        <v>11.55</v>
       </c>
       <c r="I111" s="4"/>
       <c r="J111" s="4"/>
@@ -11785,25 +11807,25 @@
     </row>
     <row r="112" spans="2:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C112" s="1">
-        <v>440</v>
+        <v>550</v>
       </c>
       <c r="D112" s="1">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="E112" s="1">
-        <v>40.799999999999997</v>
+        <v>41.9</v>
       </c>
       <c r="F112" s="1">
-        <v>-0.33</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="G112" s="4">
-        <v>10.78</v>
+        <v>13.13</v>
       </c>
       <c r="H112" s="4">
-        <v>11.34</v>
+        <v>13.75</v>
       </c>
       <c r="I112" s="4"/>
       <c r="J112" s="4"/>
@@ -11871,25 +11893,25 @@
     </row>
     <row r="113" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C113" s="1">
-        <v>505</v>
+        <v>440</v>
       </c>
       <c r="D113" s="1">
-        <v>45.8</v>
+        <v>49.6</v>
       </c>
       <c r="E113" s="1">
-        <v>38.4</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="F113" s="1">
         <v>-0.33</v>
       </c>
       <c r="G113" s="4">
-        <v>13.15</v>
+        <v>10.78</v>
       </c>
       <c r="H113" s="4">
-        <v>13.84</v>
+        <v>11.34</v>
       </c>
       <c r="I113" s="4"/>
       <c r="J113" s="4"/>
@@ -11957,28 +11979,28 @@
     </row>
     <row r="114" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C114" s="1">
-        <v>545</v>
+        <v>505</v>
       </c>
       <c r="D114" s="1">
-        <v>49.81</v>
+        <v>45.8</v>
       </c>
       <c r="E114" s="1">
-        <v>41.8</v>
+        <v>38.4</v>
       </c>
       <c r="F114" s="1">
-        <v>-0.27</v>
+        <v>-0.33</v>
       </c>
       <c r="G114" s="4">
-        <v>13.04</v>
-      </c>
-      <c r="H114" s="23">
-        <v>13.92</v>
-      </c>
-      <c r="I114" s="23"/>
-      <c r="J114" s="23"/>
+        <v>13.15</v>
+      </c>
+      <c r="H114" s="4">
+        <v>13.84</v>
+      </c>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
       <c r="L114" s="1" t="s">
         <v>269</v>
       </c>
@@ -12040,32 +12062,28 @@
     </row>
     <row r="115" spans="2:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
       <c r="C115" s="1">
-        <v>610</v>
+        <v>545</v>
       </c>
       <c r="D115" s="1">
-        <v>48.94</v>
+        <v>49.81</v>
       </c>
       <c r="E115" s="1">
-        <v>41.22</v>
+        <v>41.8</v>
       </c>
       <c r="F115" s="1">
-        <v>-0.25</v>
-      </c>
-      <c r="G115" s="1">
-        <v>14.8</v>
-      </c>
-      <c r="H115" s="1">
-        <v>15.44</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>-0.27</v>
+      </c>
+      <c r="G115" s="4">
+        <v>13.04</v>
+      </c>
+      <c r="H115" s="23">
+        <v>13.92</v>
+      </c>
+      <c r="I115" s="23"/>
+      <c r="J115" s="23"/>
       <c r="L115" s="1" t="s">
         <v>270</v>
       </c>
@@ -20259,24 +20277,262 @@
       </c>
     </row>
     <row r="232" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="Q232" s="16"/>
-      <c r="R232" s="16"/>
+      <c r="L232" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="M232" s="1">
+        <v>40</v>
+      </c>
+      <c r="N232" s="1">
+        <v>80000</v>
+      </c>
+      <c r="O232" s="1">
+        <v>1100</v>
+      </c>
+      <c r="P232" s="1">
+        <v>160</v>
+      </c>
+      <c r="Q232" s="16">
+        <v>206201</v>
+      </c>
+      <c r="R232" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="S232" s="1">
+        <v>40</v>
+      </c>
+      <c r="T232" s="1">
+        <v>40</v>
+      </c>
+      <c r="U232" s="1">
+        <v>40</v>
+      </c>
+      <c r="V232" s="1">
+        <v>40</v>
+      </c>
+      <c r="AH232" s="1">
+        <v>30</v>
+      </c>
+      <c r="AI232" s="1">
+        <v>30</v>
+      </c>
+      <c r="AJ232" s="1">
+        <v>30</v>
+      </c>
+      <c r="AK232" s="1">
+        <v>30</v>
+      </c>
+      <c r="AW232" s="1">
+        <v>2</v>
+      </c>
+      <c r="AX232" s="1">
+        <v>2</v>
+      </c>
+      <c r="AY232" s="1">
+        <v>2</v>
+      </c>
+      <c r="AZ232" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="233" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="Q233" s="5"/>
+      <c r="L233" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="M233" s="1">
+        <v>50</v>
+      </c>
+      <c r="N233" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O233" s="1">
+        <v>1100</v>
+      </c>
+      <c r="P233" s="1">
+        <v>180</v>
+      </c>
+      <c r="Q233" s="5" t="s">
+        <v>419</v>
+      </c>
       <c r="R233" s="5"/>
+      <c r="AW233" s="1">
+        <v>2</v>
+      </c>
+      <c r="AX233" s="1">
+        <v>2</v>
+      </c>
+      <c r="AY233" s="1">
+        <v>2</v>
+      </c>
+      <c r="AZ233" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="234" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="Q234" s="16"/>
+      <c r="L234" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="M234" s="1">
+        <v>100</v>
+      </c>
+      <c r="N234" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O234" s="1">
+        <v>1100</v>
+      </c>
+      <c r="P234" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q234" s="16">
+        <v>206210</v>
+      </c>
       <c r="R234" s="16"/>
+      <c r="AW234" s="1">
+        <v>2</v>
+      </c>
+      <c r="AX234" s="1">
+        <v>2</v>
+      </c>
+      <c r="AY234" s="1">
+        <v>2</v>
+      </c>
+      <c r="AZ234" s="1">
+        <v>2</v>
+      </c>
+      <c r="BA234" s="1">
+        <v>2</v>
+      </c>
+      <c r="BB234" s="1">
+        <v>2</v>
+      </c>
+      <c r="BC234" s="1">
+        <v>2</v>
+      </c>
+      <c r="BD234" s="1">
+        <v>2</v>
+      </c>
+      <c r="BE234" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="235" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="Q235" s="5"/>
-      <c r="R235" s="5"/>
+      <c r="L235" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="M235" s="1">
+        <v>50</v>
+      </c>
+      <c r="N235" s="1">
+        <v>75000</v>
+      </c>
+      <c r="O235" s="1">
+        <v>1100</v>
+      </c>
+      <c r="P235" s="1">
+        <v>150</v>
+      </c>
+      <c r="Q235" s="5">
+        <v>206214</v>
+      </c>
+      <c r="R235" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="S235" s="1">
+        <v>50</v>
+      </c>
+      <c r="T235" s="1">
+        <v>50</v>
+      </c>
+      <c r="U235" s="1">
+        <v>50</v>
+      </c>
+      <c r="V235" s="1">
+        <v>50</v>
+      </c>
+      <c r="AH235" s="1">
+        <v>40</v>
+      </c>
+      <c r="AI235" s="1">
+        <v>40</v>
+      </c>
+      <c r="AJ235" s="1">
+        <v>40</v>
+      </c>
+      <c r="AK235" s="1">
+        <v>40</v>
+      </c>
+      <c r="AW235" s="1">
+        <v>2</v>
+      </c>
+      <c r="AX235" s="1">
+        <v>2</v>
+      </c>
+      <c r="AY235" s="1">
+        <v>2</v>
+      </c>
+      <c r="AZ235" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="236" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="Q236" s="16"/>
-      <c r="R236" s="16"/>
+      <c r="L236" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="M236" s="1">
+        <v>40</v>
+      </c>
+      <c r="N236" s="1">
+        <v>80000</v>
+      </c>
+      <c r="O236" s="1">
+        <v>1100</v>
+      </c>
+      <c r="P236" s="1">
+        <v>150</v>
+      </c>
+      <c r="Q236" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="R236" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="S236" s="1">
+        <v>40</v>
+      </c>
+      <c r="T236" s="1">
+        <v>40</v>
+      </c>
+      <c r="U236" s="1">
+        <v>40</v>
+      </c>
+      <c r="V236" s="1">
+        <v>40</v>
+      </c>
+      <c r="AH236" s="1">
+        <v>30</v>
+      </c>
+      <c r="AI236" s="1">
+        <v>30</v>
+      </c>
+      <c r="AJ236" s="1">
+        <v>30</v>
+      </c>
+      <c r="AK236" s="1">
+        <v>30</v>
+      </c>
+      <c r="AW236" s="1">
+        <v>2</v>
+      </c>
+      <c r="AX236" s="1">
+        <v>2</v>
+      </c>
+      <c r="AY236" s="1">
+        <v>2</v>
+      </c>
+      <c r="AZ236" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="237" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q237" s="5"/>

--- a/calculo_mppt.xlsx
+++ b/calculo_mppt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enzo.ferreira\Desktop\dimensionador-fotovoltaico-sigiloso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A0302A-995D-4F30-969A-58985044C99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18795212-6BC3-4AF3-B352-C54B861FA4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-4695" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="421">
   <si>
     <t>Módulo</t>
   </si>
@@ -603,6 +603,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-100KTL-M2 </t>
     </r>
@@ -612,6 +613,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -631,6 +633,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-10K-LCO </t>
     </r>
@@ -640,6 +643,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -665,6 +669,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-15KTL-M5 </t>
     </r>
@@ -674,6 +679,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -699,6 +705,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-20KTL-M5 </t>
     </r>
@@ -708,6 +715,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -727,6 +735,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-250KTL-H1 </t>
     </r>
@@ -736,6 +745,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -755,6 +765,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-25KTL-M5 </t>
     </r>
@@ -764,6 +775,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -789,6 +801,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-3KTL-L1 </t>
     </r>
@@ -798,6 +811,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -832,6 +846,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-5KTL-L1 </t>
     </r>
@@ -841,6 +856,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -866,6 +882,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-6KTL-L1 </t>
     </r>
@@ -875,6 +892,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -906,6 +924,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-75KTL-M1 </t>
     </r>
@@ -915,6 +934,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -934,6 +954,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Huawei SUN2000-8K-LCO </t>
     </r>
@@ -943,6 +964,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>50%</t>
     </r>
@@ -1214,6 +1236,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Solis 75K 5G-PRO </t>
     </r>
@@ -1223,6 +1246,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>com 50%</t>
     </r>
@@ -1239,6 +1263,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Solis S5-GC 37,5K </t>
     </r>
@@ -1248,6 +1273,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>com 50%</t>
     </r>
@@ -1261,6 +1287,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Solis S5-GC 60K </t>
     </r>
@@ -1270,6 +1297,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>com 50%</t>
     </r>
@@ -1316,6 +1344,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Solis-75K-LV-5G-PRO </t>
     </r>
@@ -1325,6 +1354,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(C/ CONECTOR "Y")</t>
     </r>
@@ -1613,7 +1643,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1622,24 +1652,41 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color indexed="65"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="2"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1732,21 +1779,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1755,58 +1802,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1815,7 +1862,19 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2684,7 +2743,7 @@
       <c r="I3" s="4">
         <v>201741</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="32" t="s">
         <v>62</v>
       </c>
       <c r="L3" s="1" t="s">
@@ -2755,7 +2814,7 @@
       <c r="I4" s="4">
         <v>206291</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="32" t="s">
         <v>62</v>
       </c>
       <c r="L4" s="1" t="s">
@@ -2842,9 +2901,7 @@
       <c r="Q5" s="5">
         <v>167963</v>
       </c>
-      <c r="R5" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R5" s="5"/>
       <c r="S5" s="9">
         <v>40</v>
       </c>
@@ -3051,9 +3108,7 @@
       <c r="Q8" s="8">
         <v>186183</v>
       </c>
-      <c r="R8" s="8" t="s">
-        <v>62</v>
-      </c>
+      <c r="R8" s="8"/>
       <c r="S8" s="6">
         <v>40</v>
       </c>
@@ -3686,9 +3741,7 @@
       <c r="Q17" s="5">
         <v>186177</v>
       </c>
-      <c r="R17" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R17" s="5"/>
       <c r="S17" s="6">
         <v>50</v>
       </c>
@@ -3976,9 +4029,7 @@
       <c r="Q21" s="5">
         <v>167958</v>
       </c>
-      <c r="R21" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R21" s="5"/>
       <c r="S21" s="9">
         <v>35</v>
       </c>
@@ -4054,9 +4105,7 @@
       <c r="Q22" s="8">
         <v>186180</v>
       </c>
-      <c r="R22" s="8" t="s">
-        <v>62</v>
-      </c>
+      <c r="R22" s="8"/>
       <c r="S22" s="6">
         <v>60</v>
       </c>
@@ -5229,8 +5278,12 @@
       <c r="P33" s="1">
         <v>195</v>
       </c>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
+      <c r="Q33" s="5">
+        <v>90192</v>
+      </c>
+      <c r="R33" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="S33" s="15">
         <v>50</v>
       </c>
@@ -7290,7 +7343,7 @@
         <v>550</v>
       </c>
       <c r="P56" s="1">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="Q56" s="5">
         <v>182198</v>
@@ -7422,9 +7475,7 @@
       <c r="Q58" s="11">
         <v>107282</v>
       </c>
-      <c r="R58" s="11" t="s">
-        <v>62</v>
-      </c>
+      <c r="R58" s="11"/>
       <c r="S58" s="9">
         <v>40</v>
       </c>
@@ -7694,9 +7745,7 @@
       <c r="Q60" s="5">
         <v>107277</v>
       </c>
-      <c r="R60" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R60" s="5"/>
       <c r="S60" s="9">
         <v>20</v>
       </c>
@@ -8254,9 +8303,7 @@
       <c r="Q68" s="5">
         <v>107284</v>
       </c>
-      <c r="R68" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R68" s="5"/>
       <c r="S68" s="9">
         <v>115</v>
       </c>
@@ -8581,9 +8628,7 @@
       <c r="Q72" s="5">
         <v>140245</v>
       </c>
-      <c r="R72" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R72" s="5"/>
       <c r="S72" s="9">
         <v>40</v>
       </c>
@@ -8814,9 +8859,7 @@
       <c r="Q75" s="8">
         <v>121772</v>
       </c>
-      <c r="R75" s="8" t="s">
-        <v>62</v>
-      </c>
+      <c r="R75" s="8"/>
       <c r="S75" s="9">
         <v>20</v>
       </c>
@@ -8967,9 +9010,7 @@
       <c r="Q77" s="8">
         <v>140242</v>
       </c>
-      <c r="R77" s="8" t="s">
-        <v>62</v>
-      </c>
+      <c r="R77" s="8"/>
       <c r="S77" s="9">
         <v>40</v>
       </c>
@@ -9431,8 +9472,12 @@
       <c r="P83" s="1">
         <v>50</v>
       </c>
-      <c r="Q83" s="8"/>
-      <c r="R83" s="8"/>
+      <c r="Q83" s="8">
+        <v>170970</v>
+      </c>
+      <c r="R83" s="31" t="s">
+        <v>62</v>
+      </c>
       <c r="S83" s="6">
         <v>20</v>
       </c>
@@ -9617,9 +9662,7 @@
       <c r="Q85" s="8">
         <v>107281</v>
       </c>
-      <c r="R85" s="8" t="s">
-        <v>62</v>
-      </c>
+      <c r="R85" s="8"/>
       <c r="S85" s="9">
         <v>40</v>
       </c>
@@ -10062,9 +10105,7 @@
       <c r="Q89" s="8">
         <v>219935</v>
       </c>
-      <c r="R89" s="8" t="s">
-        <v>62</v>
-      </c>
+      <c r="R89" s="8"/>
       <c r="S89" s="6">
         <v>25</v>
       </c>
@@ -10122,9 +10163,7 @@
       <c r="Q90" s="5">
         <v>219936</v>
       </c>
-      <c r="R90" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R90" s="5"/>
       <c r="S90" s="6">
         <v>24</v>
       </c>
@@ -10188,9 +10227,7 @@
       <c r="Q91" s="8">
         <v>219938</v>
       </c>
-      <c r="R91" s="8" t="s">
-        <v>62</v>
-      </c>
+      <c r="R91" s="8"/>
       <c r="S91" s="6">
         <v>24</v>
       </c>
@@ -10254,9 +10291,7 @@
       <c r="Q92" s="11">
         <v>219939</v>
       </c>
-      <c r="R92" s="11" t="s">
-        <v>62</v>
-      </c>
+      <c r="R92" s="11"/>
       <c r="S92" s="6">
         <v>24</v>
       </c>
@@ -12019,9 +12054,7 @@
       <c r="Q114" s="5">
         <v>70396</v>
       </c>
-      <c r="R114" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R114" s="5"/>
       <c r="S114" s="15">
         <v>17</v>
       </c>
@@ -12102,9 +12135,7 @@
       <c r="Q115" s="16">
         <v>70397</v>
       </c>
-      <c r="R115" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R115" s="16"/>
       <c r="S115" s="12">
         <v>31.25</v>
       </c>
@@ -12479,9 +12510,7 @@
       <c r="Q122" s="5">
         <v>195100</v>
       </c>
-      <c r="R122" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R122" s="5"/>
       <c r="S122" s="9">
         <v>50</v>
       </c>
@@ -13473,9 +13502,7 @@
       <c r="Q137" s="16">
         <v>215049</v>
       </c>
-      <c r="R137" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R137" s="16"/>
       <c r="S137" s="6">
         <v>40</v>
       </c>
@@ -13516,9 +13543,7 @@
       <c r="Q138" s="5">
         <v>215050</v>
       </c>
-      <c r="R138" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R138" s="5"/>
       <c r="S138" s="6">
         <v>50</v>
       </c>
@@ -13559,9 +13584,7 @@
       <c r="Q139" s="16">
         <v>215051</v>
       </c>
-      <c r="R139" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R139" s="16"/>
       <c r="S139" s="1">
         <v>50</v>
       </c>
@@ -13607,9 +13630,7 @@
       <c r="Q140" s="5">
         <v>215052</v>
       </c>
-      <c r="R140" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R140" s="5"/>
       <c r="S140" s="1">
         <v>50</v>
       </c>
@@ -13649,9 +13670,7 @@
       <c r="Q141" s="16">
         <v>123552</v>
       </c>
-      <c r="R141" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R141" s="16"/>
       <c r="S141" s="1">
         <v>20</v>
       </c>
@@ -13691,9 +13710,7 @@
       <c r="Q142" s="5">
         <v>7490</v>
       </c>
-      <c r="R142" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R142" s="5"/>
       <c r="S142" s="12">
         <v>40</v>
       </c>
@@ -13916,8 +13933,12 @@
       <c r="P144" s="7">
         <v>950</v>
       </c>
-      <c r="Q144" s="5"/>
-      <c r="R144" s="5"/>
+      <c r="Q144" s="5">
+        <v>206226</v>
+      </c>
+      <c r="R144" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="S144" s="1">
         <v>300</v>
       </c>
@@ -14082,9 +14103,7 @@
       <c r="Q147" s="16">
         <v>218759</v>
       </c>
-      <c r="R147" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R147" s="16"/>
       <c r="S147" s="1">
         <v>19.5</v>
       </c>
@@ -14530,9 +14549,7 @@
       <c r="Q153" s="16">
         <v>88619</v>
       </c>
-      <c r="R153" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R153" s="16"/>
       <c r="S153" s="12">
         <v>50</v>
       </c>
@@ -14788,9 +14805,7 @@
       <c r="Q156" s="5">
         <v>75607</v>
       </c>
-      <c r="R156" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R156" s="5"/>
       <c r="S156" s="12">
         <v>40</v>
       </c>
@@ -14948,9 +14963,7 @@
       <c r="Q158" s="5">
         <v>83337</v>
       </c>
-      <c r="R158" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R158" s="5"/>
       <c r="S158" s="12">
         <v>40</v>
       </c>
@@ -15179,8 +15192,12 @@
       <c r="P161" s="7">
         <v>195</v>
       </c>
-      <c r="Q161" s="16"/>
-      <c r="R161" s="16"/>
+      <c r="Q161" s="16">
+        <v>206225</v>
+      </c>
+      <c r="R161" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="S161" s="1">
         <v>40</v>
       </c>
@@ -15341,9 +15358,7 @@
       <c r="Q164" s="5">
         <v>184846</v>
       </c>
-      <c r="R164" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R164" s="5"/>
       <c r="S164" s="1">
         <v>50</v>
       </c>
@@ -15452,8 +15467,12 @@
       <c r="P165" s="7">
         <v>180</v>
       </c>
-      <c r="Q165" s="16"/>
-      <c r="R165" s="16"/>
+      <c r="Q165" s="16">
+        <v>153075</v>
+      </c>
+      <c r="R165" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="S165" s="4">
         <v>50</v>
       </c>
@@ -15610,9 +15629,7 @@
       <c r="Q167" s="16">
         <v>105322</v>
       </c>
-      <c r="R167" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R167" s="16"/>
       <c r="S167" s="4">
         <v>22</v>
       </c>
@@ -16259,8 +16276,12 @@
       <c r="P175" s="10">
         <v>180</v>
       </c>
-      <c r="Q175" s="16"/>
-      <c r="R175" s="16"/>
+      <c r="Q175" s="16">
+        <v>152042</v>
+      </c>
+      <c r="R175" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="S175" s="1">
         <v>48</v>
       </c>
@@ -16365,9 +16386,7 @@
       <c r="Q177" s="16">
         <v>152048</v>
       </c>
-      <c r="R177" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R177" s="16"/>
       <c r="S177" s="12">
         <v>60</v>
       </c>
@@ -16429,8 +16448,12 @@
       <c r="P178" s="10">
         <v>180</v>
       </c>
-      <c r="Q178" s="5"/>
-      <c r="R178" s="5"/>
+      <c r="Q178" s="5">
+        <v>152043</v>
+      </c>
+      <c r="R178" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="S178" s="1">
         <v>48</v>
       </c>
@@ -16545,7 +16568,7 @@
         <v>180</v>
       </c>
       <c r="Q180" s="5">
-        <v>52731</v>
+        <v>152045</v>
       </c>
       <c r="R180" s="5" t="s">
         <v>62</v>
@@ -16686,8 +16709,12 @@
       <c r="P182" s="4">
         <v>550</v>
       </c>
-      <c r="Q182" s="5"/>
-      <c r="R182" s="5"/>
+      <c r="Q182" s="5">
+        <v>175388</v>
+      </c>
+      <c r="R182" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="S182" s="6">
         <v>113</v>
       </c>
@@ -16817,8 +16844,12 @@
       <c r="P184" s="4">
         <v>200</v>
       </c>
-      <c r="Q184" s="5"/>
-      <c r="R184" s="5"/>
+      <c r="Q184" s="5">
+        <v>153995</v>
+      </c>
+      <c r="R184" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="S184" s="15">
         <v>48</v>
       </c>
@@ -16963,8 +16994,12 @@
       <c r="P186" s="4">
         <v>250</v>
       </c>
-      <c r="Q186" s="5"/>
-      <c r="R186" s="5"/>
+      <c r="Q186" s="5">
+        <v>160673</v>
+      </c>
+      <c r="R186" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="S186" s="15">
         <v>60</v>
       </c>
@@ -17044,9 +17079,7 @@
       <c r="Q187" s="16">
         <v>152046</v>
       </c>
-      <c r="R187" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R187" s="16"/>
       <c r="S187" s="6">
         <v>48</v>
       </c>
@@ -17519,9 +17552,7 @@
       <c r="Q194" s="5">
         <v>143409</v>
       </c>
-      <c r="R194" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R194" s="5"/>
       <c r="S194" s="15">
         <v>48</v>
       </c>
@@ -17607,9 +17638,7 @@
       <c r="Q195" s="16">
         <v>143408</v>
       </c>
-      <c r="R195" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R195" s="16"/>
       <c r="S195" s="15">
         <v>22.5</v>
       </c>
@@ -17889,9 +17918,7 @@
       <c r="Q199" s="16">
         <v>170120</v>
       </c>
-      <c r="R199" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R199" s="16"/>
       <c r="S199" s="15">
         <v>48</v>
       </c>
@@ -18440,9 +18467,7 @@
       <c r="Q208" s="5">
         <v>143410</v>
       </c>
-      <c r="R208" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R208" s="5"/>
       <c r="S208" s="6">
         <v>60</v>
       </c>
@@ -18519,9 +18544,7 @@
       <c r="Q209" s="16">
         <v>163668</v>
       </c>
-      <c r="R209" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R209" s="16"/>
       <c r="S209" s="15">
         <v>48</v>
       </c>
@@ -18775,9 +18798,7 @@
       <c r="Q212" s="5">
         <v>216764</v>
       </c>
-      <c r="R212" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R212" s="5"/>
       <c r="S212" s="6">
         <v>25</v>
       </c>
@@ -18825,9 +18846,7 @@
       <c r="Q213" s="16">
         <v>216753</v>
       </c>
-      <c r="R213" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R213" s="16"/>
       <c r="S213" s="15">
         <v>40</v>
       </c>
@@ -19070,9 +19089,7 @@
       <c r="Q215" s="16">
         <v>216765</v>
       </c>
-      <c r="R215" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R215" s="16"/>
       <c r="S215" s="6">
         <v>40</v>
       </c>
@@ -19112,9 +19129,7 @@
       <c r="Q216" s="5">
         <v>216766</v>
       </c>
-      <c r="R216" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R216" s="5"/>
       <c r="S216" s="6">
         <v>40</v>
       </c>
@@ -19154,9 +19169,7 @@
       <c r="Q217" s="16">
         <v>216767</v>
       </c>
-      <c r="R217" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R217" s="16"/>
       <c r="S217" s="6">
         <v>40</v>
       </c>
@@ -19326,8 +19339,12 @@
       <c r="P219" s="1">
         <v>250</v>
       </c>
-      <c r="Q219" s="16"/>
-      <c r="R219" s="16"/>
+      <c r="Q219" s="16">
+        <v>206200</v>
+      </c>
+      <c r="R219" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="S219" s="1">
         <v>40</v>
       </c>
@@ -19373,9 +19390,7 @@
       <c r="Q220" s="5">
         <v>216768</v>
       </c>
-      <c r="R220" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R220" s="5"/>
       <c r="S220" s="1">
         <v>40</v>
       </c>
@@ -19424,9 +19439,7 @@
       <c r="Q221" s="16">
         <v>216769</v>
       </c>
-      <c r="R221" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R221" s="16"/>
       <c r="S221" s="1">
         <v>40</v>
       </c>
@@ -19471,8 +19484,12 @@
       <c r="P222" s="1">
         <v>880</v>
       </c>
-      <c r="Q222" s="5"/>
-      <c r="R222" s="5"/>
+      <c r="Q222" s="5">
+        <v>206199</v>
+      </c>
+      <c r="R222" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="S222" s="12">
         <v>60</v>
       </c>
@@ -19743,9 +19760,7 @@
       <c r="Q224" s="5">
         <v>216770</v>
       </c>
-      <c r="R224" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R224" s="5"/>
       <c r="S224" s="1">
         <v>40</v>
       </c>
@@ -19802,9 +19817,7 @@
       <c r="Q225" s="16">
         <v>216771</v>
       </c>
-      <c r="R225" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R225" s="16"/>
       <c r="S225" s="1">
         <v>40</v>
       </c>
@@ -19862,9 +19875,7 @@
       <c r="Q226" s="5">
         <v>216761</v>
       </c>
-      <c r="R226" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R226" s="5"/>
       <c r="S226" s="1">
         <v>25</v>
       </c>
@@ -19996,9 +20007,7 @@
       <c r="Q228" s="5">
         <v>216762</v>
       </c>
-      <c r="R228" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R228" s="5"/>
       <c r="S228" s="1">
         <v>25</v>
       </c>
@@ -20038,9 +20047,7 @@
       <c r="Q229" s="16">
         <v>216763</v>
       </c>
-      <c r="R229" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R229" s="16"/>
       <c r="S229" s="1">
         <v>25</v>
       </c>
@@ -20088,9 +20095,7 @@
       <c r="Q230" s="5">
         <v>107419</v>
       </c>
-      <c r="R230" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R230" s="5"/>
       <c r="S230" s="15">
         <v>40</v>
       </c>
@@ -20295,9 +20300,7 @@
       <c r="Q232" s="16">
         <v>206201</v>
       </c>
-      <c r="R232" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R232" s="16"/>
       <c r="S232" s="1">
         <v>40</v>
       </c>
@@ -20435,9 +20438,7 @@
       <c r="Q235" s="5">
         <v>206214</v>
       </c>
-      <c r="R235" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="R235" s="5"/>
       <c r="S235" s="1">
         <v>50</v>
       </c>
@@ -20494,9 +20495,7 @@
       <c r="Q236" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="R236" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="R236" s="16"/>
       <c r="S236" s="1">
         <v>40</v>
       </c>
@@ -21502,17 +21501,17 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="S88:U88">
     <cfRule type="containsBlanks" dxfId="2" priority="32">
-      <formula>LEN(TRIM(BP88))=0</formula>
+      <formula>LEN(TRIM(BM88))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3:AG239">
     <cfRule type="containsBlanks" dxfId="1" priority="1">
-      <formula>LEN(TRIM(BP3))=0</formula>
+      <formula>LEN(TRIM(BM3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH3:AV239">
     <cfRule type="containsBlanks" dxfId="0" priority="2">
-      <formula>LEN(TRIM(CE3))=0</formula>
+      <formula>LEN(TRIM(CB3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157500000008" bottom="0.78740157500000008" header="0" footer="0"/>

--- a/calculo_mppt.xlsx
+++ b/calculo_mppt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enzo.ferreira\Desktop\dimensionador-fotovoltaico-sigiloso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18795212-6BC3-4AF3-B352-C54B861FA4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0225D6-CB2A-4CC3-A05B-F9656C52F5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-4695" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="421">
   <si>
     <t>Módulo</t>
   </si>
@@ -1779,7 +1779,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1875,6 +1875,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -18798,7 +18801,9 @@
       <c r="Q212" s="5">
         <v>216764</v>
       </c>
-      <c r="R212" s="5"/>
+      <c r="R212" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="S212" s="6">
         <v>25</v>
       </c>
@@ -19089,7 +19094,9 @@
       <c r="Q215" s="16">
         <v>216765</v>
       </c>
-      <c r="R215" s="16"/>
+      <c r="R215" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="S215" s="6">
         <v>40</v>
       </c>
@@ -19129,7 +19136,9 @@
       <c r="Q216" s="5">
         <v>216766</v>
       </c>
-      <c r="R216" s="5"/>
+      <c r="R216" s="33" t="s">
+        <v>62</v>
+      </c>
       <c r="S216" s="6">
         <v>40</v>
       </c>
@@ -20007,7 +20016,9 @@
       <c r="Q228" s="5">
         <v>216762</v>
       </c>
-      <c r="R228" s="5"/>
+      <c r="R228" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="S228" s="1">
         <v>25</v>
       </c>
@@ -20047,7 +20058,9 @@
       <c r="Q229" s="16">
         <v>216763</v>
       </c>
-      <c r="R229" s="16"/>
+      <c r="R229" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="S229" s="1">
         <v>25</v>
       </c>

--- a/calculo_mppt.xlsx
+++ b/calculo_mppt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enzo.ferreira\Desktop\dimensionador-fotovoltaico-sigiloso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0225D6-CB2A-4CC3-A05B-F9656C52F5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C5C96A-C3BB-4906-B78A-A85C5553D34A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-4695" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="421">
   <si>
     <t>Módulo</t>
   </si>
@@ -1779,7 +1779,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1875,9 +1875,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -19136,7 +19133,7 @@
       <c r="Q216" s="5">
         <v>216766</v>
       </c>
-      <c r="R216" s="33" t="s">
+      <c r="R216" s="11" t="s">
         <v>62</v>
       </c>
       <c r="S216" s="6">
@@ -20370,7 +20367,33 @@
       <c r="Q233" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="R233" s="5"/>
+      <c r="R233" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="S233" s="1">
+        <v>40</v>
+      </c>
+      <c r="T233" s="1">
+        <v>40</v>
+      </c>
+      <c r="U233" s="1">
+        <v>40</v>
+      </c>
+      <c r="V233" s="1">
+        <v>40</v>
+      </c>
+      <c r="AH233" s="1">
+        <v>30</v>
+      </c>
+      <c r="AI233" s="1">
+        <v>30</v>
+      </c>
+      <c r="AJ233" s="1">
+        <v>30</v>
+      </c>
+      <c r="AK233" s="1">
+        <v>30</v>
+      </c>
       <c r="AW233" s="1">
         <v>2</v>
       </c>
@@ -20403,7 +20426,63 @@
       <c r="Q234" s="16">
         <v>206210</v>
       </c>
-      <c r="R234" s="16"/>
+      <c r="R234" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="S234" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="T234" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="U234" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="V234" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="W234" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="X234" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="Y234" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="Z234" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="AA234" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="AH234" s="1">
+        <v>30</v>
+      </c>
+      <c r="AI234" s="1">
+        <v>30</v>
+      </c>
+      <c r="AJ234" s="1">
+        <v>30</v>
+      </c>
+      <c r="AK234" s="1">
+        <v>30</v>
+      </c>
+      <c r="AL234" s="1">
+        <v>30</v>
+      </c>
+      <c r="AM234" s="1">
+        <v>30</v>
+      </c>
+      <c r="AN234" s="1">
+        <v>30</v>
+      </c>
+      <c r="AO234" s="1">
+        <v>30</v>
+      </c>
+      <c r="AP234" s="1">
+        <v>30</v>
+      </c>
       <c r="AW234" s="1">
         <v>2</v>
       </c>

--- a/calculo_mppt.xlsx
+++ b/calculo_mppt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enzo.ferreira\Desktop\dimensionador-fotovoltaico-sigiloso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C5C96A-C3BB-4906-B78A-A85C5553D34A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7769FE1B-8307-45D7-97EE-5DF5B80A2036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-4695" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="422">
   <si>
     <t>Módulo</t>
   </si>
@@ -1637,6 +1637,9 @@
   </si>
   <si>
     <t xml:space="preserve">206195	</t>
+  </si>
+  <si>
+    <t>HUAWEI 50KW T220 ON (50K-MGL0-BR)</t>
   </si>
 </sst>
 </file>
@@ -7745,7 +7748,9 @@
       <c r="Q60" s="5">
         <v>107277</v>
       </c>
-      <c r="R60" s="5"/>
+      <c r="R60" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="S60" s="9">
         <v>20</v>
       </c>
@@ -8859,7 +8864,9 @@
       <c r="Q75" s="8">
         <v>121772</v>
       </c>
-      <c r="R75" s="8"/>
+      <c r="R75" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="S75" s="9">
         <v>20</v>
       </c>
@@ -20626,8 +20633,90 @@
       </c>
     </row>
     <row r="237" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="Q237" s="5"/>
-      <c r="R237" s="5"/>
+      <c r="L237" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M237" s="1">
+        <v>50</v>
+      </c>
+      <c r="N237" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O237" s="1">
+        <v>750</v>
+      </c>
+      <c r="P237" s="1">
+        <v>160</v>
+      </c>
+      <c r="Q237" s="5">
+        <v>183058</v>
+      </c>
+      <c r="R237" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="S237" s="1">
+        <v>66</v>
+      </c>
+      <c r="T237" s="1">
+        <v>66</v>
+      </c>
+      <c r="U237" s="1">
+        <v>66</v>
+      </c>
+      <c r="V237" s="1">
+        <v>66</v>
+      </c>
+      <c r="W237" s="1">
+        <v>66</v>
+      </c>
+      <c r="X237" s="1">
+        <v>66</v>
+      </c>
+      <c r="Y237" s="1">
+        <v>66</v>
+      </c>
+      <c r="AH237" s="1">
+        <v>48</v>
+      </c>
+      <c r="AI237" s="1">
+        <v>48</v>
+      </c>
+      <c r="AJ237" s="1">
+        <v>48</v>
+      </c>
+      <c r="AK237" s="1">
+        <v>48</v>
+      </c>
+      <c r="AL237" s="1">
+        <v>48</v>
+      </c>
+      <c r="AM237" s="1">
+        <v>48</v>
+      </c>
+      <c r="AN237" s="1">
+        <v>48</v>
+      </c>
+      <c r="AW237" s="1">
+        <v>3</v>
+      </c>
+      <c r="AX237" s="1">
+        <v>3</v>
+      </c>
+      <c r="AY237" s="1">
+        <v>3</v>
+      </c>
+      <c r="AZ237" s="1">
+        <v>3</v>
+      </c>
+      <c r="BA237" s="1">
+        <v>3</v>
+      </c>
+      <c r="BB237" s="1">
+        <v>3</v>
+      </c>
+      <c r="BC237" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="238" spans="12:57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q238" s="16"/>
